--- a/upload/ar_aging_report_converted.xlsx
+++ b/upload/ar_aging_report_converted.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="509">
   <si>
     <t>Customer Header Number</t>
   </si>
@@ -71,46 +71,46 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>9,398.31</t>
-  </si>
-  <si>
-    <t>120.02</t>
-  </si>
-  <si>
-    <t>101.13</t>
+    <t>35,713.59</t>
+  </si>
+  <si>
+    <t>456.09</t>
+  </si>
+  <si>
+    <t>384.31</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>-18.78</t>
-  </si>
-  <si>
-    <t>-640.85</t>
-  </si>
-  <si>
-    <t>-22.15</t>
-  </si>
-  <si>
-    <t>-53.56</t>
-  </si>
-  <si>
-    <t>-9.25</t>
-  </si>
-  <si>
-    <t>42.24</t>
-  </si>
-  <si>
-    <t>66.09</t>
-  </si>
-  <si>
-    <t>215.19</t>
-  </si>
-  <si>
-    <t>25.85</t>
-  </si>
-  <si>
-    <t>37.25</t>
+    <t>-71.38</t>
+  </si>
+  <si>
+    <t>-2,435.23</t>
+  </si>
+  <si>
+    <t>-84.16</t>
+  </si>
+  <si>
+    <t>-203.54</t>
+  </si>
+  <si>
+    <t>-35.14</t>
+  </si>
+  <si>
+    <t>160.52</t>
+  </si>
+  <si>
+    <t>251.14</t>
+  </si>
+  <si>
+    <t>817.72</t>
+  </si>
+  <si>
+    <t>98.23</t>
+  </si>
+  <si>
+    <t>141.56</t>
   </si>
   <si>
     <t>PE000968001H</t>
@@ -119,37 +119,37 @@
     <t>SAGA  FALABELLA  S.A.</t>
   </si>
   <si>
-    <t>8,944.89</t>
-  </si>
-  <si>
-    <t>963.49</t>
-  </si>
-  <si>
-    <t>81.93</t>
-  </si>
-  <si>
-    <t>-9.07</t>
-  </si>
-  <si>
-    <t>-2.90</t>
-  </si>
-  <si>
-    <t>-646.27</t>
-  </si>
-  <si>
-    <t>-5.15</t>
-  </si>
-  <si>
-    <t>-4.09</t>
-  </si>
-  <si>
-    <t>-2.36</t>
-  </si>
-  <si>
-    <t>130.86</t>
-  </si>
-  <si>
-    <t>98.86</t>
+    <t>33,990.58</t>
+  </si>
+  <si>
+    <t>3,661.26</t>
+  </si>
+  <si>
+    <t>311.34</t>
+  </si>
+  <si>
+    <t>-34.48</t>
+  </si>
+  <si>
+    <t>-11.03</t>
+  </si>
+  <si>
+    <t>-2,455.84</t>
+  </si>
+  <si>
+    <t>-19.57</t>
+  </si>
+  <si>
+    <t>-15.55</t>
+  </si>
+  <si>
+    <t>-8.96</t>
+  </si>
+  <si>
+    <t>497.27</t>
+  </si>
+  <si>
+    <t>375.66</t>
   </si>
   <si>
     <t>PE001351001H</t>
@@ -158,49 +158,49 @@
     <t>SUPERMERCADOS PERUANOS  S.A.</t>
   </si>
   <si>
-    <t>6,277.05</t>
-  </si>
-  <si>
-    <t>815.91</t>
-  </si>
-  <si>
-    <t>90.16</t>
-  </si>
-  <si>
-    <t>1.75</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
-    <t>-610.72</t>
-  </si>
-  <si>
-    <t>-2.67</t>
-  </si>
-  <si>
-    <t>-96.01</t>
-  </si>
-  <si>
-    <t>-0.01</t>
-  </si>
-  <si>
-    <t>-1.88</t>
-  </si>
-  <si>
-    <t>-5.38</t>
-  </si>
-  <si>
-    <t>-0.48</t>
-  </si>
-  <si>
-    <t>67.40</t>
-  </si>
-  <si>
-    <t>30.14</t>
-  </si>
-  <si>
-    <t>36.30</t>
+    <t>23,852.80</t>
+  </si>
+  <si>
+    <t>3,100.45</t>
+  </si>
+  <si>
+    <t>342.61</t>
+  </si>
+  <si>
+    <t>6.65</t>
+  </si>
+  <si>
+    <t>4.61</t>
+  </si>
+  <si>
+    <t>-2,320.75</t>
+  </si>
+  <si>
+    <t>-10.16</t>
+  </si>
+  <si>
+    <t>-364.85</t>
+  </si>
+  <si>
+    <t>-0.05</t>
+  </si>
+  <si>
+    <t>-7.16</t>
+  </si>
+  <si>
+    <t>-20.46</t>
+  </si>
+  <si>
+    <t>-1.83</t>
+  </si>
+  <si>
+    <t>256.13</t>
+  </si>
+  <si>
+    <t>114.53</t>
+  </si>
+  <si>
+    <t>137.95</t>
   </si>
   <si>
     <t>PE000815001H</t>
@@ -209,19 +209,19 @@
     <t>IMPORTACIONES HIRAOKA S.A.</t>
   </si>
   <si>
-    <t>6,265.38</t>
-  </si>
-  <si>
-    <t>86.36</t>
-  </si>
-  <si>
-    <t>-144.44</t>
-  </si>
-  <si>
-    <t>-57.53</t>
-  </si>
-  <si>
-    <t>-64.14</t>
+    <t>23,808.44</t>
+  </si>
+  <si>
+    <t>328.17</t>
+  </si>
+  <si>
+    <t>-548.86</t>
+  </si>
+  <si>
+    <t>-218.62</t>
+  </si>
+  <si>
+    <t>-243.74</t>
   </si>
   <si>
     <t>PE000991001H</t>
@@ -230,16 +230,19 @@
     <t>CONECTA RETAIL S.A.</t>
   </si>
   <si>
-    <t>6,206.22</t>
-  </si>
-  <si>
-    <t>392.33</t>
-  </si>
-  <si>
-    <t>-4.55</t>
-  </si>
-  <si>
-    <t>2.21</t>
+    <t>23,583.64</t>
+  </si>
+  <si>
+    <t>1,490.87</t>
+  </si>
+  <si>
+    <t>-7.15</t>
+  </si>
+  <si>
+    <t>-17.27</t>
+  </si>
+  <si>
+    <t>8.40</t>
   </si>
   <si>
     <t>PE007152001H</t>
@@ -248,19 +251,19 @@
     <t>TIENDAS PERUANAS S.A.</t>
   </si>
   <si>
-    <t>5,577.07</t>
-  </si>
-  <si>
-    <t>300.56</t>
-  </si>
-  <si>
-    <t>-5.64</t>
-  </si>
-  <si>
-    <t>-0.44</t>
-  </si>
-  <si>
-    <t>39.53</t>
+    <t>21,192.86</t>
+  </si>
+  <si>
+    <t>1,142.11</t>
+  </si>
+  <si>
+    <t>-21.45</t>
+  </si>
+  <si>
+    <t>-1.68</t>
+  </si>
+  <si>
+    <t>150.23</t>
   </si>
   <si>
     <t>PE004467001H</t>
@@ -269,1191 +272,1215 @@
     <t>HIPERMERCADOS TOTTUS S.A.</t>
   </si>
   <si>
-    <t>5,118.02</t>
-  </si>
-  <si>
-    <t>118.47</t>
-  </si>
-  <si>
-    <t>-197.33</t>
-  </si>
-  <si>
-    <t>-38.95</t>
-  </si>
-  <si>
-    <t>-2.83</t>
-  </si>
-  <si>
-    <t>-0.42</t>
+    <t>19,448.48</t>
+  </si>
+  <si>
+    <t>450.20</t>
+  </si>
+  <si>
+    <t>-749.84</t>
+  </si>
+  <si>
+    <t>-148.01</t>
+  </si>
+  <si>
+    <t>-10.74</t>
+  </si>
+  <si>
+    <t>-1.58</t>
+  </si>
+  <si>
+    <t>-1.14</t>
+  </si>
+  <si>
+    <t>182.66</t>
+  </si>
+  <si>
+    <t>219.10</t>
+  </si>
+  <si>
+    <t>PE000801001H</t>
+  </si>
+  <si>
+    <t>CENCOSUD RETAIL PERU S.A.</t>
+  </si>
+  <si>
+    <t>11,421.55</t>
+  </si>
+  <si>
+    <t>645.76</t>
+  </si>
+  <si>
+    <t>42.12</t>
+  </si>
+  <si>
+    <t>-505.07</t>
+  </si>
+  <si>
+    <t>-237.77</t>
+  </si>
+  <si>
+    <t>70.96</t>
+  </si>
+  <si>
+    <t>69.18</t>
+  </si>
+  <si>
+    <t>PY000933011H</t>
+  </si>
+  <si>
+    <t>LASER IMPORT S.A.</t>
+  </si>
+  <si>
+    <t>10,252.02</t>
+  </si>
+  <si>
+    <t>171.67</t>
+  </si>
+  <si>
+    <t>UY000855005H</t>
+  </si>
+  <si>
+    <t>ESTAWOL S.A.</t>
+  </si>
+  <si>
+    <t>7,997.07</t>
+  </si>
+  <si>
+    <t>80.88</t>
+  </si>
+  <si>
+    <t>PE008204001H</t>
+  </si>
+  <si>
+    <t>INTEGRA RETAIL S.A.C.</t>
+  </si>
+  <si>
+    <t>6,833.54</t>
+  </si>
+  <si>
+    <t>-158.22</t>
+  </si>
+  <si>
+    <t>PY001022004H</t>
+  </si>
+  <si>
+    <t>Karry S.A.</t>
+  </si>
+  <si>
+    <t>6,616.12</t>
+  </si>
+  <si>
+    <t>BO000681002H</t>
+  </si>
+  <si>
+    <t>Dismatec S.A.</t>
+  </si>
+  <si>
+    <t>4,834.32</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>BO000785002H</t>
+  </si>
+  <si>
+    <t>Import Export Salvatierra S.A.</t>
+  </si>
+  <si>
+    <t>4,554.36</t>
+  </si>
+  <si>
+    <t>20.92</t>
+  </si>
+  <si>
+    <t>PE000952001H</t>
+  </si>
+  <si>
+    <t>REPRESENTACIONES VARGAS S.A.</t>
+  </si>
+  <si>
+    <t>4,022.58</t>
+  </si>
+  <si>
+    <t>-6.84</t>
+  </si>
+  <si>
+    <t>-8.28</t>
+  </si>
+  <si>
+    <t>-183.11</t>
+  </si>
+  <si>
+    <t>-2.45</t>
+  </si>
+  <si>
+    <t>-3.61</t>
+  </si>
+  <si>
+    <t>-36.76</t>
+  </si>
+  <si>
+    <t>PE003887001H</t>
+  </si>
+  <si>
+    <t>ESTILOS S.R.L.</t>
+  </si>
+  <si>
+    <t>2,770.81</t>
+  </si>
+  <si>
+    <t>148.95</t>
+  </si>
+  <si>
+    <t>-38.44</t>
+  </si>
+  <si>
+    <t>-263.46</t>
+  </si>
+  <si>
+    <t>-2.00</t>
+  </si>
+  <si>
+    <t>-8.03</t>
+  </si>
+  <si>
+    <t>-52.83</t>
+  </si>
+  <si>
+    <t>PE000820001H</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES RUBI S.A.</t>
+  </si>
+  <si>
+    <t>2,404.24</t>
+  </si>
+  <si>
+    <t>-0.59</t>
+  </si>
+  <si>
+    <t>PE008104001H</t>
+  </si>
+  <si>
+    <t>CONECTA RETAIL SELVA S.A.C.</t>
+  </si>
+  <si>
+    <t>2,337.79</t>
+  </si>
+  <si>
+    <t>195.11</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>PE008110001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL REFRIGERACION PERU S</t>
+  </si>
+  <si>
+    <t>2,079.19</t>
+  </si>
+  <si>
+    <t>279.00</t>
+  </si>
+  <si>
+    <t>PE000984001H</t>
+  </si>
+  <si>
+    <t>INGRAM MICRO S.A.C.</t>
+  </si>
+  <si>
+    <t>2,032.05</t>
+  </si>
+  <si>
+    <t>9.25</t>
+  </si>
+  <si>
+    <t>-78.95</t>
+  </si>
+  <si>
+    <t>-2.19</t>
+  </si>
+  <si>
+    <t>-0.51</t>
+  </si>
+  <si>
+    <t>-1.56</t>
+  </si>
+  <si>
+    <t>PE008158001H</t>
+  </si>
+  <si>
+    <t>HOMECENTERS PERUANOS S.A.</t>
+  </si>
+  <si>
+    <t>1,975.74</t>
+  </si>
+  <si>
+    <t>246.41</t>
+  </si>
+  <si>
+    <t>17.16</t>
+  </si>
+  <si>
+    <t>7.72</t>
+  </si>
+  <si>
+    <t>-182.12</t>
+  </si>
+  <si>
+    <t>-1.94</t>
+  </si>
+  <si>
+    <t>11.28</t>
+  </si>
+  <si>
+    <t>PE001839001H</t>
+  </si>
+  <si>
+    <t>PC LINK SOCIEDAD ANONIMA CERRA</t>
+  </si>
+  <si>
+    <t>1,701.26</t>
+  </si>
+  <si>
+    <t>116.36</t>
+  </si>
+  <si>
+    <t>-119.55</t>
+  </si>
+  <si>
+    <t>-2.68</t>
+  </si>
+  <si>
+    <t>PE006374001H</t>
+  </si>
+  <si>
+    <t>TIENDAS DEL MEJORAMIENTO DEL H</t>
+  </si>
+  <si>
+    <t>1,624.12</t>
+  </si>
+  <si>
+    <t>238.24</t>
+  </si>
+  <si>
+    <t>175.32</t>
+  </si>
+  <si>
+    <t>-2.24</t>
+  </si>
+  <si>
+    <t>-141.06</t>
+  </si>
+  <si>
+    <t>-1.85</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>15.73</t>
+  </si>
+  <si>
+    <t>PE002194001H</t>
+  </si>
+  <si>
+    <t>COMPUDISKETT SRL</t>
+  </si>
+  <si>
+    <t>1,527.89</t>
+  </si>
+  <si>
+    <t>-0.40</t>
+  </si>
+  <si>
+    <t>-4.47</t>
+  </si>
+  <si>
+    <t>PE002897001H</t>
+  </si>
+  <si>
+    <t>GRUPO DELTRON S.A.</t>
+  </si>
+  <si>
+    <t>1,209.12</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>68.07</t>
+  </si>
+  <si>
+    <t>-0.34</t>
+  </si>
+  <si>
+    <t>-74.10</t>
+  </si>
+  <si>
+    <t>UY000615003H</t>
+  </si>
+  <si>
+    <t>OCEANLUX, S.A.</t>
+  </si>
+  <si>
+    <t>1,175.10</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>PE008303001H</t>
+  </si>
+  <si>
+    <t>GRUPO MERPES PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>1,022.31</t>
+  </si>
+  <si>
+    <t>PE006905001H</t>
+  </si>
+  <si>
+    <t>UEZU COMERCIAL SAC</t>
+  </si>
+  <si>
+    <t>1,005.02</t>
+  </si>
+  <si>
+    <t>-0.55</t>
+  </si>
+  <si>
+    <t>PE008257001H</t>
+  </si>
+  <si>
+    <t>COLDSMART PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>873.62</t>
+  </si>
+  <si>
+    <t>121.53</t>
+  </si>
+  <si>
+    <t>PE007687001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL FRIONORTE E.I.R.L.</t>
+  </si>
+  <si>
+    <t>681.35</t>
+  </si>
+  <si>
+    <t>PE008420001H</t>
+  </si>
+  <si>
+    <t>AIR COOL SYSTEM SM S.A.C.</t>
+  </si>
+  <si>
+    <t>674.85</t>
+  </si>
+  <si>
+    <t>PE004417001H</t>
+  </si>
+  <si>
+    <t>REPRESENTACIONES MONTERO S.R.L</t>
+  </si>
+  <si>
+    <t>666.65</t>
+  </si>
+  <si>
+    <t>UY000854004H</t>
+  </si>
+  <si>
+    <t>Solution Box Uruguay</t>
+  </si>
+  <si>
+    <t>651.10</t>
+  </si>
+  <si>
+    <t>PE000717001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL COUNTRY S.A.</t>
+  </si>
+  <si>
+    <t>609.48</t>
+  </si>
+  <si>
+    <t>85.54</t>
+  </si>
+  <si>
+    <t>PE008466001H</t>
+  </si>
+  <si>
+    <t>SONEPAR PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>487.07</t>
+  </si>
+  <si>
+    <t>PE008453001H</t>
+  </si>
+  <si>
+    <t>MAXIMA INTERNACIONAL S.A.</t>
+  </si>
+  <si>
+    <t>486.37</t>
+  </si>
+  <si>
+    <t>106.39</t>
+  </si>
+  <si>
+    <t>PE008292001H</t>
+  </si>
+  <si>
+    <t>One time_OBS</t>
+  </si>
+  <si>
+    <t>417.11</t>
+  </si>
+  <si>
+    <t>62.40</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>3.40</t>
+  </si>
+  <si>
+    <t>-2.61</t>
+  </si>
+  <si>
+    <t>-1.67</t>
+  </si>
+  <si>
+    <t>86.92</t>
+  </si>
+  <si>
+    <t>77.32</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>PE008153001H</t>
+  </si>
+  <si>
+    <t>DACER SOCIEDAD ANONIMA CERRADA</t>
+  </si>
+  <si>
+    <t>378.32</t>
+  </si>
+  <si>
+    <t>PE001507001H</t>
+  </si>
+  <si>
+    <t>IREDI INTERNATIONAL S.R.L</t>
+  </si>
+  <si>
+    <t>375.56</t>
+  </si>
+  <si>
+    <t>PA000001010H</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS PANAMA S.A.</t>
+  </si>
+  <si>
+    <t>346.14</t>
+  </si>
+  <si>
+    <t>PE003288001H</t>
+  </si>
+  <si>
+    <t>PKC TECHNOLOGY S.R.L.</t>
+  </si>
+  <si>
+    <t>335.08</t>
+  </si>
+  <si>
+    <t>-4.42</t>
+  </si>
+  <si>
+    <t>PE008291001H</t>
+  </si>
+  <si>
+    <t>SERFAC S.A.C.</t>
+  </si>
+  <si>
+    <t>290.56</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>PE000854001H</t>
+  </si>
+  <si>
+    <t>SUCESION JUAN PINTO RUIZ</t>
+  </si>
+  <si>
+    <t>278.21</t>
+  </si>
+  <si>
+    <t>PE000853001H</t>
+  </si>
+  <si>
+    <t>JUAN PABLO MORI E.I.R.L.</t>
+  </si>
+  <si>
+    <t>259.18</t>
+  </si>
+  <si>
+    <t>PE007607001H</t>
+  </si>
+  <si>
+    <t>INGENIEROS FRIOTEMP S.A.C.</t>
+  </si>
+  <si>
+    <t>246.88</t>
+  </si>
+  <si>
+    <t>PE008441001H</t>
+  </si>
+  <si>
+    <t>RICOH DEL PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>231.94</t>
+  </si>
+  <si>
+    <t>PE007714001H</t>
+  </si>
+  <si>
+    <t>COINREFRI AIR S.A.C.</t>
+  </si>
+  <si>
+    <t>215.26</t>
+  </si>
+  <si>
+    <t>47.93</t>
+  </si>
+  <si>
+    <t>UY000858004H</t>
+  </si>
+  <si>
+    <t>JOACAMAR</t>
+  </si>
+  <si>
+    <t>192.66</t>
+  </si>
+  <si>
+    <t>PY001162002H</t>
+  </si>
+  <si>
+    <t>CENTRONIC S.A.</t>
+  </si>
+  <si>
+    <t>189.02</t>
+  </si>
+  <si>
+    <t>PE008312001H</t>
+  </si>
+  <si>
+    <t>TIENDAS CHANCAFE S.A.C.</t>
+  </si>
+  <si>
+    <t>171.96</t>
+  </si>
+  <si>
+    <t>-0.52</t>
+  </si>
+  <si>
+    <t>-2.95</t>
+  </si>
+  <si>
+    <t>PE004725001H</t>
+  </si>
+  <si>
+    <t>NEXSYS DEL PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>170.08</t>
+  </si>
+  <si>
+    <t>-34.65</t>
+  </si>
+  <si>
+    <t>-26.84</t>
+  </si>
+  <si>
+    <t>PE008017001H</t>
+  </si>
+  <si>
+    <t>CHANCAFE ORIENTE S.A.C.</t>
+  </si>
+  <si>
+    <t>160.32</t>
+  </si>
+  <si>
+    <t>-2.27</t>
+  </si>
+  <si>
+    <t>PE004373001H</t>
+  </si>
+  <si>
+    <t>PROTERM PERU S..AC.</t>
+  </si>
+  <si>
+    <t>143.42</t>
+  </si>
+  <si>
+    <t>CO000002006H</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>140.40</t>
+  </si>
+  <si>
+    <t>PE008165001H</t>
+  </si>
+  <si>
+    <t>TODOCLIMA PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>123.28</t>
+  </si>
+  <si>
+    <t>PE008064001H</t>
+  </si>
+  <si>
+    <t>MEGA SHOP FRIO SOC. COM. RESPO</t>
+  </si>
+  <si>
+    <t>110.04</t>
+  </si>
+  <si>
+    <t>18.93</t>
+  </si>
+  <si>
+    <t>PE008139001H</t>
+  </si>
+  <si>
+    <t>GREENCORP PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>97.12</t>
+  </si>
+  <si>
+    <t>PE008020001H</t>
+  </si>
+  <si>
+    <t>HIPERMERCADOS TOTTUS ORIENTE S</t>
+  </si>
+  <si>
+    <t>90.36</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>PE000777001H</t>
+  </si>
+  <si>
+    <t>ELECTRONICA NORTE S.R.LTDA</t>
+  </si>
+  <si>
+    <t>33.87</t>
+  </si>
+  <si>
+    <t>PE003268001H</t>
+  </si>
+  <si>
+    <t>SERVICIOS ELECTRONICOS LA RECO</t>
+  </si>
+  <si>
+    <t>31.51</t>
+  </si>
+  <si>
+    <t>-1.53</t>
+  </si>
+  <si>
+    <t>PE001020001H</t>
+  </si>
+  <si>
+    <t>TECNICAV S</t>
+  </si>
+  <si>
+    <t>30.12</t>
+  </si>
+  <si>
+    <t>PY001038002H</t>
+  </si>
+  <si>
+    <t>SERVIPHIL S.R.L</t>
+  </si>
+  <si>
+    <t>30.11</t>
+  </si>
+  <si>
+    <t>PE008083001H</t>
+  </si>
+  <si>
+    <t>CLIMA TECNICA PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>27.58</t>
+  </si>
+  <si>
+    <t>PE008141001H</t>
+  </si>
+  <si>
+    <t>ANIXTER PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>26.04</t>
+  </si>
+  <si>
+    <t>UY000836002H</t>
+  </si>
+  <si>
+    <t>LAVOMAT</t>
+  </si>
+  <si>
+    <t>25.34</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>PE006831001H</t>
+  </si>
+  <si>
+    <t>FORCE SERVICE S.R.L.</t>
+  </si>
+  <si>
+    <t>23.82</t>
+  </si>
+  <si>
+    <t>PE005273001H</t>
+  </si>
+  <si>
+    <t>CESER EIRL</t>
+  </si>
+  <si>
+    <t>22.36</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>UY000853002H</t>
+  </si>
+  <si>
+    <t>Odalmar S.A.</t>
+  </si>
+  <si>
+    <t>20.59</t>
+  </si>
+  <si>
+    <t>12.92</t>
+  </si>
+  <si>
+    <t>PE006934001H</t>
+  </si>
+  <si>
+    <t>PROMOTICK S.A.C.</t>
+  </si>
+  <si>
+    <t>19.79</t>
+  </si>
+  <si>
+    <t>18.43</t>
   </si>
   <si>
     <t>-0.30</t>
   </si>
   <si>
-    <t>48.07</t>
-  </si>
-  <si>
-    <t>57.66</t>
-  </si>
-  <si>
-    <t>PE000801001H</t>
-  </si>
-  <si>
-    <t>CENCOSUD RETAIL PERU S.A.</t>
-  </si>
-  <si>
-    <t>3,005.67</t>
-  </si>
-  <si>
-    <t>169.94</t>
-  </si>
-  <si>
-    <t>11.09</t>
-  </si>
-  <si>
-    <t>-132.91</t>
-  </si>
-  <si>
-    <t>-62.57</t>
-  </si>
-  <si>
-    <t>18.67</t>
-  </si>
-  <si>
-    <t>18.21</t>
-  </si>
-  <si>
-    <t>PY000933011H</t>
-  </si>
-  <si>
-    <t>LASER IMPORT S.A.</t>
-  </si>
-  <si>
-    <t>2,708.59</t>
-  </si>
-  <si>
-    <t>45.36</t>
-  </si>
-  <si>
-    <t>UY000855005H</t>
-  </si>
-  <si>
-    <t>ESTAWOL S.A.</t>
-  </si>
-  <si>
-    <t>2,112.83</t>
-  </si>
-  <si>
-    <t>21.37</t>
-  </si>
-  <si>
-    <t>PE008204001H</t>
-  </si>
-  <si>
-    <t>INTEGRA RETAIL S.A.C.</t>
-  </si>
-  <si>
-    <t>1,798.30</t>
-  </si>
-  <si>
-    <t>-41.64</t>
-  </si>
-  <si>
-    <t>PY001022004H</t>
-  </si>
-  <si>
-    <t>Karry S.A.</t>
-  </si>
-  <si>
-    <t>1,747.99</t>
-  </si>
-  <si>
-    <t>BO000681002H</t>
-  </si>
-  <si>
-    <t>Dismatec S.A.</t>
-  </si>
-  <si>
-    <t>1,277.23</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>BO000785002H</t>
-  </si>
-  <si>
-    <t>Import Export Salvatierra S.A.</t>
-  </si>
-  <si>
-    <t>1,203.27</t>
-  </si>
-  <si>
-    <t>5.53</t>
-  </si>
-  <si>
-    <t>PE000952001H</t>
-  </si>
-  <si>
-    <t>REPRESENTACIONES VARGAS S.A.</t>
-  </si>
-  <si>
-    <t>1,058.57</t>
-  </si>
-  <si>
-    <t>-1.81</t>
-  </si>
-  <si>
-    <t>-2.18</t>
-  </si>
-  <si>
-    <t>-48.19</t>
-  </si>
-  <si>
-    <t>-0.64</t>
-  </si>
-  <si>
-    <t>-0.95</t>
-  </si>
-  <si>
-    <t>-9.67</t>
-  </si>
-  <si>
-    <t>PE003887001H</t>
-  </si>
-  <si>
-    <t>ESTILOS S.R.L.</t>
-  </si>
-  <si>
-    <t>729.16</t>
-  </si>
-  <si>
-    <t>39.20</t>
-  </si>
-  <si>
-    <t>-10.12</t>
-  </si>
-  <si>
-    <t>-69.33</t>
-  </si>
-  <si>
-    <t>-0.53</t>
-  </si>
-  <si>
-    <t>-2.11</t>
-  </si>
-  <si>
-    <t>-13.90</t>
-  </si>
-  <si>
-    <t>PE000820001H</t>
-  </si>
-  <si>
-    <t>IMPORTACIONES RUBI S.A.</t>
-  </si>
-  <si>
-    <t>632.69</t>
-  </si>
-  <si>
-    <t>-0.16</t>
-  </si>
-  <si>
-    <t>PE008104001H</t>
-  </si>
-  <si>
-    <t>CONECTA RETAIL SELVA S.A.C.</t>
-  </si>
-  <si>
-    <t>615.21</t>
-  </si>
-  <si>
-    <t>51.34</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>PE008110001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL REFRIGERACION PERU S</t>
-  </si>
-  <si>
-    <t>549.32</t>
-  </si>
-  <si>
-    <t>73.71</t>
-  </si>
-  <si>
-    <t>PE000984001H</t>
-  </si>
-  <si>
-    <t>INGRAM MICRO S.A.C.</t>
-  </si>
-  <si>
-    <t>536.87</t>
-  </si>
-  <si>
-    <t>2.44</t>
-  </si>
-  <si>
-    <t>-20.86</t>
-  </si>
-  <si>
-    <t>-0.58</t>
-  </si>
-  <si>
-    <t>-0.14</t>
-  </si>
-  <si>
-    <t>-0.41</t>
-  </si>
-  <si>
-    <t>PE008158001H</t>
-  </si>
-  <si>
-    <t>HOMECENTERS PERUANOS S.A.</t>
-  </si>
-  <si>
-    <t>519.93</t>
-  </si>
-  <si>
-    <t>64.84</t>
-  </si>
-  <si>
-    <t>4.52</t>
-  </si>
-  <si>
-    <t>2.03</t>
-  </si>
-  <si>
-    <t>-47.93</t>
-  </si>
-  <si>
-    <t>-0.51</t>
-  </si>
-  <si>
-    <t>2.97</t>
-  </si>
-  <si>
-    <t>PE001839001H</t>
-  </si>
-  <si>
-    <t>PC LINK SOCIEDAD ANONIMA CERRA</t>
-  </si>
-  <si>
-    <t>449.47</t>
-  </si>
-  <si>
-    <t>30.74</t>
-  </si>
-  <si>
-    <t>-31.58</t>
-  </si>
-  <si>
-    <t>-0.71</t>
-  </si>
-  <si>
-    <t>PE006374001H</t>
-  </si>
-  <si>
-    <t>TIENDAS DEL MEJORAMIENTO DEL H</t>
-  </si>
-  <si>
-    <t>427.40</t>
-  </si>
-  <si>
-    <t>62.70</t>
-  </si>
-  <si>
-    <t>46.14</t>
-  </si>
-  <si>
-    <t>-0.59</t>
-  </si>
-  <si>
-    <t>-37.12</t>
-  </si>
-  <si>
-    <t>-0.49</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>4.14</t>
-  </si>
-  <si>
-    <t>PE002194001H</t>
-  </si>
-  <si>
-    <t>COMPUDISKETT SRL</t>
-  </si>
-  <si>
-    <t>403.67</t>
-  </si>
-  <si>
-    <t>-0.11</t>
-  </si>
-  <si>
-    <t>-1.18</t>
-  </si>
-  <si>
-    <t>PE002897001H</t>
-  </si>
-  <si>
-    <t>GRUPO DELTRON S.A.</t>
-  </si>
-  <si>
-    <t>319.45</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>17.98</t>
+    <t>-2.60</t>
+  </si>
+  <si>
+    <t>PE008455001H</t>
+  </si>
+  <si>
+    <t>REWARDS PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>19.72</t>
+  </si>
+  <si>
+    <t>BO000662002H</t>
+  </si>
+  <si>
+    <t>Censel</t>
+  </si>
+  <si>
+    <t>19.16</t>
+  </si>
+  <si>
+    <t>PE008022001H</t>
+  </si>
+  <si>
+    <t>SERTEPI E.I.R.L.</t>
+  </si>
+  <si>
+    <t>17.46</t>
+  </si>
+  <si>
+    <t>PE004102001H</t>
+  </si>
+  <si>
+    <t>MI NEGOCIO EMPRESA INDIVIDUAL</t>
+  </si>
+  <si>
+    <t>17.27</t>
+  </si>
+  <si>
+    <t>-6.10</t>
+  </si>
+  <si>
+    <t>-2.75</t>
+  </si>
+  <si>
+    <t>-5.90</t>
+  </si>
+  <si>
+    <t>PE008105001H</t>
+  </si>
+  <si>
+    <t>LATINAMENITIES S.A.C.</t>
+  </si>
+  <si>
+    <t>17.23</t>
+  </si>
+  <si>
+    <t>PE007296001H</t>
+  </si>
+  <si>
+    <t>One time_Employee</t>
+  </si>
+  <si>
+    <t>16.85</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>4.95</t>
+  </si>
+  <si>
+    <t>PE004799001H</t>
+  </si>
+  <si>
+    <t>SERVINORTE EIRL</t>
+  </si>
+  <si>
+    <t>16.19</t>
+  </si>
+  <si>
+    <t>PE004800001H</t>
+  </si>
+  <si>
+    <t>MULTIREPARACIONES DIGITALES IC</t>
+  </si>
+  <si>
+    <t>15.11</t>
+  </si>
+  <si>
+    <t>-0.27</t>
+  </si>
+  <si>
+    <t>PE001399001H</t>
+  </si>
+  <si>
+    <t>ASPERSUD</t>
+  </si>
+  <si>
+    <t>13.71</t>
+  </si>
+  <si>
+    <t>8.83</t>
+  </si>
+  <si>
+    <t>PE008175001H</t>
+  </si>
+  <si>
+    <t>HAROLD MULTISERVIS EIRL</t>
+  </si>
+  <si>
+    <t>13.46</t>
+  </si>
+  <si>
+    <t>PE008108001H</t>
+  </si>
+  <si>
+    <t>SERVICIOS DIGITALES E &amp; R E.I.</t>
+  </si>
+  <si>
+    <t>11.99</t>
+  </si>
+  <si>
+    <t>PE008237001H</t>
+  </si>
+  <si>
+    <t>TGESTIONA SERVICIOS GLOBALES S</t>
+  </si>
+  <si>
+    <t>7.80</t>
+  </si>
+  <si>
+    <t>PE004853001H</t>
+  </si>
+  <si>
+    <t>E LAU SI EIRL</t>
+  </si>
+  <si>
+    <t>7.17</t>
+  </si>
+  <si>
+    <t>PE008036001H</t>
+  </si>
+  <si>
+    <t>SERVICIOS ELECTRONICOS SERVINO</t>
+  </si>
+  <si>
+    <t>6.11</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>PE001016001H</t>
+  </si>
+  <si>
+    <t>SERV.TEC.</t>
+  </si>
+  <si>
+    <t>5.64</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>PE008198001H</t>
+  </si>
+  <si>
+    <t>CORPORACION EFAMEINSA E INGENI</t>
+  </si>
+  <si>
+    <t>5.39</t>
+  </si>
+  <si>
+    <t>PE008171001H</t>
+  </si>
+  <si>
+    <t>TELECOMUNICACIONES STUDIO WEB</t>
+  </si>
+  <si>
+    <t>2.96</t>
+  </si>
+  <si>
+    <t>PE007297001H</t>
+  </si>
+  <si>
+    <t>One time_SVC</t>
+  </si>
+  <si>
+    <t>2.46</t>
   </si>
   <si>
     <t>-0.09</t>
   </si>
   <si>
-    <t>-19.58</t>
-  </si>
-  <si>
-    <t>UY000615003H</t>
-  </si>
-  <si>
-    <t>OCEANLUX, S.A.</t>
-  </si>
-  <si>
-    <t>310.46</t>
-  </si>
-  <si>
-    <t>PE008303001H</t>
-  </si>
-  <si>
-    <t>GRUPO MERPES PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>269.03</t>
-  </si>
-  <si>
-    <t>PE006905001H</t>
-  </si>
-  <si>
-    <t>UEZU COMERCIAL SAC</t>
-  </si>
-  <si>
-    <t>265.52</t>
-  </si>
-  <si>
-    <t>-0.15</t>
-  </si>
-  <si>
-    <t>PE008257001H</t>
-  </si>
-  <si>
-    <t>COLDSMART PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>230.81</t>
-  </si>
-  <si>
-    <t>32.11</t>
-  </si>
-  <si>
-    <t>PE007687001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL FRIONORTE E.I.R.L.</t>
-  </si>
-  <si>
-    <t>180.01</t>
-  </si>
-  <si>
-    <t>PE008420001H</t>
-  </si>
-  <si>
-    <t>AIR COOL SYSTEM SM S.A.C.</t>
-  </si>
-  <si>
-    <t>178.30</t>
-  </si>
-  <si>
-    <t>PE004417001H</t>
-  </si>
-  <si>
-    <t>REPRESENTACIONES MONTERO S.R.L</t>
-  </si>
-  <si>
-    <t>176.13</t>
-  </si>
-  <si>
-    <t>UY000854004H</t>
-  </si>
-  <si>
-    <t>Solution Box Uruguay</t>
-  </si>
-  <si>
-    <t>172.02</t>
-  </si>
-  <si>
-    <t>PE000717001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL COUNTRY S.A.</t>
-  </si>
-  <si>
-    <t>160.39</t>
-  </si>
-  <si>
-    <t>22.51</t>
-  </si>
-  <si>
-    <t>PE008466001H</t>
-  </si>
-  <si>
-    <t>SONEPAR PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>128.69</t>
-  </si>
-  <si>
-    <t>PE008453001H</t>
-  </si>
-  <si>
-    <t>MAXIMA INTERNACIONAL S.A.</t>
-  </si>
-  <si>
-    <t>128.50</t>
-  </si>
-  <si>
-    <t>28.11</t>
-  </si>
-  <si>
-    <t>PE008292001H</t>
-  </si>
-  <si>
-    <t>One time_OBS</t>
-  </si>
-  <si>
-    <t>109.76</t>
-  </si>
-  <si>
-    <t>16.42</t>
-  </si>
-  <si>
-    <t>0.01</t>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>PY001043003H</t>
+  </si>
+  <si>
+    <t>ENVING S.A.</t>
+  </si>
+  <si>
+    <t>2.35</t>
+  </si>
+  <si>
+    <t>PE008439001H</t>
+  </si>
+  <si>
+    <t>SEAL TELECOM COMERCIO E SERVIC</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>UY000851005H</t>
+  </si>
+  <si>
+    <t>INGENIERO TUGENTMAN</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>PE005274001H</t>
+  </si>
+  <si>
+    <t>CORPORACION PERUANA DE SERVICI</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>PE003269001H</t>
+  </si>
+  <si>
+    <t>MELGISC ELECTRONICS EIRL</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>PY001035002H</t>
+  </si>
+  <si>
+    <t>MIGUEL MAKOTO NISHIOEDA TSUKUD</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>PE008030001H</t>
+  </si>
+  <si>
+    <t>T &amp; C ELECTRONIC'S E.I.R.L.</t>
+  </si>
+  <si>
+    <t>PY001168001H</t>
+  </si>
+  <si>
+    <t>RIGSTAR S.A.</t>
+  </si>
+  <si>
+    <t>361.89</t>
+  </si>
+  <si>
+    <t>PE000001006H</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS PERU S.A.</t>
+  </si>
+  <si>
+    <t>312.50</t>
+  </si>
+  <si>
+    <t>PE005206001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL IMPORTADORA J. MORA</t>
+  </si>
+  <si>
+    <t>71.12</t>
+  </si>
+  <si>
+    <t>-4.70</t>
+  </si>
+  <si>
+    <t>PE008239001H</t>
+  </si>
+  <si>
+    <t>DELEXPORT E.I.R.L.</t>
+  </si>
+  <si>
+    <t>35.68</t>
+  </si>
+  <si>
+    <t>PE000759001H</t>
+  </si>
+  <si>
+    <t>DERRAMA MAGISTERIAL</t>
+  </si>
+  <si>
+    <t>34.27</t>
+  </si>
+  <si>
+    <t>27.79</t>
+  </si>
+  <si>
+    <t>PE008220001H</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES MONTERO E.I.R.L.</t>
+  </si>
+  <si>
+    <t>31.00</t>
+  </si>
+  <si>
+    <t>PE008423001H</t>
+  </si>
+  <si>
+    <t>SUMINISTROS E INVERSIONES DEL</t>
+  </si>
+  <si>
+    <t>16.70</t>
+  </si>
+  <si>
+    <t>PE000690001H</t>
+  </si>
+  <si>
+    <t>CENSEL E.I.R.L.</t>
+  </si>
+  <si>
+    <t>6.18</t>
+  </si>
+  <si>
+    <t>PE008125001H</t>
+  </si>
+  <si>
+    <t>TORALVA FLORES JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>2.92</t>
+  </si>
+  <si>
+    <t>PE008131001H</t>
+  </si>
+  <si>
+    <t>COLD MACHINES S.A.C</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>PE001009001H</t>
+  </si>
+  <si>
+    <t>ELECTRONICA A Y C EIRL</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>PE008217001H</t>
+  </si>
+  <si>
+    <t>OK HOUSE E.I.R.L.</t>
   </si>
   <si>
     <t>0.90</t>
   </si>
   <si>
-    <t>-0.69</t>
-  </si>
-  <si>
-    <t>22.87</t>
-  </si>
-  <si>
-    <t>20.35</t>
-  </si>
-  <si>
-    <t>0.19</t>
-  </si>
-  <si>
-    <t>PE008153001H</t>
-  </si>
-  <si>
-    <t>DACER SOCIEDAD ANONIMA CERRADA</t>
-  </si>
-  <si>
-    <t>99.95</t>
-  </si>
-  <si>
-    <t>PE001507001H</t>
-  </si>
-  <si>
-    <t>IREDI INTERNATIONAL S.R.L</t>
-  </si>
-  <si>
-    <t>99.22</t>
-  </si>
-  <si>
-    <t>PA000001010H</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS PANAMA S.A.</t>
-  </si>
-  <si>
-    <t>91.45</t>
-  </si>
-  <si>
-    <t>PE003288001H</t>
-  </si>
-  <si>
-    <t>PKC TECHNOLOGY S.R.L.</t>
-  </si>
-  <si>
-    <t>88.18</t>
-  </si>
-  <si>
-    <t>-1.16</t>
-  </si>
-  <si>
-    <t>PE008291001H</t>
-  </si>
-  <si>
-    <t>SERFAC S.A.C.</t>
-  </si>
-  <si>
-    <t>76.76</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>PE000854001H</t>
-  </si>
-  <si>
-    <t>SUCESION JUAN PINTO RUIZ</t>
-  </si>
-  <si>
-    <t>73.50</t>
-  </si>
-  <si>
-    <t>PE000853001H</t>
-  </si>
-  <si>
-    <t>JUAN PABLO MORI E.I.R.L.</t>
-  </si>
-  <si>
-    <t>68.20</t>
-  </si>
-  <si>
-    <t>PE007607001H</t>
-  </si>
-  <si>
-    <t>INGENIEROS FRIOTEMP S.A.C.</t>
-  </si>
-  <si>
-    <t>65.23</t>
-  </si>
-  <si>
-    <t>PE008441001H</t>
-  </si>
-  <si>
-    <t>RICOH DEL PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>61.28</t>
-  </si>
-  <si>
-    <t>PE007714001H</t>
-  </si>
-  <si>
-    <t>COINREFRI AIR S.A.C.</t>
-  </si>
-  <si>
-    <t>56.87</t>
-  </si>
-  <si>
-    <t>12.66</t>
-  </si>
-  <si>
-    <t>UY000858004H</t>
-  </si>
-  <si>
-    <t>JOACAMAR</t>
-  </si>
-  <si>
-    <t>50.90</t>
-  </si>
-  <si>
-    <t>PY001162002H</t>
-  </si>
-  <si>
-    <t>CENTRONIC S.A.</t>
-  </si>
-  <si>
-    <t>49.94</t>
-  </si>
-  <si>
-    <t>PE008312001H</t>
-  </si>
-  <si>
-    <t>TIENDAS CHANCAFE S.A.C.</t>
-  </si>
-  <si>
-    <t>45.25</t>
-  </si>
-  <si>
-    <t>-0.78</t>
-  </si>
-  <si>
-    <t>PE004725001H</t>
-  </si>
-  <si>
-    <t>NEXSYS DEL PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>44.94</t>
-  </si>
-  <si>
-    <t>-9.15</t>
-  </si>
-  <si>
-    <t>-7.09</t>
-  </si>
-  <si>
-    <t>PE008017001H</t>
-  </si>
-  <si>
-    <t>CHANCAFE ORIENTE S.A.C.</t>
-  </si>
-  <si>
-    <t>42.19</t>
-  </si>
-  <si>
-    <t>-0.60</t>
-  </si>
-  <si>
-    <t>PE004373001H</t>
-  </si>
-  <si>
-    <t>PROTERM PERU S..AC.</t>
-  </si>
-  <si>
-    <t>37.89</t>
-  </si>
-  <si>
-    <t>CO000002006H</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>37.09</t>
-  </si>
-  <si>
-    <t>PE008165001H</t>
-  </si>
-  <si>
-    <t>TODOCLIMA PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>32.57</t>
-  </si>
-  <si>
-    <t>PE008064001H</t>
-  </si>
-  <si>
-    <t>MEGA SHOP FRIO SOC. COM. RESPO</t>
-  </si>
-  <si>
-    <t>29.07</t>
-  </si>
-  <si>
-    <t>5.00</t>
-  </si>
-  <si>
-    <t>PE008139001H</t>
-  </si>
-  <si>
-    <t>GREENCORP PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>25.66</t>
-  </si>
-  <si>
-    <t>PE008020001H</t>
-  </si>
-  <si>
-    <t>HIPERMERCADOS TOTTUS ORIENTE S</t>
-  </si>
-  <si>
-    <t>23.78</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>PE000777001H</t>
-  </si>
-  <si>
-    <t>ELECTRONICA NORTE S.R.LTDA</t>
-  </si>
-  <si>
-    <t>8.91</t>
-  </si>
-  <si>
-    <t>PE003268001H</t>
-  </si>
-  <si>
-    <t>SERVICIOS ELECTRONICOS LA RECO</t>
-  </si>
-  <si>
-    <t>8.29</t>
-  </si>
-  <si>
-    <t>-0.40</t>
-  </si>
-  <si>
-    <t>PY001038002H</t>
-  </si>
-  <si>
-    <t>SERVIPHIL S.R.L</t>
-  </si>
-  <si>
-    <t>7.96</t>
-  </si>
-  <si>
-    <t>PE001020001H</t>
-  </si>
-  <si>
-    <t>TECNICAV S</t>
-  </si>
-  <si>
-    <t>7.93</t>
-  </si>
-  <si>
-    <t>PE008083001H</t>
-  </si>
-  <si>
-    <t>CLIMA TECNICA PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>7.26</t>
-  </si>
-  <si>
-    <t>PE008141001H</t>
-  </si>
-  <si>
-    <t>ANIXTER PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>6.88</t>
-  </si>
-  <si>
-    <t>UY000836002H</t>
-  </si>
-  <si>
-    <t>LAVOMAT</t>
-  </si>
-  <si>
-    <t>6.69</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>PE006831001H</t>
-  </si>
-  <si>
-    <t>FORCE SERVICE S.R.L.</t>
-  </si>
-  <si>
-    <t>6.27</t>
-  </si>
-  <si>
-    <t>PE005273001H</t>
-  </si>
-  <si>
-    <t>CESER EIRL</t>
-  </si>
-  <si>
-    <t>5.88</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>UY000853002H</t>
-  </si>
-  <si>
-    <t>Odalmar S.A.</t>
-  </si>
-  <si>
-    <t>5.44</t>
-  </si>
-  <si>
-    <t>3.41</t>
-  </si>
-  <si>
-    <t>PE006934001H</t>
-  </si>
-  <si>
-    <t>PROMOTICK S.A.C.</t>
-  </si>
-  <si>
-    <t>5.21</t>
-  </si>
-  <si>
-    <t>4.85</t>
-  </si>
-  <si>
-    <t>-0.08</t>
-  </si>
-  <si>
-    <t>-0.68</t>
-  </si>
-  <si>
-    <t>PE008455001H</t>
-  </si>
-  <si>
-    <t>REWARDS PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>5.19</t>
-  </si>
-  <si>
-    <t>BO000662002H</t>
-  </si>
-  <si>
-    <t>Censel</t>
-  </si>
-  <si>
-    <t>5.06</t>
-  </si>
-  <si>
-    <t>PE008022001H</t>
-  </si>
-  <si>
-    <t>SERTEPI E.I.R.L.</t>
-  </si>
-  <si>
-    <t>4.59</t>
-  </si>
-  <si>
-    <t>PE008105001H</t>
-  </si>
-  <si>
-    <t>LATINAMENITIES S.A.C.</t>
-  </si>
-  <si>
-    <t>4.55</t>
-  </si>
-  <si>
-    <t>PE004102001H</t>
-  </si>
-  <si>
-    <t>MI NEGOCIO EMPRESA INDIVIDUAL</t>
-  </si>
-  <si>
-    <t>-1.61</t>
-  </si>
-  <si>
-    <t>-0.72</t>
-  </si>
-  <si>
-    <t>-1.55</t>
-  </si>
-  <si>
-    <t>PE007296001H</t>
-  </si>
-  <si>
-    <t>One time_Employee</t>
-  </si>
-  <si>
-    <t>4.44</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>1.30</t>
-  </si>
-  <si>
-    <t>PE004799001H</t>
-  </si>
-  <si>
-    <t>SERVINORTE EIRL</t>
-  </si>
-  <si>
-    <t>4.26</t>
-  </si>
-  <si>
-    <t>PE004800001H</t>
-  </si>
-  <si>
-    <t>MULTIREPARACIONES DIGITALES IC</t>
-  </si>
-  <si>
-    <t>3.98</t>
-  </si>
-  <si>
-    <t>-0.07</t>
-  </si>
-  <si>
-    <t>PE001399001H</t>
-  </si>
-  <si>
-    <t>ASPERSUD</t>
-  </si>
-  <si>
-    <t>3.61</t>
-  </si>
-  <si>
-    <t>2.32</t>
-  </si>
-  <si>
-    <t>PE008175001H</t>
-  </si>
-  <si>
-    <t>HAROLD MULTISERVIS EIRL</t>
-  </si>
-  <si>
-    <t>3.54</t>
-  </si>
-  <si>
-    <t>PE008108001H</t>
-  </si>
-  <si>
-    <t>SERVICIOS DIGITALES E &amp; R E.I.</t>
-  </si>
-  <si>
-    <t>3.16</t>
-  </si>
-  <si>
-    <t>PE008237001H</t>
-  </si>
-  <si>
-    <t>TGESTIONA SERVICIOS GLOBALES S</t>
-  </si>
-  <si>
-    <t>2.06</t>
-  </si>
-  <si>
-    <t>PE004853001H</t>
-  </si>
-  <si>
-    <t>E LAU SI EIRL</t>
-  </si>
-  <si>
-    <t>1.89</t>
-  </si>
-  <si>
-    <t>PE008036001H</t>
-  </si>
-  <si>
-    <t>SERVICIOS ELECTRONICOS SERVINO</t>
-  </si>
-  <si>
-    <t>1.61</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>PE001016001H</t>
-  </si>
-  <si>
-    <t>SERV.TEC.</t>
-  </si>
-  <si>
-    <t>1.48</t>
-  </si>
-  <si>
-    <t>PE008198001H</t>
-  </si>
-  <si>
-    <t>CORPORACION EFAMEINSA E INGENI</t>
-  </si>
-  <si>
-    <t>1.42</t>
-  </si>
-  <si>
-    <t>PE008171001H</t>
-  </si>
-  <si>
-    <t>TELECOMUNICACIONES STUDIO WEB</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>PE007297001H</t>
-  </si>
-  <si>
-    <t>One time_SVC</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>-0.02</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>PY001043003H</t>
-  </si>
-  <si>
-    <t>ENVING S.A.</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>PE008439001H</t>
-  </si>
-  <si>
-    <t>SEAL TELECOM COMERCIO E SERVIC</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>UY000851005H</t>
-  </si>
-  <si>
-    <t>INGENIERO TUGENTMAN</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>PE005274001H</t>
-  </si>
-  <si>
-    <t>CORPORACION PERUANA DE SERVICI</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>PE003269001H</t>
-  </si>
-  <si>
-    <t>MELGISC ELECTRONICS EIRL</t>
-  </si>
-  <si>
-    <t>PY001035002H</t>
-  </si>
-  <si>
-    <t>MIGUEL MAKOTO NISHIOEDA TSUKUD</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>PE008030001H</t>
-  </si>
-  <si>
-    <t>T &amp; C ELECTRONIC'S E.I.R.L.</t>
-  </si>
-  <si>
-    <t>PY001168001H</t>
-  </si>
-  <si>
-    <t>RIGSTAR S.A.</t>
-  </si>
-  <si>
-    <t>95.61</t>
-  </si>
-  <si>
-    <t>PE000001006H</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS PERU S.A.</t>
-  </si>
-  <si>
-    <t>82.56</t>
-  </si>
-  <si>
-    <t>PE005206001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL IMPORTADORA J. MORA</t>
-  </si>
-  <si>
-    <t>18.71</t>
-  </si>
-  <si>
-    <t>-1.24</t>
-  </si>
-  <si>
-    <t>PE008239001H</t>
-  </si>
-  <si>
-    <t>DELEXPORT E.I.R.L.</t>
-  </si>
-  <si>
-    <t>9.39</t>
-  </si>
-  <si>
-    <t>PE000759001H</t>
-  </si>
-  <si>
-    <t>DERRAMA MAGISTERIAL</t>
-  </si>
-  <si>
-    <t>9.02</t>
-  </si>
-  <si>
-    <t>7.31</t>
-  </si>
-  <si>
-    <t>PE008220001H</t>
-  </si>
-  <si>
-    <t>IMPORTACIONES MONTERO E.I.R.L.</t>
-  </si>
-  <si>
-    <t>8.19</t>
-  </si>
-  <si>
-    <t>PE008423001H</t>
-  </si>
-  <si>
-    <t>SUMINISTROS E INVERSIONES DEL</t>
-  </si>
-  <si>
-    <t>4.41</t>
-  </si>
-  <si>
-    <t>PE000690001H</t>
-  </si>
-  <si>
-    <t>CENSEL E.I.R.L.</t>
-  </si>
-  <si>
-    <t>1.63</t>
-  </si>
-  <si>
-    <t>PE008125001H</t>
-  </si>
-  <si>
-    <t>TORALVA FLORES JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>PE008131001H</t>
-  </si>
-  <si>
-    <t>COLD MACHINES S.A.C</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>PE001009001H</t>
-  </si>
-  <si>
-    <t>ELECTRONICA A Y C EIRL</t>
-  </si>
-  <si>
-    <t>PE008217001H</t>
-  </si>
-  <si>
-    <t>OK HOUSE E.I.R.L.</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
     <t>PE007675002H</t>
   </si>
   <si>
@@ -1466,12 +1493,18 @@
     <t>SERVICIO TECNICO MARTIN VILLAR</t>
   </si>
   <si>
+    <t>0.41</t>
+  </si>
+  <si>
     <t>PE008121001H</t>
   </si>
   <si>
     <t>SOLUCIONES MULTITECNICAS S.A.C</t>
   </si>
   <si>
+    <t>0.20</t>
+  </si>
+  <si>
     <t>PE008117001H</t>
   </si>
   <si>
@@ -1484,7 +1517,7 @@
     <t>XPERTOS SERVICIOS GENERALES S.</t>
   </si>
   <si>
-    <t>0.03</t>
+    <t>0.12</t>
   </si>
   <si>
     <t>PE001097001H</t>
@@ -1499,7 +1532,7 @@
     <t>TAI LOY S.A.</t>
   </si>
   <si>
-    <t>-0.99</t>
+    <t>-3.76</t>
   </si>
   <si>
     <t>AR000001039H</t>
@@ -1508,7 +1541,7 @@
     <t>LGEAR</t>
   </si>
   <si>
-    <t>5.63</t>
+    <t>21.30</t>
   </si>
 </sst>
 </file>
@@ -2433,10 +2466,10 @@
         <v>21</v>
       </c>
       <c r="P6" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="Q6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R6" t="s">
         <v>21</v>
@@ -2472,7 +2505,7 @@
         <v>21</v>
       </c>
       <c r="AC6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD6" t="s">
         <v>21</v>
@@ -2495,19 +2528,19 @@
     </row>
     <row r="7" spans="1:35">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -2543,10 +2576,10 @@
         <v>21</v>
       </c>
       <c r="Q7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S7" t="s">
         <v>21</v>
@@ -2576,7 +2609,7 @@
         <v>21</v>
       </c>
       <c r="AB7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC7" t="s">
         <v>21</v>
@@ -2602,19 +2635,19 @@
     </row>
     <row r="8" spans="1:35">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -2647,19 +2680,19 @@
         <v>21</v>
       </c>
       <c r="P8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S8" t="s">
         <v>21</v>
       </c>
       <c r="T8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U8" t="s">
         <v>21</v>
@@ -2668,7 +2701,7 @@
         <v>21</v>
       </c>
       <c r="W8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X8" t="s">
         <v>21</v>
@@ -2686,10 +2719,10 @@
         <v>21</v>
       </c>
       <c r="AC8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AD8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
         <v>21</v>
@@ -2709,22 +2742,22 @@
     </row>
     <row r="9" spans="1:35">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" t="s">
         <v>21</v>
@@ -2754,10 +2787,10 @@
         <v>21</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R9" t="s">
         <v>21</v>
@@ -2790,10 +2823,10 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AC9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AD9" t="s">
         <v>21</v>
@@ -2816,19 +2849,19 @@
     </row>
     <row r="10" spans="1:35">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -2923,19 +2956,19 @@
     </row>
     <row r="11" spans="1:35">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -3030,16 +3063,16 @@
     </row>
     <row r="12" spans="1:35">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -3075,7 +3108,7 @@
         <v>21</v>
       </c>
       <c r="P12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q12" t="s">
         <v>21</v>
@@ -3137,16 +3170,16 @@
     </row>
     <row r="13" spans="1:35">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
@@ -3244,16 +3277,16 @@
     </row>
     <row r="14" spans="1:35">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -3322,7 +3355,7 @@
         <v>21</v>
       </c>
       <c r="AA14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AB14" t="s">
         <v>21</v>
@@ -3351,19 +3384,19 @@
     </row>
     <row r="15" spans="1:35">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -3458,16 +3491,16 @@
     </row>
     <row r="16" spans="1:35">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -3503,22 +3536,22 @@
         <v>21</v>
       </c>
       <c r="P16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="U16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="V16" t="s">
         <v>21</v>
@@ -3565,19 +3598,19 @@
     </row>
     <row r="17" spans="1:35">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -3610,19 +3643,19 @@
         <v>21</v>
       </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U17" t="s">
         <v>21</v>
@@ -3672,16 +3705,16 @@
     </row>
     <row r="18" spans="1:35">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
@@ -3717,7 +3750,7 @@
         <v>21</v>
       </c>
       <c r="P18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q18" t="s">
         <v>21</v>
@@ -3779,19 +3812,19 @@
     </row>
     <row r="19" spans="1:35">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -3860,7 +3893,7 @@
         <v>21</v>
       </c>
       <c r="AB19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AC19" t="s">
         <v>21</v>
@@ -3886,19 +3919,19 @@
     </row>
     <row r="20" spans="1:35">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -3993,19 +4026,19 @@
     </row>
     <row r="21" spans="1:35">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -4038,16 +4071,16 @@
         <v>21</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="T21" t="s">
         <v>21</v>
@@ -4100,31 +4133,31 @@
     </row>
     <row r="22" spans="1:35">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H22" t="s">
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J22" t="s">
         <v>21</v>
@@ -4145,7 +4178,7 @@
         <v>21</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q22" t="s">
         <v>21</v>
@@ -4166,7 +4199,7 @@
         <v>21</v>
       </c>
       <c r="W22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X22" t="s">
         <v>21</v>
@@ -4181,7 +4214,7 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AC22" t="s">
         <v>21</v>
@@ -4207,19 +4240,19 @@
     </row>
     <row r="23" spans="1:35">
       <c r="A23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -4252,10 +4285,10 @@
         <v>21</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R23" t="s">
         <v>21</v>
@@ -4314,22 +4347,22 @@
     </row>
     <row r="24" spans="1:35">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G24" t="s">
         <v>21</v>
@@ -4359,23 +4392,23 @@
         <v>21</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q24" t="s">
         <v>21</v>
       </c>
       <c r="R24" t="s">
+        <v>186</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s">
+        <v>187</v>
+      </c>
+      <c r="U24" t="s">
         <v>185</v>
       </c>
-      <c r="S24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T24" t="s">
-        <v>186</v>
-      </c>
-      <c r="U24" t="s">
-        <v>184</v>
-      </c>
       <c r="V24" t="s">
         <v>21</v>
       </c>
@@ -4398,10 +4431,10 @@
         <v>21</v>
       </c>
       <c r="AC24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AD24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AE24" t="s">
         <v>21</v>
@@ -4421,16 +4454,16 @@
     </row>
     <row r="25" spans="1:35">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
         <v>21</v>
@@ -4469,10 +4502,10 @@
         <v>21</v>
       </c>
       <c r="Q25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S25" t="s">
         <v>21</v>
@@ -4528,22 +4561,22 @@
     </row>
     <row r="26" spans="1:35">
       <c r="A26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G26" t="s">
         <v>21</v>
@@ -4573,13 +4606,13 @@
         <v>21</v>
       </c>
       <c r="P26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q26" t="s">
         <v>21</v>
       </c>
       <c r="R26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="S26" t="s">
         <v>21</v>
@@ -4635,16 +4668,16 @@
     </row>
     <row r="27" spans="1:35">
       <c r="A27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E27" t="s">
         <v>21</v>
@@ -4659,7 +4692,7 @@
         <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="J27" t="s">
         <v>21</v>
@@ -4742,16 +4775,16 @@
     </row>
     <row r="28" spans="1:35">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
@@ -4849,16 +4882,16 @@
     </row>
     <row r="29" spans="1:35">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E29" t="s">
         <v>21</v>
@@ -4894,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q29" t="s">
         <v>21</v>
@@ -4903,7 +4936,7 @@
         <v>21</v>
       </c>
       <c r="S29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="T29" t="s">
         <v>21</v>
@@ -4956,19 +4989,19 @@
     </row>
     <row r="30" spans="1:35">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -5063,16 +5096,16 @@
     </row>
     <row r="31" spans="1:35">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E31" t="s">
         <v>21</v>
@@ -5170,16 +5203,16 @@
     </row>
     <row r="32" spans="1:35">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E32" t="s">
         <v>21</v>
@@ -5277,16 +5310,16 @@
     </row>
     <row r="33" spans="1:35">
       <c r="A33" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
@@ -5384,16 +5417,16 @@
     </row>
     <row r="34" spans="1:35">
       <c r="A34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E34" t="s">
         <v>21</v>
@@ -5491,19 +5524,19 @@
     </row>
     <row r="35" spans="1:35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E35" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -5539,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="Q35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R35" t="s">
         <v>21</v>
@@ -5598,16 +5631,16 @@
     </row>
     <row r="36" spans="1:35">
       <c r="A36" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E36" t="s">
         <v>21</v>
@@ -5705,19 +5738,19 @@
     </row>
     <row r="37" spans="1:35">
       <c r="A37" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E37" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -5812,22 +5845,22 @@
     </row>
     <row r="38" spans="1:35">
       <c r="A38" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G38" t="s">
         <v>21</v>
@@ -5842,7 +5875,7 @@
         <v>21</v>
       </c>
       <c r="K38" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L38" t="s">
         <v>21</v>
@@ -5860,10 +5893,10 @@
         <v>21</v>
       </c>
       <c r="Q38" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="R38" t="s">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="S38" t="s">
         <v>21</v>
@@ -5890,16 +5923,16 @@
         <v>21</v>
       </c>
       <c r="AA38" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AB38" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AC38" t="s">
         <v>21</v>
       </c>
       <c r="AD38" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AE38" t="s">
         <v>21</v>
@@ -5919,16 +5952,16 @@
     </row>
     <row r="39" spans="1:35">
       <c r="A39" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
@@ -6026,16 +6059,16 @@
     </row>
     <row r="40" spans="1:35">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E40" t="s">
         <v>21</v>
@@ -6133,16 +6166,16 @@
     </row>
     <row r="41" spans="1:35">
       <c r="A41" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B41" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E41" t="s">
         <v>21</v>
@@ -6240,16 +6273,16 @@
     </row>
     <row r="42" spans="1:35">
       <c r="A42" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
@@ -6291,7 +6324,7 @@
         <v>21</v>
       </c>
       <c r="R42" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="S42" t="s">
         <v>21</v>
@@ -6347,22 +6380,22 @@
     </row>
     <row r="43" spans="1:35">
       <c r="A43" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E43" t="s">
         <v>21</v>
       </c>
       <c r="F43" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G43" t="s">
         <v>21</v>
@@ -6454,16 +6487,16 @@
     </row>
     <row r="44" spans="1:35">
       <c r="A44" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B44" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
@@ -6561,16 +6594,16 @@
     </row>
     <row r="45" spans="1:35">
       <c r="A45" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B45" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
@@ -6668,16 +6701,16 @@
     </row>
     <row r="46" spans="1:35">
       <c r="A46" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
@@ -6775,16 +6808,16 @@
     </row>
     <row r="47" spans="1:35">
       <c r="A47" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B47" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E47" t="s">
         <v>21</v>
@@ -6882,19 +6915,19 @@
     </row>
     <row r="48" spans="1:35">
       <c r="A48" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B48" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C48" t="s">
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E48" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -6989,16 +7022,16 @@
     </row>
     <row r="49" spans="1:35">
       <c r="A49" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B49" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E49" t="s">
         <v>21</v>
@@ -7096,16 +7129,16 @@
     </row>
     <row r="50" spans="1:35">
       <c r="A50" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B50" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E50" t="s">
         <v>21</v>
@@ -7203,16 +7236,16 @@
     </row>
     <row r="51" spans="1:35">
       <c r="A51" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B51" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E51" t="s">
         <v>21</v>
@@ -7248,13 +7281,13 @@
         <v>21</v>
       </c>
       <c r="P51" t="s">
-        <v>162</v>
+        <v>293</v>
       </c>
       <c r="Q51" t="s">
         <v>21</v>
       </c>
       <c r="R51" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="S51" t="s">
         <v>21</v>
@@ -7310,16 +7343,16 @@
     </row>
     <row r="52" spans="1:35">
       <c r="A52" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B52" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E52" t="s">
         <v>21</v>
@@ -7361,10 +7394,10 @@
         <v>21</v>
       </c>
       <c r="R52" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="S52" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="T52" t="s">
         <v>21</v>
@@ -7417,16 +7450,16 @@
     </row>
     <row r="53" spans="1:35">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B53" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E53" t="s">
         <v>21</v>
@@ -7462,7 +7495,7 @@
         <v>21</v>
       </c>
       <c r="P53" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q53" t="s">
         <v>21</v>
@@ -7524,16 +7557,16 @@
     </row>
     <row r="54" spans="1:35">
       <c r="A54" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B54" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E54" t="s">
         <v>21</v>
@@ -7631,16 +7664,16 @@
     </row>
     <row r="55" spans="1:35">
       <c r="A55" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B55" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E55" t="s">
         <v>21</v>
@@ -7738,16 +7771,16 @@
     </row>
     <row r="56" spans="1:35">
       <c r="A56" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B56" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E56" t="s">
         <v>21</v>
@@ -7845,22 +7878,22 @@
     </row>
     <row r="57" spans="1:35">
       <c r="A57" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B57" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E57" t="s">
         <v>21</v>
       </c>
       <c r="F57" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G57" t="s">
         <v>21</v>
@@ -7952,16 +7985,16 @@
     </row>
     <row r="58" spans="1:35">
       <c r="A58" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B58" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E58" t="s">
         <v>21</v>
@@ -8059,16 +8092,16 @@
     </row>
     <row r="59" spans="1:35">
       <c r="A59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B59" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C59" t="s">
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E59" t="s">
         <v>21</v>
@@ -8143,7 +8176,7 @@
         <v>21</v>
       </c>
       <c r="AC59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AD59" t="s">
         <v>21</v>
@@ -8166,16 +8199,16 @@
     </row>
     <row r="60" spans="1:35">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E60" t="s">
         <v>21</v>
@@ -8273,16 +8306,16 @@
     </row>
     <row r="61" spans="1:35">
       <c r="A61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E61" t="s">
         <v>21</v>
@@ -8330,7 +8363,7 @@
         <v>21</v>
       </c>
       <c r="T61" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="U61" t="s">
         <v>21</v>
@@ -8380,16 +8413,16 @@
     </row>
     <row r="62" spans="1:35">
       <c r="A62" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E62" t="s">
         <v>21</v>
@@ -8487,16 +8520,16 @@
     </row>
     <row r="63" spans="1:35">
       <c r="A63" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B63" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E63" t="s">
         <v>21</v>
@@ -8594,16 +8627,16 @@
     </row>
     <row r="64" spans="1:35">
       <c r="A64" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B64" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E64" t="s">
         <v>21</v>
@@ -8701,16 +8734,16 @@
     </row>
     <row r="65" spans="1:35">
       <c r="A65" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B65" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E65" t="s">
         <v>21</v>
@@ -8808,16 +8841,16 @@
     </row>
     <row r="66" spans="1:35">
       <c r="A66" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B66" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C66" t="s">
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E66" t="s">
         <v>21</v>
@@ -8886,7 +8919,7 @@
         <v>21</v>
       </c>
       <c r="AA66" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AB66" t="s">
         <v>21</v>
@@ -8915,16 +8948,16 @@
     </row>
     <row r="67" spans="1:35">
       <c r="A67" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B67" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E67" t="s">
         <v>21</v>
@@ -9022,19 +9055,19 @@
     </row>
     <row r="68" spans="1:35">
       <c r="A68" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B68" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C68" t="s">
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E68" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F68" t="s">
         <v>21</v>
@@ -9129,19 +9162,19 @@
     </row>
     <row r="69" spans="1:35">
       <c r="A69" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B69" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E69" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -9236,19 +9269,19 @@
     </row>
     <row r="70" spans="1:35">
       <c r="A70" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B70" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E70" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F70" t="s">
         <v>21</v>
@@ -9281,7 +9314,7 @@
         <v>21</v>
       </c>
       <c r="P70" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q70" t="s">
         <v>21</v>
@@ -9296,7 +9329,7 @@
         <v>21</v>
       </c>
       <c r="U70" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="V70" t="s">
         <v>21</v>
@@ -9343,16 +9376,16 @@
     </row>
     <row r="71" spans="1:35">
       <c r="A71" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B71" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E71" t="s">
         <v>21</v>
@@ -9450,16 +9483,16 @@
     </row>
     <row r="72" spans="1:35">
       <c r="A72" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B72" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E72" t="s">
         <v>21</v>
@@ -9557,16 +9590,16 @@
     </row>
     <row r="73" spans="1:35">
       <c r="A73" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E73" t="s">
         <v>21</v>
@@ -9664,16 +9697,16 @@
     </row>
     <row r="74" spans="1:35">
       <c r="A74" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B74" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E74" t="s">
         <v>21</v>
@@ -9715,13 +9748,13 @@
         <v>21</v>
       </c>
       <c r="R74" t="s">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="S74" t="s">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="T74" t="s">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="U74" t="s">
         <v>21</v>
@@ -9771,16 +9804,16 @@
     </row>
     <row r="75" spans="1:35">
       <c r="A75" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B75" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="E75" t="s">
         <v>21</v>
@@ -9822,13 +9855,13 @@
         <v>21</v>
       </c>
       <c r="R75" t="s">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="S75" t="s">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="T75" t="s">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="U75" t="s">
         <v>21</v>
@@ -9878,22 +9911,22 @@
     </row>
     <row r="76" spans="1:35">
       <c r="A76" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B76" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E76" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F76" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="G76" t="s">
         <v>21</v>
@@ -9985,16 +10018,16 @@
     </row>
     <row r="77" spans="1:35">
       <c r="A77" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B77" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E77" t="s">
         <v>21</v>
@@ -10092,16 +10125,16 @@
     </row>
     <row r="78" spans="1:35">
       <c r="A78" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B78" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E78" t="s">
         <v>21</v>
@@ -10140,7 +10173,7 @@
         <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="R78" t="s">
         <v>21</v>
@@ -10199,19 +10232,19 @@
     </row>
     <row r="79" spans="1:35">
       <c r="A79" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B79" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E79" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F79" t="s">
         <v>21</v>
@@ -10306,16 +10339,16 @@
     </row>
     <row r="80" spans="1:35">
       <c r="A80" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B80" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E80" t="s">
         <v>21</v>
@@ -10413,16 +10446,16 @@
     </row>
     <row r="81" spans="1:35">
       <c r="A81" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B81" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E81" t="s">
         <v>21</v>
@@ -10520,16 +10553,16 @@
     </row>
     <row r="82" spans="1:35">
       <c r="A82" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B82" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E82" t="s">
         <v>21</v>
@@ -10627,16 +10660,16 @@
     </row>
     <row r="83" spans="1:35">
       <c r="A83" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B83" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E83" t="s">
         <v>21</v>
@@ -10734,19 +10767,19 @@
     </row>
     <row r="84" spans="1:35">
       <c r="A84" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B84" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E84" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F84" t="s">
         <v>21</v>
@@ -10841,19 +10874,19 @@
     </row>
     <row r="85" spans="1:35">
       <c r="A85" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B85" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E85" t="s">
-        <v>197</v>
+        <v>417</v>
       </c>
       <c r="F85" t="s">
         <v>21</v>
@@ -10948,16 +10981,16 @@
     </row>
     <row r="86" spans="1:35">
       <c r="A86" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B86" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E86" t="s">
         <v>21</v>
@@ -11055,16 +11088,16 @@
     </row>
     <row r="87" spans="1:35">
       <c r="A87" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B87" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E87" t="s">
         <v>21</v>
@@ -11162,16 +11195,16 @@
     </row>
     <row r="88" spans="1:35">
       <c r="A88" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B88" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E88" t="s">
         <v>21</v>
@@ -11228,7 +11261,7 @@
         <v>21</v>
       </c>
       <c r="W88" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="X88" t="s">
         <v>21</v>
@@ -11240,16 +11273,16 @@
         <v>21</v>
       </c>
       <c r="AA88" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AB88" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AC88" t="s">
-        <v>151</v>
+        <v>428</v>
       </c>
       <c r="AD88" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AE88" t="s">
         <v>21</v>
@@ -11269,16 +11302,16 @@
     </row>
     <row r="89" spans="1:35">
       <c r="A89" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E89" t="s">
         <v>21</v>
@@ -11376,16 +11409,16 @@
     </row>
     <row r="90" spans="1:35">
       <c r="A90" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B90" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="E90" t="s">
         <v>21</v>
@@ -11483,16 +11516,16 @@
     </row>
     <row r="91" spans="1:35">
       <c r="A91" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B91" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E91" t="s">
         <v>21</v>
@@ -11590,16 +11623,16 @@
     </row>
     <row r="92" spans="1:35">
       <c r="A92" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B92" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E92" t="s">
         <v>21</v>
@@ -11697,16 +11730,16 @@
     </row>
     <row r="93" spans="1:35">
       <c r="A93" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B93" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>247</v>
+        <v>444</v>
       </c>
       <c r="E93" t="s">
         <v>21</v>
@@ -11804,16 +11837,16 @@
     </row>
     <row r="94" spans="1:35">
       <c r="A94" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B94" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="E94" t="s">
         <v>21</v>
@@ -11911,16 +11944,16 @@
     </row>
     <row r="95" spans="1:35">
       <c r="A95" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B95" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E95" t="s">
         <v>21</v>
@@ -12018,10 +12051,10 @@
     </row>
     <row r="96" spans="1:35">
       <c r="A96" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B96" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
@@ -12030,7 +12063,7 @@
         <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="F96" t="s">
         <v>21</v>
@@ -12125,10 +12158,10 @@
     </row>
     <row r="97" spans="1:35">
       <c r="A97" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B97" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -12137,7 +12170,7 @@
         <v>21</v>
       </c>
       <c r="E97" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
@@ -12232,10 +12265,10 @@
     </row>
     <row r="98" spans="1:35">
       <c r="A98" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B98" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
@@ -12244,7 +12277,7 @@
         <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="F98" t="s">
         <v>21</v>
@@ -12283,7 +12316,7 @@
         <v>21</v>
       </c>
       <c r="R98" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="S98" t="s">
         <v>21</v>
@@ -12339,10 +12372,10 @@
     </row>
     <row r="99" spans="1:35">
       <c r="A99" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B99" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
@@ -12351,7 +12384,7 @@
         <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F99" t="s">
         <v>21</v>
@@ -12446,10 +12479,10 @@
     </row>
     <row r="100" spans="1:35">
       <c r="A100" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B100" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C100" t="s">
         <v>17</v>
@@ -12458,10 +12491,10 @@
         <v>21</v>
       </c>
       <c r="E100" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F100" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="G100" t="s">
         <v>21</v>
@@ -12497,7 +12530,7 @@
         <v>21</v>
       </c>
       <c r="R100" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="S100" t="s">
         <v>21</v>
@@ -12553,10 +12586,10 @@
     </row>
     <row r="101" spans="1:35">
       <c r="A101" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B101" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
@@ -12565,7 +12598,7 @@
         <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="F101" t="s">
         <v>21</v>
@@ -12660,10 +12693,10 @@
     </row>
     <row r="102" spans="1:35">
       <c r="A102" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B102" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
@@ -12672,7 +12705,7 @@
         <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F102" t="s">
         <v>21</v>
@@ -12767,10 +12800,10 @@
     </row>
     <row r="103" spans="1:35">
       <c r="A103" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B103" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C103" t="s">
         <v>17</v>
@@ -12779,7 +12812,7 @@
         <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F103" t="s">
         <v>21</v>
@@ -12874,10 +12907,10 @@
     </row>
     <row r="104" spans="1:35">
       <c r="A104" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B104" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C104" t="s">
         <v>17</v>
@@ -12886,7 +12919,7 @@
         <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="F104" t="s">
         <v>21</v>
@@ -12981,10 +13014,10 @@
     </row>
     <row r="105" spans="1:35">
       <c r="A105" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B105" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C105" t="s">
         <v>17</v>
@@ -12993,7 +13026,7 @@
         <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="F105" t="s">
         <v>21</v>
@@ -13088,10 +13121,10 @@
     </row>
     <row r="106" spans="1:35">
       <c r="A106" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B106" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C106" t="s">
         <v>17</v>
@@ -13100,7 +13133,7 @@
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="F106" t="s">
         <v>21</v>
@@ -13195,10 +13228,10 @@
     </row>
     <row r="107" spans="1:35">
       <c r="A107" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B107" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="C107" t="s">
         <v>17</v>
@@ -13207,7 +13240,7 @@
         <v>21</v>
       </c>
       <c r="E107" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="F107" t="s">
         <v>21</v>
@@ -13302,10 +13335,10 @@
     </row>
     <row r="108" spans="1:35">
       <c r="A108" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B108" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C108" t="s">
         <v>17</v>
@@ -13314,7 +13347,7 @@
         <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F108" t="s">
         <v>21</v>
@@ -13409,10 +13442,10 @@
     </row>
     <row r="109" spans="1:35">
       <c r="A109" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B109" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="C109" t="s">
         <v>17</v>
@@ -13421,7 +13454,7 @@
         <v>21</v>
       </c>
       <c r="E109" t="s">
-        <v>439</v>
+        <v>492</v>
       </c>
       <c r="F109" t="s">
         <v>21</v>
@@ -13516,10 +13549,10 @@
     </row>
     <row r="110" spans="1:35">
       <c r="A110" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B110" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
@@ -13528,7 +13561,7 @@
         <v>21</v>
       </c>
       <c r="E110" t="s">
-        <v>151</v>
+        <v>495</v>
       </c>
       <c r="F110" t="s">
         <v>21</v>
@@ -13623,10 +13656,10 @@
     </row>
     <row r="111" spans="1:35">
       <c r="A111" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B111" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C111" t="s">
         <v>17</v>
@@ -13635,7 +13668,7 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>151</v>
+        <v>428</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
@@ -13730,10 +13763,10 @@
     </row>
     <row r="112" spans="1:35">
       <c r="A112" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B112" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C112" t="s">
         <v>17</v>
@@ -13742,7 +13775,7 @@
         <v>21</v>
       </c>
       <c r="E112" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -13837,10 +13870,10 @@
     </row>
     <row r="113" spans="1:35">
       <c r="A113" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B113" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C113" t="s">
         <v>17</v>
@@ -13852,7 +13885,7 @@
         <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G113" t="s">
         <v>21</v>
@@ -13944,10 +13977,10 @@
     </row>
     <row r="114" spans="1:35">
       <c r="A114" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B114" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="C114" t="s">
         <v>17</v>
@@ -14004,7 +14037,7 @@
         <v>21</v>
       </c>
       <c r="U114" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="V114" t="s">
         <v>21</v>
@@ -14051,10 +14084,10 @@
     </row>
     <row r="115" spans="1:35">
       <c r="A115" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C115" t="s">
         <v>17</v>
@@ -14081,7 +14114,7 @@
         <v>21</v>
       </c>
       <c r="K115" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>

--- a/upload/ar_aging_report_converted.xlsx
+++ b/upload/ar_aging_report_converted.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="508">
   <si>
     <t>Customer Header Number</t>
   </si>
@@ -332,10 +332,10 @@
     <t>LASER IMPORT S.A.</t>
   </si>
   <si>
-    <t>10,252.02</t>
-  </si>
-  <si>
-    <t>171.67</t>
+    <t>10,292.65</t>
+  </si>
+  <si>
+    <t>172.35</t>
   </si>
   <si>
     <t>UY000855005H</t>
@@ -344,10 +344,10 @@
     <t>ESTAWOL S.A.</t>
   </si>
   <si>
-    <t>7,997.07</t>
-  </si>
-  <si>
-    <t>80.88</t>
+    <t>8,028.76</t>
+  </si>
+  <si>
+    <t>81.20</t>
   </si>
   <si>
     <t>PE008204001H</t>
@@ -368,7 +368,7 @@
     <t>Karry S.A.</t>
   </si>
   <si>
-    <t>6,616.12</t>
+    <t>6,642.34</t>
   </si>
   <si>
     <t>BO000681002H</t>
@@ -377,7 +377,7 @@
     <t>Dismatec S.A.</t>
   </si>
   <si>
-    <t>4,834.32</t>
+    <t>4,853.48</t>
   </si>
   <si>
     <t>0.36</t>
@@ -389,10 +389,10 @@
     <t>Import Export Salvatierra S.A.</t>
   </si>
   <si>
-    <t>4,554.36</t>
-  </si>
-  <si>
-    <t>20.92</t>
+    <t>4,572.41</t>
+  </si>
+  <si>
+    <t>21.00</t>
   </si>
   <si>
     <t>PE000952001H</t>
@@ -404,7 +404,7 @@
     <t>4,022.58</t>
   </si>
   <si>
-    <t>-6.84</t>
+    <t>-6.86</t>
   </si>
   <si>
     <t>-8.28</t>
@@ -482,10 +482,10 @@
     <t>COMERCIAL REFRIGERACION PERU S</t>
   </si>
   <si>
-    <t>2,079.19</t>
-  </si>
-  <si>
-    <t>279.00</t>
+    <t>2,087.43</t>
+  </si>
+  <si>
+    <t>280.11</t>
   </si>
   <si>
     <t>PE000984001H</t>
@@ -494,22 +494,22 @@
     <t>INGRAM MICRO S.A.C.</t>
   </si>
   <si>
-    <t>2,032.05</t>
-  </si>
-  <si>
-    <t>9.25</t>
-  </si>
-  <si>
-    <t>-78.95</t>
-  </si>
-  <si>
-    <t>-2.19</t>
-  </si>
-  <si>
-    <t>-0.51</t>
-  </si>
-  <si>
-    <t>-1.56</t>
+    <t>2,040.10</t>
+  </si>
+  <si>
+    <t>9.28</t>
+  </si>
+  <si>
+    <t>-79.26</t>
+  </si>
+  <si>
+    <t>-2.20</t>
+  </si>
+  <si>
+    <t>-0.52</t>
+  </si>
+  <si>
+    <t>-1.57</t>
   </si>
   <si>
     <t>PE008158001H</t>
@@ -545,16 +545,16 @@
     <t>PC LINK SOCIEDAD ANONIMA CERRA</t>
   </si>
   <si>
-    <t>1,701.26</t>
-  </si>
-  <si>
-    <t>116.36</t>
-  </si>
-  <si>
-    <t>-119.55</t>
-  </si>
-  <si>
-    <t>-2.68</t>
+    <t>1,708.00</t>
+  </si>
+  <si>
+    <t>116.82</t>
+  </si>
+  <si>
+    <t>-120.02</t>
+  </si>
+  <si>
+    <t>-2.69</t>
   </si>
   <si>
     <t>PE006374001H</t>
@@ -593,13 +593,13 @@
     <t>COMPUDISKETT SRL</t>
   </si>
   <si>
-    <t>1,527.89</t>
+    <t>1,533.95</t>
   </si>
   <si>
     <t>-0.40</t>
   </si>
   <si>
-    <t>-4.47</t>
+    <t>-4.48</t>
   </si>
   <si>
     <t>PE002897001H</t>
@@ -608,19 +608,19 @@
     <t>GRUPO DELTRON S.A.</t>
   </si>
   <si>
-    <t>1,209.12</t>
+    <t>1,213.91</t>
   </si>
   <si>
     <t>0.69</t>
   </si>
   <si>
-    <t>68.07</t>
+    <t>68.34</t>
   </si>
   <si>
     <t>-0.34</t>
   </si>
   <si>
-    <t>-74.10</t>
+    <t>-74.40</t>
   </si>
   <si>
     <t>UY000615003H</t>
@@ -629,7 +629,7 @@
     <t>OCEANLUX, S.A.</t>
   </si>
   <si>
-    <t>1,175.10</t>
+    <t>1,179.76</t>
   </si>
   <si>
     <t>0.39</t>
@@ -650,7 +650,7 @@
     <t>UEZU COMERCIAL SAC</t>
   </si>
   <si>
-    <t>1,005.02</t>
+    <t>1,008.98</t>
   </si>
   <si>
     <t>-0.55</t>
@@ -662,10 +662,10 @@
     <t>COLDSMART PERU S.A.C.</t>
   </si>
   <si>
-    <t>873.62</t>
-  </si>
-  <si>
-    <t>121.53</t>
+    <t>877.09</t>
+  </si>
+  <si>
+    <t>122.01</t>
   </si>
   <si>
     <t>PE007687001H</t>
@@ -674,7 +674,7 @@
     <t>COMERCIAL FRIONORTE E.I.R.L.</t>
   </si>
   <si>
-    <t>681.35</t>
+    <t>684.05</t>
   </si>
   <si>
     <t>PE008420001H</t>
@@ -683,7 +683,7 @@
     <t>AIR COOL SYSTEM SM S.A.C.</t>
   </si>
   <si>
-    <t>674.85</t>
+    <t>677.53</t>
   </si>
   <si>
     <t>PE004417001H</t>
@@ -692,7 +692,7 @@
     <t>REPRESENTACIONES MONTERO S.R.L</t>
   </si>
   <si>
-    <t>666.65</t>
+    <t>669.29</t>
   </si>
   <si>
     <t>UY000854004H</t>
@@ -701,7 +701,7 @@
     <t>Solution Box Uruguay</t>
   </si>
   <si>
-    <t>651.10</t>
+    <t>653.68</t>
   </si>
   <si>
     <t>PE000717001H</t>
@@ -722,7 +722,7 @@
     <t>SONEPAR PERU S.A.C.</t>
   </si>
   <si>
-    <t>487.07</t>
+    <t>489.00</t>
   </si>
   <si>
     <t>PE008453001H</t>
@@ -731,10 +731,10 @@
     <t>MAXIMA INTERNACIONAL S.A.</t>
   </si>
   <si>
-    <t>486.37</t>
-  </si>
-  <si>
-    <t>106.39</t>
+    <t>488.30</t>
+  </si>
+  <si>
+    <t>106.81</t>
   </si>
   <si>
     <t>PE008292001H</t>
@@ -776,7 +776,7 @@
     <t>DACER SOCIEDAD ANONIMA CERRADA</t>
   </si>
   <si>
-    <t>378.32</t>
+    <t>379.82</t>
   </si>
   <si>
     <t>PE001507001H</t>
@@ -785,7 +785,7 @@
     <t>IREDI INTERNATIONAL S.R.L</t>
   </si>
   <si>
-    <t>375.56</t>
+    <t>377.04</t>
   </si>
   <si>
     <t>PA000001010H</t>
@@ -794,7 +794,7 @@
     <t>LG ELECTRONICS PANAMA S.A.</t>
   </si>
   <si>
-    <t>346.14</t>
+    <t>347.51</t>
   </si>
   <si>
     <t>PE003288001H</t>
@@ -815,7 +815,7 @@
     <t>SERFAC S.A.C.</t>
   </si>
   <si>
-    <t>290.56</t>
+    <t>291.71</t>
   </si>
   <si>
     <t>0.84</t>
@@ -827,7 +827,7 @@
     <t>SUCESION JUAN PINTO RUIZ</t>
   </si>
   <si>
-    <t>278.21</t>
+    <t>279.31</t>
   </si>
   <si>
     <t>PE000853001H</t>
@@ -845,7 +845,7 @@
     <t>INGENIEROS FRIOTEMP S.A.C.</t>
   </si>
   <si>
-    <t>246.88</t>
+    <t>247.86</t>
   </si>
   <si>
     <t>PE008441001H</t>
@@ -854,7 +854,7 @@
     <t>RICOH DEL PERU S.A.C.</t>
   </si>
   <si>
-    <t>231.94</t>
+    <t>232.86</t>
   </si>
   <si>
     <t>PE007714001H</t>
@@ -863,10 +863,10 @@
     <t>COINREFRI AIR S.A.C.</t>
   </si>
   <si>
-    <t>215.26</t>
-  </si>
-  <si>
-    <t>47.93</t>
+    <t>216.11</t>
+  </si>
+  <si>
+    <t>48.12</t>
   </si>
   <si>
     <t>UY000858004H</t>
@@ -875,7 +875,7 @@
     <t>JOACAMAR</t>
   </si>
   <si>
-    <t>192.66</t>
+    <t>193.42</t>
   </si>
   <si>
     <t>PY001162002H</t>
@@ -884,7 +884,7 @@
     <t>CENTRONIC S.A.</t>
   </si>
   <si>
-    <t>189.02</t>
+    <t>189.77</t>
   </si>
   <si>
     <t>PE008312001H</t>
@@ -896,9 +896,6 @@
     <t>171.96</t>
   </si>
   <si>
-    <t>-0.52</t>
-  </si>
-  <si>
     <t>-2.95</t>
   </si>
   <si>
@@ -908,13 +905,13 @@
     <t>NEXSYS DEL PERU S.A.C.</t>
   </si>
   <si>
-    <t>170.08</t>
-  </si>
-  <si>
-    <t>-34.65</t>
-  </si>
-  <si>
-    <t>-26.84</t>
+    <t>170.75</t>
+  </si>
+  <si>
+    <t>-34.79</t>
+  </si>
+  <si>
+    <t>-26.95</t>
   </si>
   <si>
     <t>PE008017001H</t>
@@ -935,7 +932,7 @@
     <t>PROTERM PERU S..AC.</t>
   </si>
   <si>
-    <t>143.42</t>
+    <t>143.98</t>
   </si>
   <si>
     <t>CO000002006H</t>
@@ -944,7 +941,7 @@
     <t>LG ELECTRONICS COLOMBIA LTDA</t>
   </si>
   <si>
-    <t>140.40</t>
+    <t>140.96</t>
   </si>
   <si>
     <t>PE008165001H</t>
@@ -953,7 +950,7 @@
     <t>TODOCLIMA PERU S.A.C.</t>
   </si>
   <si>
-    <t>123.28</t>
+    <t>123.77</t>
   </si>
   <si>
     <t>PE008064001H</t>
@@ -962,10 +959,10 @@
     <t>MEGA SHOP FRIO SOC. COM. RESPO</t>
   </si>
   <si>
-    <t>110.04</t>
-  </si>
-  <si>
-    <t>18.93</t>
+    <t>110.48</t>
+  </si>
+  <si>
+    <t>19.00</t>
   </si>
   <si>
     <t>PE008139001H</t>
@@ -974,7 +971,7 @@
     <t>GREENCORP PERU S.A.C.</t>
   </si>
   <si>
-    <t>97.12</t>
+    <t>97.50</t>
   </si>
   <si>
     <t>PE008020001H</t>
@@ -1010,6 +1007,15 @@
     <t>-1.53</t>
   </si>
   <si>
+    <t>PY001038002H</t>
+  </si>
+  <si>
+    <t>SERVIPHIL S.R.L</t>
+  </si>
+  <si>
+    <t>30.23</t>
+  </si>
+  <si>
     <t>PE001020001H</t>
   </si>
   <si>
@@ -1019,15 +1025,6 @@
     <t>30.12</t>
   </si>
   <si>
-    <t>PY001038002H</t>
-  </si>
-  <si>
-    <t>SERVIPHIL S.R.L</t>
-  </si>
-  <si>
-    <t>30.11</t>
-  </si>
-  <si>
     <t>PE008083001H</t>
   </si>
   <si>
@@ -1043,7 +1040,7 @@
     <t>ANIXTER PERU S.A.C.</t>
   </si>
   <si>
-    <t>26.04</t>
+    <t>26.14</t>
   </si>
   <si>
     <t>UY000836002H</t>
@@ -1052,10 +1049,10 @@
     <t>LAVOMAT</t>
   </si>
   <si>
-    <t>25.34</t>
-  </si>
-  <si>
-    <t>0.26</t>
+    <t>25.44</t>
+  </si>
+  <si>
+    <t>0.27</t>
   </si>
   <si>
     <t>PE006831001H</t>
@@ -1085,10 +1082,10 @@
     <t>Odalmar S.A.</t>
   </si>
   <si>
-    <t>20.59</t>
-  </si>
-  <si>
-    <t>12.92</t>
+    <t>20.67</t>
+  </si>
+  <si>
+    <t>12.97</t>
   </si>
   <si>
     <t>PE006934001H</t>
@@ -1124,7 +1121,7 @@
     <t>Censel</t>
   </si>
   <si>
-    <t>19.16</t>
+    <t>19.24</t>
   </si>
   <si>
     <t>PE008022001H</t>
@@ -1136,6 +1133,15 @@
     <t>17.46</t>
   </si>
   <si>
+    <t>PE008105001H</t>
+  </si>
+  <si>
+    <t>LATINAMENITIES S.A.C.</t>
+  </si>
+  <si>
+    <t>17.30</t>
+  </si>
+  <si>
     <t>PE004102001H</t>
   </si>
   <si>
@@ -1154,15 +1160,6 @@
     <t>-5.90</t>
   </si>
   <si>
-    <t>PE008105001H</t>
-  </si>
-  <si>
-    <t>LATINAMENITIES S.A.C.</t>
-  </si>
-  <si>
-    <t>17.23</t>
-  </si>
-  <si>
     <t>PE007296001H</t>
   </si>
   <si>
@@ -1235,7 +1232,7 @@
     <t>TGESTIONA SERVICIOS GLOBALES S</t>
   </si>
   <si>
-    <t>7.80</t>
+    <t>7.83</t>
   </si>
   <si>
     <t>PE004853001H</t>
@@ -1286,7 +1283,7 @@
     <t>TELECOMUNICACIONES STUDIO WEB</t>
   </si>
   <si>
-    <t>2.96</t>
+    <t>2.97</t>
   </si>
   <si>
     <t>PE007297001H</t>
@@ -1313,7 +1310,7 @@
     <t>ENVING S.A.</t>
   </si>
   <si>
-    <t>2.35</t>
+    <t>2.36</t>
   </si>
   <si>
     <t>PE008439001H</t>
@@ -1322,7 +1319,7 @@
     <t>SEAL TELECOM COMERCIO E SERVIC</t>
   </si>
   <si>
-    <t>2.32</t>
+    <t>2.33</t>
   </si>
   <si>
     <t>UY000851005H</t>
@@ -1331,7 +1328,7 @@
     <t>INGENIERO TUGENTMAN</t>
   </si>
   <si>
-    <t>1.12</t>
+    <t>1.13</t>
   </si>
   <si>
     <t>PE005274001H</t>
@@ -1373,7 +1370,7 @@
     <t>RIGSTAR S.A.</t>
   </si>
   <si>
-    <t>361.89</t>
+    <t>363.33</t>
   </si>
   <si>
     <t>PE000001006H</t>
@@ -1382,7 +1379,7 @@
     <t>LG ELECTRONICS PERU S.A.</t>
   </si>
   <si>
-    <t>312.50</t>
+    <t>313.74</t>
   </si>
   <si>
     <t>PE005206001H</t>
@@ -1424,7 +1421,7 @@
     <t>IMPORTACIONES MONTERO E.I.R.L.</t>
   </si>
   <si>
-    <t>31.00</t>
+    <t>31.12</t>
   </si>
   <si>
     <t>PE008423001H</t>
@@ -1433,7 +1430,7 @@
     <t>SUMINISTROS E INVERSIONES DEL</t>
   </si>
   <si>
-    <t>16.70</t>
+    <t>16.77</t>
   </si>
   <si>
     <t>PE000690001H</t>
@@ -1460,7 +1457,7 @@
     <t>COLD MACHINES S.A.C</t>
   </si>
   <si>
-    <t>1.70</t>
+    <t>1.71</t>
   </si>
   <si>
     <t>PE001009001H</t>
@@ -1502,7 +1499,7 @@
     <t>SOLUCIONES MULTITECNICAS S.A.C</t>
   </si>
   <si>
-    <t>0.20</t>
+    <t>0.21</t>
   </si>
   <si>
     <t>PE008117001H</t>
@@ -1541,7 +1538,7 @@
     <t>LGEAR</t>
   </si>
   <si>
-    <t>21.30</t>
+    <t>21.39</t>
   </si>
 </sst>
 </file>
@@ -7281,13 +7278,13 @@
         <v>21</v>
       </c>
       <c r="P51" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" t="s">
         <v>293</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>21</v>
-      </c>
-      <c r="R51" t="s">
-        <v>294</v>
       </c>
       <c r="S51" t="s">
         <v>21</v>
@@ -7343,61 +7340,61 @@
     </row>
     <row r="52" spans="1:35">
       <c r="A52" t="s">
+        <v>294</v>
+      </c>
+      <c r="B52" t="s">
         <v>295</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
         <v>296</v>
       </c>
-      <c r="C52" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" t="s">
         <v>297</v>
       </c>
-      <c r="E52" t="s">
-        <v>21</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52" t="s">
-        <v>21</v>
-      </c>
-      <c r="H52" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s">
-        <v>21</v>
-      </c>
-      <c r="K52" t="s">
-        <v>21</v>
-      </c>
-      <c r="L52" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" t="s">
-        <v>21</v>
-      </c>
-      <c r="N52" t="s">
-        <v>17</v>
-      </c>
-      <c r="O52" t="s">
-        <v>21</v>
-      </c>
-      <c r="P52" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>21</v>
-      </c>
-      <c r="R52" t="s">
+      <c r="S52" t="s">
         <v>298</v>
-      </c>
-      <c r="S52" t="s">
-        <v>299</v>
       </c>
       <c r="T52" t="s">
         <v>21</v>
@@ -7450,52 +7447,52 @@
     </row>
     <row r="53" spans="1:35">
       <c r="A53" t="s">
+        <v>299</v>
+      </c>
+      <c r="B53" t="s">
         <v>300</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
         <v>301</v>
       </c>
-      <c r="C53" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" t="s">
+        <v>17</v>
+      </c>
+      <c r="O53" t="s">
+        <v>21</v>
+      </c>
+      <c r="P53" t="s">
         <v>302</v>
-      </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s">
-        <v>21</v>
-      </c>
-      <c r="K53" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" t="s">
-        <v>21</v>
-      </c>
-      <c r="N53" t="s">
-        <v>17</v>
-      </c>
-      <c r="O53" t="s">
-        <v>21</v>
-      </c>
-      <c r="P53" t="s">
-        <v>303</v>
       </c>
       <c r="Q53" t="s">
         <v>21</v>
@@ -7557,16 +7554,16 @@
     </row>
     <row r="54" spans="1:35">
       <c r="A54" t="s">
+        <v>303</v>
+      </c>
+      <c r="B54" t="s">
         <v>304</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
         <v>305</v>
-      </c>
-      <c r="C54" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" t="s">
-        <v>306</v>
       </c>
       <c r="E54" t="s">
         <v>21</v>
@@ -7664,16 +7661,16 @@
     </row>
     <row r="55" spans="1:35">
       <c r="A55" t="s">
+        <v>306</v>
+      </c>
+      <c r="B55" t="s">
         <v>307</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
         <v>308</v>
-      </c>
-      <c r="C55" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" t="s">
-        <v>309</v>
       </c>
       <c r="E55" t="s">
         <v>21</v>
@@ -7771,16 +7768,16 @@
     </row>
     <row r="56" spans="1:35">
       <c r="A56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B56" t="s">
         <v>310</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
         <v>311</v>
-      </c>
-      <c r="C56" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" t="s">
-        <v>312</v>
       </c>
       <c r="E56" t="s">
         <v>21</v>
@@ -7878,22 +7875,22 @@
     </row>
     <row r="57" spans="1:35">
       <c r="A57" t="s">
+        <v>312</v>
+      </c>
+      <c r="B57" t="s">
         <v>313</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
         <v>314</v>
       </c>
-      <c r="C57" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
         <v>315</v>
-      </c>
-      <c r="E57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F57" t="s">
-        <v>316</v>
       </c>
       <c r="G57" t="s">
         <v>21</v>
@@ -7985,16 +7982,16 @@
     </row>
     <row r="58" spans="1:35">
       <c r="A58" t="s">
+        <v>316</v>
+      </c>
+      <c r="B58" t="s">
         <v>317</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
         <v>318</v>
-      </c>
-      <c r="C58" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" t="s">
-        <v>319</v>
       </c>
       <c r="E58" t="s">
         <v>21</v>
@@ -8092,91 +8089,91 @@
     </row>
     <row r="59" spans="1:35">
       <c r="A59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" t="s">
         <v>320</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
         <v>321</v>
       </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" t="s">
+        <v>17</v>
+      </c>
+      <c r="O59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>21</v>
+      </c>
+      <c r="R59" t="s">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s">
         <v>322</v>
-      </c>
-      <c r="E59" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59" t="s">
-        <v>21</v>
-      </c>
-      <c r="J59" t="s">
-        <v>21</v>
-      </c>
-      <c r="K59" t="s">
-        <v>21</v>
-      </c>
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" t="s">
-        <v>17</v>
-      </c>
-      <c r="O59" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>21</v>
-      </c>
-      <c r="R59" t="s">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>323</v>
       </c>
       <c r="AD59" t="s">
         <v>21</v>
@@ -8199,16 +8196,16 @@
     </row>
     <row r="60" spans="1:35">
       <c r="A60" t="s">
+        <v>323</v>
+      </c>
+      <c r="B60" t="s">
         <v>324</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" t="s">
         <v>325</v>
-      </c>
-      <c r="C60" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" t="s">
-        <v>326</v>
       </c>
       <c r="E60" t="s">
         <v>21</v>
@@ -8306,64 +8303,64 @@
     </row>
     <row r="61" spans="1:35">
       <c r="A61" t="s">
+        <v>326</v>
+      </c>
+      <c r="B61" t="s">
         <v>327</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
         <v>328</v>
       </c>
-      <c r="C61" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" t="s">
+        <v>21</v>
+      </c>
+      <c r="N61" t="s">
+        <v>17</v>
+      </c>
+      <c r="O61" t="s">
+        <v>21</v>
+      </c>
+      <c r="P61" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>21</v>
+      </c>
+      <c r="R61" t="s">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s">
         <v>329</v>
-      </c>
-      <c r="E61" t="s">
-        <v>21</v>
-      </c>
-      <c r="F61" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s">
-        <v>21</v>
-      </c>
-      <c r="K61" t="s">
-        <v>21</v>
-      </c>
-      <c r="L61" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" t="s">
-        <v>17</v>
-      </c>
-      <c r="O61" t="s">
-        <v>21</v>
-      </c>
-      <c r="P61" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>21</v>
-      </c>
-      <c r="R61" t="s">
-        <v>21</v>
-      </c>
-      <c r="S61" t="s">
-        <v>21</v>
-      </c>
-      <c r="T61" t="s">
-        <v>330</v>
       </c>
       <c r="U61" t="s">
         <v>21</v>
@@ -8413,16 +8410,16 @@
     </row>
     <row r="62" spans="1:35">
       <c r="A62" t="s">
+        <v>330</v>
+      </c>
+      <c r="B62" t="s">
         <v>331</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
         <v>332</v>
-      </c>
-      <c r="C62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" t="s">
-        <v>333</v>
       </c>
       <c r="E62" t="s">
         <v>21</v>
@@ -8520,16 +8517,16 @@
     </row>
     <row r="63" spans="1:35">
       <c r="A63" t="s">
+        <v>333</v>
+      </c>
+      <c r="B63" t="s">
         <v>334</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" t="s">
         <v>335</v>
-      </c>
-      <c r="C63" t="s">
-        <v>17</v>
-      </c>
-      <c r="D63" t="s">
-        <v>336</v>
       </c>
       <c r="E63" t="s">
         <v>21</v>
@@ -8627,16 +8624,16 @@
     </row>
     <row r="64" spans="1:35">
       <c r="A64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" t="s">
         <v>337</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
         <v>338</v>
-      </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" t="s">
-        <v>339</v>
       </c>
       <c r="E64" t="s">
         <v>21</v>
@@ -8734,16 +8731,16 @@
     </row>
     <row r="65" spans="1:35">
       <c r="A65" t="s">
+        <v>339</v>
+      </c>
+      <c r="B65" t="s">
         <v>340</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
         <v>341</v>
-      </c>
-      <c r="C65" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" t="s">
-        <v>342</v>
       </c>
       <c r="E65" t="s">
         <v>21</v>
@@ -8841,85 +8838,85 @@
     </row>
     <row r="66" spans="1:35">
       <c r="A66" t="s">
+        <v>342</v>
+      </c>
+      <c r="B66" t="s">
         <v>343</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
         <v>344</v>
       </c>
-      <c r="C66" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" t="s">
+        <v>17</v>
+      </c>
+      <c r="O66" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>21</v>
+      </c>
+      <c r="R66" t="s">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s">
         <v>345</v>
-      </c>
-      <c r="E66" t="s">
-        <v>21</v>
-      </c>
-      <c r="F66" t="s">
-        <v>21</v>
-      </c>
-      <c r="G66" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66" t="s">
-        <v>21</v>
-      </c>
-      <c r="J66" t="s">
-        <v>21</v>
-      </c>
-      <c r="K66" t="s">
-        <v>21</v>
-      </c>
-      <c r="L66" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" t="s">
-        <v>21</v>
-      </c>
-      <c r="N66" t="s">
-        <v>17</v>
-      </c>
-      <c r="O66" t="s">
-        <v>21</v>
-      </c>
-      <c r="P66" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>21</v>
-      </c>
-      <c r="R66" t="s">
-        <v>21</v>
-      </c>
-      <c r="S66" t="s">
-        <v>21</v>
-      </c>
-      <c r="T66" t="s">
-        <v>21</v>
-      </c>
-      <c r="U66" t="s">
-        <v>21</v>
-      </c>
-      <c r="V66" t="s">
-        <v>21</v>
-      </c>
-      <c r="W66" t="s">
-        <v>21</v>
-      </c>
-      <c r="X66" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>346</v>
       </c>
       <c r="AB66" t="s">
         <v>21</v>
@@ -8948,16 +8945,16 @@
     </row>
     <row r="67" spans="1:35">
       <c r="A67" t="s">
+        <v>346</v>
+      </c>
+      <c r="B67" t="s">
         <v>347</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
         <v>348</v>
-      </c>
-      <c r="C67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" t="s">
-        <v>349</v>
       </c>
       <c r="E67" t="s">
         <v>21</v>
@@ -9055,19 +9052,19 @@
     </row>
     <row r="68" spans="1:35">
       <c r="A68" t="s">
+        <v>349</v>
+      </c>
+      <c r="B68" t="s">
         <v>350</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
         <v>351</v>
       </c>
-      <c r="C68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>352</v>
-      </c>
-      <c r="E68" t="s">
-        <v>353</v>
       </c>
       <c r="F68" t="s">
         <v>21</v>
@@ -9162,19 +9159,19 @@
     </row>
     <row r="69" spans="1:35">
       <c r="A69" t="s">
+        <v>353</v>
+      </c>
+      <c r="B69" t="s">
         <v>354</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" t="s">
         <v>355</v>
       </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>356</v>
-      </c>
-      <c r="E69" t="s">
-        <v>357</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -9269,67 +9266,67 @@
     </row>
     <row r="70" spans="1:35">
       <c r="A70" t="s">
+        <v>357</v>
+      </c>
+      <c r="B70" t="s">
         <v>358</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
         <v>359</v>
       </c>
-      <c r="C70" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>360</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" t="s">
+        <v>17</v>
+      </c>
+      <c r="O70" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" t="s">
         <v>361</v>
       </c>
-      <c r="F70" t="s">
-        <v>21</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70" t="s">
-        <v>21</v>
-      </c>
-      <c r="J70" t="s">
-        <v>21</v>
-      </c>
-      <c r="K70" t="s">
-        <v>21</v>
-      </c>
-      <c r="L70" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" t="s">
-        <v>21</v>
-      </c>
-      <c r="N70" t="s">
-        <v>17</v>
-      </c>
-      <c r="O70" t="s">
-        <v>21</v>
-      </c>
-      <c r="P70" t="s">
+      <c r="Q70" t="s">
+        <v>21</v>
+      </c>
+      <c r="R70" t="s">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s">
         <v>362</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>21</v>
-      </c>
-      <c r="R70" t="s">
-        <v>21</v>
-      </c>
-      <c r="S70" t="s">
-        <v>21</v>
-      </c>
-      <c r="T70" t="s">
-        <v>21</v>
-      </c>
-      <c r="U70" t="s">
-        <v>363</v>
       </c>
       <c r="V70" t="s">
         <v>21</v>
@@ -9376,16 +9373,16 @@
     </row>
     <row r="71" spans="1:35">
       <c r="A71" t="s">
+        <v>363</v>
+      </c>
+      <c r="B71" t="s">
         <v>364</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
         <v>365</v>
-      </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" t="s">
-        <v>366</v>
       </c>
       <c r="E71" t="s">
         <v>21</v>
@@ -9483,16 +9480,16 @@
     </row>
     <row r="72" spans="1:35">
       <c r="A72" t="s">
+        <v>366</v>
+      </c>
+      <c r="B72" t="s">
         <v>367</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
         <v>368</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" t="s">
-        <v>369</v>
       </c>
       <c r="E72" t="s">
         <v>21</v>
@@ -9590,16 +9587,16 @@
     </row>
     <row r="73" spans="1:35">
       <c r="A73" t="s">
+        <v>369</v>
+      </c>
+      <c r="B73" t="s">
         <v>370</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
         <v>371</v>
-      </c>
-      <c r="C73" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" t="s">
-        <v>372</v>
       </c>
       <c r="E73" t="s">
         <v>21</v>
@@ -9697,17 +9694,17 @@
     </row>
     <row r="74" spans="1:35">
       <c r="A74" t="s">
+        <v>372</v>
+      </c>
+      <c r="B74" t="s">
         <v>373</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
         <v>374</v>
       </c>
-      <c r="C74" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" t="s">
-        <v>375</v>
-      </c>
       <c r="E74" t="s">
         <v>21</v>
       </c>
@@ -9748,13 +9745,13 @@
         <v>21</v>
       </c>
       <c r="R74" t="s">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="S74" t="s">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="T74" t="s">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="U74" t="s">
         <v>21</v>
@@ -9804,64 +9801,64 @@
     </row>
     <row r="75" spans="1:35">
       <c r="A75" t="s">
+        <v>375</v>
+      </c>
+      <c r="B75" t="s">
+        <v>376</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>377</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" t="s">
+        <v>17</v>
+      </c>
+      <c r="O75" t="s">
+        <v>21</v>
+      </c>
+      <c r="P75" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>21</v>
+      </c>
+      <c r="R75" t="s">
+        <v>378</v>
+      </c>
+      <c r="S75" t="s">
         <v>379</v>
       </c>
-      <c r="B75" t="s">
+      <c r="T75" t="s">
         <v>380</v>
-      </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" t="s">
-        <v>381</v>
-      </c>
-      <c r="E75" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" t="s">
-        <v>21</v>
-      </c>
-      <c r="G75" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s">
-        <v>21</v>
-      </c>
-      <c r="K75" t="s">
-        <v>21</v>
-      </c>
-      <c r="L75" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" t="s">
-        <v>21</v>
-      </c>
-      <c r="N75" t="s">
-        <v>17</v>
-      </c>
-      <c r="O75" t="s">
-        <v>21</v>
-      </c>
-      <c r="P75" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>21</v>
-      </c>
-      <c r="R75" t="s">
-        <v>21</v>
-      </c>
-      <c r="S75" t="s">
-        <v>21</v>
-      </c>
-      <c r="T75" t="s">
-        <v>21</v>
       </c>
       <c r="U75" t="s">
         <v>21</v>
@@ -9911,22 +9908,22 @@
     </row>
     <row r="76" spans="1:35">
       <c r="A76" t="s">
+        <v>381</v>
+      </c>
+      <c r="B76" t="s">
         <v>382</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
         <v>383</v>
       </c>
-      <c r="C76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>384</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>385</v>
-      </c>
-      <c r="F76" t="s">
-        <v>386</v>
       </c>
       <c r="G76" t="s">
         <v>21</v>
@@ -10018,16 +10015,16 @@
     </row>
     <row r="77" spans="1:35">
       <c r="A77" t="s">
+        <v>386</v>
+      </c>
+      <c r="B77" t="s">
         <v>387</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" t="s">
         <v>388</v>
-      </c>
-      <c r="C77" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" t="s">
-        <v>389</v>
       </c>
       <c r="E77" t="s">
         <v>21</v>
@@ -10125,55 +10122,55 @@
     </row>
     <row r="78" spans="1:35">
       <c r="A78" t="s">
+        <v>389</v>
+      </c>
+      <c r="B78" t="s">
         <v>390</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
         <v>391</v>
       </c>
-      <c r="C78" t="s">
-        <v>17</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s">
+        <v>21</v>
+      </c>
+      <c r="L78" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" t="s">
+        <v>17</v>
+      </c>
+      <c r="O78" t="s">
+        <v>21</v>
+      </c>
+      <c r="P78" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q78" t="s">
         <v>392</v>
-      </c>
-      <c r="E78" t="s">
-        <v>21</v>
-      </c>
-      <c r="F78" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" t="s">
-        <v>21</v>
-      </c>
-      <c r="H78" t="s">
-        <v>21</v>
-      </c>
-      <c r="I78" t="s">
-        <v>21</v>
-      </c>
-      <c r="J78" t="s">
-        <v>21</v>
-      </c>
-      <c r="K78" t="s">
-        <v>21</v>
-      </c>
-      <c r="L78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" t="s">
-        <v>21</v>
-      </c>
-      <c r="N78" t="s">
-        <v>17</v>
-      </c>
-      <c r="O78" t="s">
-        <v>21</v>
-      </c>
-      <c r="P78" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>393</v>
       </c>
       <c r="R78" t="s">
         <v>21</v>
@@ -10232,19 +10229,19 @@
     </row>
     <row r="79" spans="1:35">
       <c r="A79" t="s">
+        <v>393</v>
+      </c>
+      <c r="B79" t="s">
         <v>394</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" t="s">
         <v>395</v>
       </c>
-      <c r="C79" t="s">
-        <v>17</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>396</v>
-      </c>
-      <c r="E79" t="s">
-        <v>397</v>
       </c>
       <c r="F79" t="s">
         <v>21</v>
@@ -10339,16 +10336,16 @@
     </row>
     <row r="80" spans="1:35">
       <c r="A80" t="s">
+        <v>397</v>
+      </c>
+      <c r="B80" t="s">
         <v>398</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" t="s">
         <v>399</v>
-      </c>
-      <c r="C80" t="s">
-        <v>17</v>
-      </c>
-      <c r="D80" t="s">
-        <v>400</v>
       </c>
       <c r="E80" t="s">
         <v>21</v>
@@ -10446,16 +10443,16 @@
     </row>
     <row r="81" spans="1:35">
       <c r="A81" t="s">
+        <v>400</v>
+      </c>
+      <c r="B81" t="s">
         <v>401</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" t="s">
         <v>402</v>
-      </c>
-      <c r="C81" t="s">
-        <v>17</v>
-      </c>
-      <c r="D81" t="s">
-        <v>403</v>
       </c>
       <c r="E81" t="s">
         <v>21</v>
@@ -10553,16 +10550,16 @@
     </row>
     <row r="82" spans="1:35">
       <c r="A82" t="s">
+        <v>403</v>
+      </c>
+      <c r="B82" t="s">
         <v>404</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" t="s">
         <v>405</v>
-      </c>
-      <c r="C82" t="s">
-        <v>17</v>
-      </c>
-      <c r="D82" t="s">
-        <v>406</v>
       </c>
       <c r="E82" t="s">
         <v>21</v>
@@ -10660,16 +10657,16 @@
     </row>
     <row r="83" spans="1:35">
       <c r="A83" t="s">
+        <v>406</v>
+      </c>
+      <c r="B83" t="s">
         <v>407</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" t="s">
         <v>408</v>
-      </c>
-      <c r="C83" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" t="s">
-        <v>409</v>
       </c>
       <c r="E83" t="s">
         <v>21</v>
@@ -10767,19 +10764,19 @@
     </row>
     <row r="84" spans="1:35">
       <c r="A84" t="s">
+        <v>409</v>
+      </c>
+      <c r="B84" t="s">
         <v>410</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" t="s">
         <v>411</v>
       </c>
-      <c r="C84" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>412</v>
-      </c>
-      <c r="E84" t="s">
-        <v>413</v>
       </c>
       <c r="F84" t="s">
         <v>21</v>
@@ -10874,19 +10871,19 @@
     </row>
     <row r="85" spans="1:35">
       <c r="A85" t="s">
+        <v>413</v>
+      </c>
+      <c r="B85" t="s">
         <v>414</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" t="s">
         <v>415</v>
       </c>
-      <c r="C85" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>416</v>
-      </c>
-      <c r="E85" t="s">
-        <v>417</v>
       </c>
       <c r="F85" t="s">
         <v>21</v>
@@ -10981,16 +10978,16 @@
     </row>
     <row r="86" spans="1:35">
       <c r="A86" t="s">
+        <v>417</v>
+      </c>
+      <c r="B86" t="s">
         <v>418</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" t="s">
         <v>419</v>
-      </c>
-      <c r="C86" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" t="s">
-        <v>420</v>
       </c>
       <c r="E86" t="s">
         <v>21</v>
@@ -11088,16 +11085,16 @@
     </row>
     <row r="87" spans="1:35">
       <c r="A87" t="s">
+        <v>420</v>
+      </c>
+      <c r="B87" t="s">
         <v>421</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" t="s">
         <v>422</v>
-      </c>
-      <c r="C87" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" t="s">
-        <v>423</v>
       </c>
       <c r="E87" t="s">
         <v>21</v>
@@ -11195,73 +11192,73 @@
     </row>
     <row r="88" spans="1:35">
       <c r="A88" t="s">
+        <v>423</v>
+      </c>
+      <c r="B88" t="s">
         <v>424</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" t="s">
         <v>425</v>
       </c>
-      <c r="C88" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>21</v>
+      </c>
+      <c r="K88" t="s">
+        <v>21</v>
+      </c>
+      <c r="L88" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" t="s">
+        <v>17</v>
+      </c>
+      <c r="O88" t="s">
+        <v>21</v>
+      </c>
+      <c r="P88" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>21</v>
+      </c>
+      <c r="R88" t="s">
+        <v>21</v>
+      </c>
+      <c r="S88" t="s">
+        <v>21</v>
+      </c>
+      <c r="T88" t="s">
+        <v>21</v>
+      </c>
+      <c r="U88" t="s">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s">
         <v>426</v>
-      </c>
-      <c r="E88" t="s">
-        <v>21</v>
-      </c>
-      <c r="F88" t="s">
-        <v>21</v>
-      </c>
-      <c r="G88" t="s">
-        <v>21</v>
-      </c>
-      <c r="H88" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" t="s">
-        <v>21</v>
-      </c>
-      <c r="J88" t="s">
-        <v>21</v>
-      </c>
-      <c r="K88" t="s">
-        <v>21</v>
-      </c>
-      <c r="L88" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" t="s">
-        <v>21</v>
-      </c>
-      <c r="N88" t="s">
-        <v>17</v>
-      </c>
-      <c r="O88" t="s">
-        <v>21</v>
-      </c>
-      <c r="P88" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>21</v>
-      </c>
-      <c r="R88" t="s">
-        <v>21</v>
-      </c>
-      <c r="S88" t="s">
-        <v>21</v>
-      </c>
-      <c r="T88" t="s">
-        <v>21</v>
-      </c>
-      <c r="U88" t="s">
-        <v>21</v>
-      </c>
-      <c r="V88" t="s">
-        <v>21</v>
-      </c>
-      <c r="W88" t="s">
-        <v>427</v>
       </c>
       <c r="X88" t="s">
         <v>21</v>
@@ -11279,10 +11276,10 @@
         <v>198</v>
       </c>
       <c r="AC88" t="s">
+        <v>427</v>
+      </c>
+      <c r="AD88" t="s">
         <v>428</v>
-      </c>
-      <c r="AD88" t="s">
-        <v>429</v>
       </c>
       <c r="AE88" t="s">
         <v>21</v>
@@ -11302,16 +11299,16 @@
     </row>
     <row r="89" spans="1:35">
       <c r="A89" t="s">
+        <v>429</v>
+      </c>
+      <c r="B89" t="s">
         <v>430</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
         <v>431</v>
-      </c>
-      <c r="C89" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" t="s">
-        <v>432</v>
       </c>
       <c r="E89" t="s">
         <v>21</v>
@@ -11409,16 +11406,16 @@
     </row>
     <row r="90" spans="1:35">
       <c r="A90" t="s">
+        <v>432</v>
+      </c>
+      <c r="B90" t="s">
         <v>433</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" t="s">
         <v>434</v>
-      </c>
-      <c r="C90" t="s">
-        <v>17</v>
-      </c>
-      <c r="D90" t="s">
-        <v>435</v>
       </c>
       <c r="E90" t="s">
         <v>21</v>
@@ -11516,16 +11513,16 @@
     </row>
     <row r="91" spans="1:35">
       <c r="A91" t="s">
+        <v>435</v>
+      </c>
+      <c r="B91" t="s">
         <v>436</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
         <v>437</v>
-      </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" t="s">
-        <v>438</v>
       </c>
       <c r="E91" t="s">
         <v>21</v>
@@ -11623,16 +11620,16 @@
     </row>
     <row r="92" spans="1:35">
       <c r="A92" t="s">
+        <v>438</v>
+      </c>
+      <c r="B92" t="s">
         <v>439</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
         <v>440</v>
-      </c>
-      <c r="C92" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" t="s">
-        <v>441</v>
       </c>
       <c r="E92" t="s">
         <v>21</v>
@@ -11730,16 +11727,16 @@
     </row>
     <row r="93" spans="1:35">
       <c r="A93" t="s">
+        <v>441</v>
+      </c>
+      <c r="B93" t="s">
         <v>442</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
         <v>443</v>
-      </c>
-      <c r="C93" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" t="s">
-        <v>444</v>
       </c>
       <c r="E93" t="s">
         <v>21</v>
@@ -11837,16 +11834,16 @@
     </row>
     <row r="94" spans="1:35">
       <c r="A94" t="s">
+        <v>444</v>
+      </c>
+      <c r="B94" t="s">
         <v>445</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" t="s">
         <v>446</v>
-      </c>
-      <c r="C94" t="s">
-        <v>17</v>
-      </c>
-      <c r="D94" t="s">
-        <v>447</v>
       </c>
       <c r="E94" t="s">
         <v>21</v>
@@ -11944,10 +11941,10 @@
     </row>
     <row r="95" spans="1:35">
       <c r="A95" t="s">
+        <v>447</v>
+      </c>
+      <c r="B95" t="s">
         <v>448</v>
-      </c>
-      <c r="B95" t="s">
-        <v>449</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
@@ -12051,19 +12048,19 @@
     </row>
     <row r="96" spans="1:35">
       <c r="A96" t="s">
+        <v>449</v>
+      </c>
+      <c r="B96" t="s">
         <v>450</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" t="s">
         <v>451</v>
-      </c>
-      <c r="C96" t="s">
-        <v>17</v>
-      </c>
-      <c r="D96" t="s">
-        <v>21</v>
-      </c>
-      <c r="E96" t="s">
-        <v>452</v>
       </c>
       <c r="F96" t="s">
         <v>21</v>
@@ -12158,19 +12155,19 @@
     </row>
     <row r="97" spans="1:35">
       <c r="A97" t="s">
+        <v>452</v>
+      </c>
+      <c r="B97" t="s">
         <v>453</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97" t="s">
         <v>454</v>
-      </c>
-      <c r="C97" t="s">
-        <v>17</v>
-      </c>
-      <c r="D97" t="s">
-        <v>21</v>
-      </c>
-      <c r="E97" t="s">
-        <v>455</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
@@ -12265,58 +12262,58 @@
     </row>
     <row r="98" spans="1:35">
       <c r="A98" t="s">
+        <v>455</v>
+      </c>
+      <c r="B98" t="s">
         <v>456</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>21</v>
+      </c>
+      <c r="E98" t="s">
         <v>457</v>
       </c>
-      <c r="C98" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98" t="s">
-        <v>21</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
+        <v>21</v>
+      </c>
+      <c r="G98" t="s">
+        <v>21</v>
+      </c>
+      <c r="H98" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s">
+        <v>21</v>
+      </c>
+      <c r="L98" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" t="s">
+        <v>17</v>
+      </c>
+      <c r="O98" t="s">
+        <v>21</v>
+      </c>
+      <c r="P98" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>21</v>
+      </c>
+      <c r="R98" t="s">
         <v>458</v>
-      </c>
-      <c r="F98" t="s">
-        <v>21</v>
-      </c>
-      <c r="G98" t="s">
-        <v>21</v>
-      </c>
-      <c r="H98" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" t="s">
-        <v>21</v>
-      </c>
-      <c r="J98" t="s">
-        <v>21</v>
-      </c>
-      <c r="K98" t="s">
-        <v>21</v>
-      </c>
-      <c r="L98" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" t="s">
-        <v>21</v>
-      </c>
-      <c r="N98" t="s">
-        <v>17</v>
-      </c>
-      <c r="O98" t="s">
-        <v>21</v>
-      </c>
-      <c r="P98" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>21</v>
-      </c>
-      <c r="R98" t="s">
-        <v>459</v>
       </c>
       <c r="S98" t="s">
         <v>21</v>
@@ -12372,19 +12369,19 @@
     </row>
     <row r="99" spans="1:35">
       <c r="A99" t="s">
+        <v>459</v>
+      </c>
+      <c r="B99" t="s">
         <v>460</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" t="s">
         <v>461</v>
-      </c>
-      <c r="C99" t="s">
-        <v>17</v>
-      </c>
-      <c r="D99" t="s">
-        <v>21</v>
-      </c>
-      <c r="E99" t="s">
-        <v>462</v>
       </c>
       <c r="F99" t="s">
         <v>21</v>
@@ -12479,22 +12476,22 @@
     </row>
     <row r="100" spans="1:35">
       <c r="A100" t="s">
+        <v>462</v>
+      </c>
+      <c r="B100" t="s">
         <v>463</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" t="s">
         <v>464</v>
       </c>
-      <c r="C100" t="s">
-        <v>17</v>
-      </c>
-      <c r="D100" t="s">
-        <v>21</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>465</v>
-      </c>
-      <c r="F100" t="s">
-        <v>466</v>
       </c>
       <c r="G100" t="s">
         <v>21</v>
@@ -12586,19 +12583,19 @@
     </row>
     <row r="101" spans="1:35">
       <c r="A101" t="s">
+        <v>466</v>
+      </c>
+      <c r="B101" t="s">
         <v>467</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" t="s">
         <v>468</v>
-      </c>
-      <c r="C101" t="s">
-        <v>17</v>
-      </c>
-      <c r="D101" t="s">
-        <v>21</v>
-      </c>
-      <c r="E101" t="s">
-        <v>469</v>
       </c>
       <c r="F101" t="s">
         <v>21</v>
@@ -12693,19 +12690,19 @@
     </row>
     <row r="102" spans="1:35">
       <c r="A102" t="s">
+        <v>469</v>
+      </c>
+      <c r="B102" t="s">
         <v>470</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
+        <v>21</v>
+      </c>
+      <c r="E102" t="s">
         <v>471</v>
-      </c>
-      <c r="C102" t="s">
-        <v>17</v>
-      </c>
-      <c r="D102" t="s">
-        <v>21</v>
-      </c>
-      <c r="E102" t="s">
-        <v>472</v>
       </c>
       <c r="F102" t="s">
         <v>21</v>
@@ -12800,19 +12797,19 @@
     </row>
     <row r="103" spans="1:35">
       <c r="A103" t="s">
+        <v>472</v>
+      </c>
+      <c r="B103" t="s">
         <v>473</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
+        <v>21</v>
+      </c>
+      <c r="E103" t="s">
         <v>474</v>
-      </c>
-      <c r="C103" t="s">
-        <v>17</v>
-      </c>
-      <c r="D103" t="s">
-        <v>21</v>
-      </c>
-      <c r="E103" t="s">
-        <v>475</v>
       </c>
       <c r="F103" t="s">
         <v>21</v>
@@ -12907,19 +12904,19 @@
     </row>
     <row r="104" spans="1:35">
       <c r="A104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B104" t="s">
         <v>476</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>21</v>
+      </c>
+      <c r="E104" t="s">
         <v>477</v>
-      </c>
-      <c r="C104" t="s">
-        <v>17</v>
-      </c>
-      <c r="D104" t="s">
-        <v>21</v>
-      </c>
-      <c r="E104" t="s">
-        <v>478</v>
       </c>
       <c r="F104" t="s">
         <v>21</v>
@@ -13014,19 +13011,19 @@
     </row>
     <row r="105" spans="1:35">
       <c r="A105" t="s">
+        <v>478</v>
+      </c>
+      <c r="B105" t="s">
         <v>479</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105" t="s">
         <v>480</v>
-      </c>
-      <c r="C105" t="s">
-        <v>17</v>
-      </c>
-      <c r="D105" t="s">
-        <v>21</v>
-      </c>
-      <c r="E105" t="s">
-        <v>481</v>
       </c>
       <c r="F105" t="s">
         <v>21</v>
@@ -13121,19 +13118,19 @@
     </row>
     <row r="106" spans="1:35">
       <c r="A106" t="s">
+        <v>481</v>
+      </c>
+      <c r="B106" t="s">
         <v>482</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" t="s">
         <v>483</v>
-      </c>
-      <c r="C106" t="s">
-        <v>17</v>
-      </c>
-      <c r="D106" t="s">
-        <v>21</v>
-      </c>
-      <c r="E106" t="s">
-        <v>484</v>
       </c>
       <c r="F106" t="s">
         <v>21</v>
@@ -13228,19 +13225,19 @@
     </row>
     <row r="107" spans="1:35">
       <c r="A107" t="s">
+        <v>484</v>
+      </c>
+      <c r="B107" t="s">
         <v>485</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" t="s">
+        <v>21</v>
+      </c>
+      <c r="E107" t="s">
         <v>486</v>
-      </c>
-      <c r="C107" t="s">
-        <v>17</v>
-      </c>
-      <c r="D107" t="s">
-        <v>21</v>
-      </c>
-      <c r="E107" t="s">
-        <v>487</v>
       </c>
       <c r="F107" t="s">
         <v>21</v>
@@ -13335,11 +13332,11 @@
     </row>
     <row r="108" spans="1:35">
       <c r="A108" t="s">
+        <v>487</v>
+      </c>
+      <c r="B108" t="s">
         <v>488</v>
       </c>
-      <c r="B108" t="s">
-        <v>489</v>
-      </c>
       <c r="C108" t="s">
         <v>17</v>
       </c>
@@ -13347,7 +13344,7 @@
         <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F108" t="s">
         <v>21</v>
@@ -13442,19 +13439,19 @@
     </row>
     <row r="109" spans="1:35">
       <c r="A109" t="s">
+        <v>489</v>
+      </c>
+      <c r="B109" t="s">
         <v>490</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" t="s">
+        <v>21</v>
+      </c>
+      <c r="E109" t="s">
         <v>491</v>
-      </c>
-      <c r="C109" t="s">
-        <v>17</v>
-      </c>
-      <c r="D109" t="s">
-        <v>21</v>
-      </c>
-      <c r="E109" t="s">
-        <v>492</v>
       </c>
       <c r="F109" t="s">
         <v>21</v>
@@ -13549,19 +13546,19 @@
     </row>
     <row r="110" spans="1:35">
       <c r="A110" t="s">
+        <v>492</v>
+      </c>
+      <c r="B110" t="s">
         <v>493</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" t="s">
         <v>494</v>
-      </c>
-      <c r="C110" t="s">
-        <v>17</v>
-      </c>
-      <c r="D110" t="s">
-        <v>21</v>
-      </c>
-      <c r="E110" t="s">
-        <v>495</v>
       </c>
       <c r="F110" t="s">
         <v>21</v>
@@ -13656,11 +13653,11 @@
     </row>
     <row r="111" spans="1:35">
       <c r="A111" t="s">
+        <v>495</v>
+      </c>
+      <c r="B111" t="s">
         <v>496</v>
       </c>
-      <c r="B111" t="s">
-        <v>497</v>
-      </c>
       <c r="C111" t="s">
         <v>17</v>
       </c>
@@ -13668,7 +13665,7 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
@@ -13763,19 +13760,19 @@
     </row>
     <row r="112" spans="1:35">
       <c r="A112" t="s">
+        <v>497</v>
+      </c>
+      <c r="B112" t="s">
         <v>498</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" t="s">
+        <v>21</v>
+      </c>
+      <c r="E112" t="s">
         <v>499</v>
-      </c>
-      <c r="C112" t="s">
-        <v>17</v>
-      </c>
-      <c r="D112" t="s">
-        <v>21</v>
-      </c>
-      <c r="E112" t="s">
-        <v>500</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -13870,10 +13867,10 @@
     </row>
     <row r="113" spans="1:35">
       <c r="A113" t="s">
+        <v>500</v>
+      </c>
+      <c r="B113" t="s">
         <v>501</v>
-      </c>
-      <c r="B113" t="s">
-        <v>502</v>
       </c>
       <c r="C113" t="s">
         <v>17</v>
@@ -13977,67 +13974,67 @@
     </row>
     <row r="114" spans="1:35">
       <c r="A114" t="s">
+        <v>502</v>
+      </c>
+      <c r="B114" t="s">
         <v>503</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114" t="s">
+        <v>21</v>
+      </c>
+      <c r="F114" t="s">
+        <v>21</v>
+      </c>
+      <c r="G114" t="s">
+        <v>21</v>
+      </c>
+      <c r="H114" t="s">
+        <v>21</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s">
+        <v>21</v>
+      </c>
+      <c r="K114" t="s">
+        <v>21</v>
+      </c>
+      <c r="L114" t="s">
+        <v>21</v>
+      </c>
+      <c r="M114" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" t="s">
+        <v>17</v>
+      </c>
+      <c r="O114" t="s">
+        <v>21</v>
+      </c>
+      <c r="P114" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>21</v>
+      </c>
+      <c r="R114" t="s">
+        <v>21</v>
+      </c>
+      <c r="S114" t="s">
+        <v>21</v>
+      </c>
+      <c r="T114" t="s">
+        <v>21</v>
+      </c>
+      <c r="U114" t="s">
         <v>504</v>
-      </c>
-      <c r="C114" t="s">
-        <v>17</v>
-      </c>
-      <c r="D114" t="s">
-        <v>21</v>
-      </c>
-      <c r="E114" t="s">
-        <v>21</v>
-      </c>
-      <c r="F114" t="s">
-        <v>21</v>
-      </c>
-      <c r="G114" t="s">
-        <v>21</v>
-      </c>
-      <c r="H114" t="s">
-        <v>21</v>
-      </c>
-      <c r="I114" t="s">
-        <v>21</v>
-      </c>
-      <c r="J114" t="s">
-        <v>21</v>
-      </c>
-      <c r="K114" t="s">
-        <v>21</v>
-      </c>
-      <c r="L114" t="s">
-        <v>21</v>
-      </c>
-      <c r="M114" t="s">
-        <v>21</v>
-      </c>
-      <c r="N114" t="s">
-        <v>17</v>
-      </c>
-      <c r="O114" t="s">
-        <v>21</v>
-      </c>
-      <c r="P114" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>21</v>
-      </c>
-      <c r="R114" t="s">
-        <v>21</v>
-      </c>
-      <c r="S114" t="s">
-        <v>21</v>
-      </c>
-      <c r="T114" t="s">
-        <v>21</v>
-      </c>
-      <c r="U114" t="s">
-        <v>505</v>
       </c>
       <c r="V114" t="s">
         <v>21</v>
@@ -14084,37 +14081,37 @@
     </row>
     <row r="115" spans="1:35">
       <c r="A115" t="s">
+        <v>505</v>
+      </c>
+      <c r="B115" t="s">
         <v>506</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115" t="s">
+        <v>21</v>
+      </c>
+      <c r="F115" t="s">
+        <v>21</v>
+      </c>
+      <c r="G115" t="s">
+        <v>21</v>
+      </c>
+      <c r="H115" t="s">
+        <v>21</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s">
+        <v>21</v>
+      </c>
+      <c r="K115" t="s">
         <v>507</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
-      </c>
-      <c r="D115" t="s">
-        <v>21</v>
-      </c>
-      <c r="E115" t="s">
-        <v>21</v>
-      </c>
-      <c r="F115" t="s">
-        <v>21</v>
-      </c>
-      <c r="G115" t="s">
-        <v>21</v>
-      </c>
-      <c r="H115" t="s">
-        <v>21</v>
-      </c>
-      <c r="I115" t="s">
-        <v>21</v>
-      </c>
-      <c r="J115" t="s">
-        <v>21</v>
-      </c>
-      <c r="K115" t="s">
-        <v>508</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>

--- a/upload/ar_aging_report_converted.xlsx
+++ b/upload/ar_aging_report_converted.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="498">
   <si>
     <t>Customer Header Number</t>
   </si>
@@ -71,46 +71,46 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>35,713.59</t>
-  </si>
-  <si>
-    <t>456.09</t>
-  </si>
-  <si>
-    <t>384.31</t>
+    <t>9,398.31</t>
+  </si>
+  <si>
+    <t>120.02</t>
+  </si>
+  <si>
+    <t>101.13</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>-71.38</t>
-  </si>
-  <si>
-    <t>-2,435.23</t>
-  </si>
-  <si>
-    <t>-84.16</t>
-  </si>
-  <si>
-    <t>-203.54</t>
-  </si>
-  <si>
-    <t>-35.14</t>
-  </si>
-  <si>
-    <t>160.52</t>
-  </si>
-  <si>
-    <t>251.14</t>
-  </si>
-  <si>
-    <t>817.72</t>
-  </si>
-  <si>
-    <t>98.23</t>
-  </si>
-  <si>
-    <t>141.56</t>
+    <t>-18.78</t>
+  </si>
+  <si>
+    <t>-640.85</t>
+  </si>
+  <si>
+    <t>-22.15</t>
+  </si>
+  <si>
+    <t>-53.56</t>
+  </si>
+  <si>
+    <t>-9.25</t>
+  </si>
+  <si>
+    <t>42.24</t>
+  </si>
+  <si>
+    <t>66.09</t>
+  </si>
+  <si>
+    <t>215.19</t>
+  </si>
+  <si>
+    <t>25.85</t>
+  </si>
+  <si>
+    <t>37.25</t>
   </si>
   <si>
     <t>PE000968001H</t>
@@ -119,37 +119,37 @@
     <t>SAGA  FALABELLA  S.A.</t>
   </si>
   <si>
-    <t>33,990.58</t>
-  </si>
-  <si>
-    <t>3,661.26</t>
-  </si>
-  <si>
-    <t>311.34</t>
-  </si>
-  <si>
-    <t>-34.48</t>
-  </si>
-  <si>
-    <t>-11.03</t>
-  </si>
-  <si>
-    <t>-2,455.84</t>
-  </si>
-  <si>
-    <t>-19.57</t>
-  </si>
-  <si>
-    <t>-15.55</t>
-  </si>
-  <si>
-    <t>-8.96</t>
-  </si>
-  <si>
-    <t>497.27</t>
-  </si>
-  <si>
-    <t>375.66</t>
+    <t>8,944.89</t>
+  </si>
+  <si>
+    <t>963.49</t>
+  </si>
+  <si>
+    <t>81.93</t>
+  </si>
+  <si>
+    <t>-9.07</t>
+  </si>
+  <si>
+    <t>-2.90</t>
+  </si>
+  <si>
+    <t>-646.27</t>
+  </si>
+  <si>
+    <t>-5.15</t>
+  </si>
+  <si>
+    <t>-4.09</t>
+  </si>
+  <si>
+    <t>-2.36</t>
+  </si>
+  <si>
+    <t>130.86</t>
+  </si>
+  <si>
+    <t>98.86</t>
   </si>
   <si>
     <t>PE001351001H</t>
@@ -158,49 +158,49 @@
     <t>SUPERMERCADOS PERUANOS  S.A.</t>
   </si>
   <si>
-    <t>23,852.80</t>
-  </si>
-  <si>
-    <t>3,100.45</t>
-  </si>
-  <si>
-    <t>342.61</t>
-  </si>
-  <si>
-    <t>6.65</t>
-  </si>
-  <si>
-    <t>4.61</t>
-  </si>
-  <si>
-    <t>-2,320.75</t>
-  </si>
-  <si>
-    <t>-10.16</t>
-  </si>
-  <si>
-    <t>-364.85</t>
-  </si>
-  <si>
-    <t>-0.05</t>
-  </si>
-  <si>
-    <t>-7.16</t>
-  </si>
-  <si>
-    <t>-20.46</t>
-  </si>
-  <si>
-    <t>-1.83</t>
-  </si>
-  <si>
-    <t>256.13</t>
-  </si>
-  <si>
-    <t>114.53</t>
-  </si>
-  <si>
-    <t>137.95</t>
+    <t>6,277.05</t>
+  </si>
+  <si>
+    <t>815.91</t>
+  </si>
+  <si>
+    <t>90.16</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>-610.72</t>
+  </si>
+  <si>
+    <t>-2.67</t>
+  </si>
+  <si>
+    <t>-96.01</t>
+  </si>
+  <si>
+    <t>-0.01</t>
+  </si>
+  <si>
+    <t>-1.88</t>
+  </si>
+  <si>
+    <t>-5.38</t>
+  </si>
+  <si>
+    <t>-0.48</t>
+  </si>
+  <si>
+    <t>67.40</t>
+  </si>
+  <si>
+    <t>30.14</t>
+  </si>
+  <si>
+    <t>36.30</t>
   </si>
   <si>
     <t>PE000815001H</t>
@@ -209,19 +209,19 @@
     <t>IMPORTACIONES HIRAOKA S.A.</t>
   </si>
   <si>
-    <t>23,808.44</t>
-  </si>
-  <si>
-    <t>328.17</t>
-  </si>
-  <si>
-    <t>-548.86</t>
-  </si>
-  <si>
-    <t>-218.62</t>
-  </si>
-  <si>
-    <t>-243.74</t>
+    <t>6,265.38</t>
+  </si>
+  <si>
+    <t>86.36</t>
+  </si>
+  <si>
+    <t>-144.44</t>
+  </si>
+  <si>
+    <t>-57.53</t>
+  </si>
+  <si>
+    <t>-64.14</t>
   </si>
   <si>
     <t>PE000991001H</t>
@@ -230,19 +230,16 @@
     <t>CONECTA RETAIL S.A.</t>
   </si>
   <si>
-    <t>23,583.64</t>
-  </si>
-  <si>
-    <t>1,490.87</t>
-  </si>
-  <si>
-    <t>-7.15</t>
-  </si>
-  <si>
-    <t>-17.27</t>
-  </si>
-  <si>
-    <t>8.40</t>
+    <t>6,206.22</t>
+  </si>
+  <si>
+    <t>392.33</t>
+  </si>
+  <si>
+    <t>-4.55</t>
+  </si>
+  <si>
+    <t>2.21</t>
   </si>
   <si>
     <t>PE007152001H</t>
@@ -251,19 +248,19 @@
     <t>TIENDAS PERUANAS S.A.</t>
   </si>
   <si>
-    <t>21,192.86</t>
-  </si>
-  <si>
-    <t>1,142.11</t>
-  </si>
-  <si>
-    <t>-21.45</t>
-  </si>
-  <si>
-    <t>-1.68</t>
-  </si>
-  <si>
-    <t>150.23</t>
+    <t>5,577.07</t>
+  </si>
+  <si>
+    <t>300.56</t>
+  </si>
+  <si>
+    <t>-5.64</t>
+  </si>
+  <si>
+    <t>-0.44</t>
+  </si>
+  <si>
+    <t>39.53</t>
   </si>
   <si>
     <t>PE004467001H</t>
@@ -272,31 +269,31 @@
     <t>HIPERMERCADOS TOTTUS S.A.</t>
   </si>
   <si>
-    <t>19,448.48</t>
-  </si>
-  <si>
-    <t>450.20</t>
-  </si>
-  <si>
-    <t>-749.84</t>
-  </si>
-  <si>
-    <t>-148.01</t>
-  </si>
-  <si>
-    <t>-10.74</t>
-  </si>
-  <si>
-    <t>-1.58</t>
-  </si>
-  <si>
-    <t>-1.14</t>
-  </si>
-  <si>
-    <t>182.66</t>
-  </si>
-  <si>
-    <t>219.10</t>
+    <t>5,118.02</t>
+  </si>
+  <si>
+    <t>118.47</t>
+  </si>
+  <si>
+    <t>-197.33</t>
+  </si>
+  <si>
+    <t>-38.95</t>
+  </si>
+  <si>
+    <t>-2.83</t>
+  </si>
+  <si>
+    <t>-0.42</t>
+  </si>
+  <si>
+    <t>-0.30</t>
+  </si>
+  <si>
+    <t>48.07</t>
+  </si>
+  <si>
+    <t>57.66</t>
   </si>
   <si>
     <t>PE000801001H</t>
@@ -305,25 +302,25 @@
     <t>CENCOSUD RETAIL PERU S.A.</t>
   </si>
   <si>
-    <t>11,421.55</t>
-  </si>
-  <si>
-    <t>645.76</t>
-  </si>
-  <si>
-    <t>42.12</t>
-  </si>
-  <si>
-    <t>-505.07</t>
-  </si>
-  <si>
-    <t>-237.77</t>
-  </si>
-  <si>
-    <t>70.96</t>
-  </si>
-  <si>
-    <t>69.18</t>
+    <t>3,005.67</t>
+  </si>
+  <si>
+    <t>169.94</t>
+  </si>
+  <si>
+    <t>11.09</t>
+  </si>
+  <si>
+    <t>-132.91</t>
+  </si>
+  <si>
+    <t>-62.57</t>
+  </si>
+  <si>
+    <t>18.67</t>
+  </si>
+  <si>
+    <t>18.21</t>
   </si>
   <si>
     <t>PY000933011H</t>
@@ -332,10 +329,10 @@
     <t>LASER IMPORT S.A.</t>
   </si>
   <si>
-    <t>10,292.65</t>
-  </si>
-  <si>
-    <t>172.35</t>
+    <t>2,708.59</t>
+  </si>
+  <si>
+    <t>45.36</t>
   </si>
   <si>
     <t>UY000855005H</t>
@@ -344,10 +341,10 @@
     <t>ESTAWOL S.A.</t>
   </si>
   <si>
-    <t>8,028.76</t>
-  </si>
-  <si>
-    <t>81.20</t>
+    <t>2,112.83</t>
+  </si>
+  <si>
+    <t>21.37</t>
   </si>
   <si>
     <t>PE008204001H</t>
@@ -356,10 +353,10 @@
     <t>INTEGRA RETAIL S.A.C.</t>
   </si>
   <si>
-    <t>6,833.54</t>
-  </si>
-  <si>
-    <t>-158.22</t>
+    <t>1,798.30</t>
+  </si>
+  <si>
+    <t>-41.64</t>
   </si>
   <si>
     <t>PY001022004H</t>
@@ -368,7 +365,7 @@
     <t>Karry S.A.</t>
   </si>
   <si>
-    <t>6,642.34</t>
+    <t>1,747.99</t>
   </si>
   <si>
     <t>BO000681002H</t>
@@ -377,10 +374,10 @@
     <t>Dismatec S.A.</t>
   </si>
   <si>
-    <t>4,853.48</t>
-  </si>
-  <si>
-    <t>0.36</t>
+    <t>1,277.23</t>
+  </si>
+  <si>
+    <t>0.10</t>
   </si>
   <si>
     <t>BO000785002H</t>
@@ -389,10 +386,10 @@
     <t>Import Export Salvatierra S.A.</t>
   </si>
   <si>
-    <t>4,572.41</t>
-  </si>
-  <si>
-    <t>21.00</t>
+    <t>1,203.27</t>
+  </si>
+  <si>
+    <t>5.53</t>
   </si>
   <si>
     <t>PE000952001H</t>
@@ -401,25 +398,25 @@
     <t>REPRESENTACIONES VARGAS S.A.</t>
   </si>
   <si>
-    <t>4,022.58</t>
-  </si>
-  <si>
-    <t>-6.86</t>
-  </si>
-  <si>
-    <t>-8.28</t>
-  </si>
-  <si>
-    <t>-183.11</t>
-  </si>
-  <si>
-    <t>-2.45</t>
-  </si>
-  <si>
-    <t>-3.61</t>
-  </si>
-  <si>
-    <t>-36.76</t>
+    <t>1,058.57</t>
+  </si>
+  <si>
+    <t>-1.81</t>
+  </si>
+  <si>
+    <t>-2.18</t>
+  </si>
+  <si>
+    <t>-48.19</t>
+  </si>
+  <si>
+    <t>-0.64</t>
+  </si>
+  <si>
+    <t>-0.95</t>
+  </si>
+  <si>
+    <t>-9.67</t>
   </si>
   <si>
     <t>PE003887001H</t>
@@ -428,25 +425,25 @@
     <t>ESTILOS S.R.L.</t>
   </si>
   <si>
-    <t>2,770.81</t>
-  </si>
-  <si>
-    <t>148.95</t>
-  </si>
-  <si>
-    <t>-38.44</t>
-  </si>
-  <si>
-    <t>-263.46</t>
-  </si>
-  <si>
-    <t>-2.00</t>
-  </si>
-  <si>
-    <t>-8.03</t>
-  </si>
-  <si>
-    <t>-52.83</t>
+    <t>729.16</t>
+  </si>
+  <si>
+    <t>39.20</t>
+  </si>
+  <si>
+    <t>-10.12</t>
+  </si>
+  <si>
+    <t>-69.33</t>
+  </si>
+  <si>
+    <t>-0.53</t>
+  </si>
+  <si>
+    <t>-2.11</t>
+  </si>
+  <si>
+    <t>-13.90</t>
   </si>
   <si>
     <t>PE000820001H</t>
@@ -455,1068 +452,1041 @@
     <t>IMPORTACIONES RUBI S.A.</t>
   </si>
   <si>
-    <t>2,404.24</t>
+    <t>632.69</t>
+  </si>
+  <si>
+    <t>-0.16</t>
+  </si>
+  <si>
+    <t>PE008104001H</t>
+  </si>
+  <si>
+    <t>CONECTA RETAIL SELVA S.A.C.</t>
+  </si>
+  <si>
+    <t>615.21</t>
+  </si>
+  <si>
+    <t>51.34</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>PE008110001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL REFRIGERACION PERU S</t>
+  </si>
+  <si>
+    <t>549.32</t>
+  </si>
+  <si>
+    <t>73.71</t>
+  </si>
+  <si>
+    <t>PE000984001H</t>
+  </si>
+  <si>
+    <t>INGRAM MICRO S.A.C.</t>
+  </si>
+  <si>
+    <t>536.87</t>
+  </si>
+  <si>
+    <t>2.44</t>
+  </si>
+  <si>
+    <t>-20.86</t>
+  </si>
+  <si>
+    <t>-0.58</t>
+  </si>
+  <si>
+    <t>-0.14</t>
+  </si>
+  <si>
+    <t>-0.41</t>
+  </si>
+  <si>
+    <t>PE008158001H</t>
+  </si>
+  <si>
+    <t>HOMECENTERS PERUANOS S.A.</t>
+  </si>
+  <si>
+    <t>519.93</t>
+  </si>
+  <si>
+    <t>64.84</t>
+  </si>
+  <si>
+    <t>4.52</t>
+  </si>
+  <si>
+    <t>2.03</t>
+  </si>
+  <si>
+    <t>-47.93</t>
+  </si>
+  <si>
+    <t>-0.51</t>
+  </si>
+  <si>
+    <t>2.97</t>
+  </si>
+  <si>
+    <t>PE001839001H</t>
+  </si>
+  <si>
+    <t>PC LINK SOCIEDAD ANONIMA CERRA</t>
+  </si>
+  <si>
+    <t>449.47</t>
+  </si>
+  <si>
+    <t>30.74</t>
+  </si>
+  <si>
+    <t>-31.58</t>
+  </si>
+  <si>
+    <t>-0.71</t>
+  </si>
+  <si>
+    <t>PE006374001H</t>
+  </si>
+  <si>
+    <t>TIENDAS DEL MEJORAMIENTO DEL H</t>
+  </si>
+  <si>
+    <t>427.40</t>
+  </si>
+  <si>
+    <t>62.70</t>
+  </si>
+  <si>
+    <t>46.14</t>
   </si>
   <si>
     <t>-0.59</t>
   </si>
   <si>
-    <t>PE008104001H</t>
-  </si>
-  <si>
-    <t>CONECTA RETAIL SELVA S.A.C.</t>
-  </si>
-  <si>
-    <t>2,337.79</t>
-  </si>
-  <si>
-    <t>195.11</t>
+    <t>-37.12</t>
+  </si>
+  <si>
+    <t>-0.49</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>4.14</t>
+  </si>
+  <si>
+    <t>PE002194001H</t>
+  </si>
+  <si>
+    <t>COMPUDISKETT SRL</t>
+  </si>
+  <si>
+    <t>403.67</t>
+  </si>
+  <si>
+    <t>-0.11</t>
+  </si>
+  <si>
+    <t>-1.18</t>
+  </si>
+  <si>
+    <t>PE002897001H</t>
+  </si>
+  <si>
+    <t>GRUPO DELTRON S.A.</t>
+  </si>
+  <si>
+    <t>319.45</t>
   </si>
   <si>
     <t>0.18</t>
   </si>
   <si>
-    <t>PE008110001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL REFRIGERACION PERU S</t>
-  </si>
-  <si>
-    <t>2,087.43</t>
-  </si>
-  <si>
-    <t>280.11</t>
-  </si>
-  <si>
-    <t>PE000984001H</t>
-  </si>
-  <si>
-    <t>INGRAM MICRO S.A.C.</t>
-  </si>
-  <si>
-    <t>2,040.10</t>
-  </si>
-  <si>
-    <t>9.28</t>
-  </si>
-  <si>
-    <t>-79.26</t>
-  </si>
-  <si>
-    <t>-2.20</t>
-  </si>
-  <si>
-    <t>-0.52</t>
-  </si>
-  <si>
-    <t>-1.57</t>
-  </si>
-  <si>
-    <t>PE008158001H</t>
-  </si>
-  <si>
-    <t>HOMECENTERS PERUANOS S.A.</t>
-  </si>
-  <si>
-    <t>1,975.74</t>
-  </si>
-  <si>
-    <t>246.41</t>
-  </si>
-  <si>
-    <t>17.16</t>
-  </si>
-  <si>
-    <t>7.72</t>
-  </si>
-  <si>
-    <t>-182.12</t>
-  </si>
-  <si>
-    <t>-1.94</t>
-  </si>
-  <si>
-    <t>11.28</t>
-  </si>
-  <si>
-    <t>PE001839001H</t>
-  </si>
-  <si>
-    <t>PC LINK SOCIEDAD ANONIMA CERRA</t>
-  </si>
-  <si>
-    <t>1,708.00</t>
-  </si>
-  <si>
-    <t>116.82</t>
-  </si>
-  <si>
-    <t>-120.02</t>
-  </si>
-  <si>
-    <t>-2.69</t>
-  </si>
-  <si>
-    <t>PE006374001H</t>
-  </si>
-  <si>
-    <t>TIENDAS DEL MEJORAMIENTO DEL H</t>
-  </si>
-  <si>
-    <t>1,624.12</t>
-  </si>
-  <si>
-    <t>238.24</t>
-  </si>
-  <si>
-    <t>175.32</t>
-  </si>
-  <si>
-    <t>-2.24</t>
-  </si>
-  <si>
-    <t>-141.06</t>
-  </si>
-  <si>
-    <t>-1.85</t>
-  </si>
-  <si>
-    <t>0.14</t>
-  </si>
-  <si>
-    <t>15.73</t>
-  </si>
-  <si>
-    <t>PE002194001H</t>
-  </si>
-  <si>
-    <t>COMPUDISKETT SRL</t>
-  </si>
-  <si>
-    <t>1,533.95</t>
+    <t>17.98</t>
+  </si>
+  <si>
+    <t>-0.09</t>
+  </si>
+  <si>
+    <t>-19.58</t>
+  </si>
+  <si>
+    <t>UY000615003H</t>
+  </si>
+  <si>
+    <t>OCEANLUX, S.A.</t>
+  </si>
+  <si>
+    <t>310.46</t>
+  </si>
+  <si>
+    <t>PE008303001H</t>
+  </si>
+  <si>
+    <t>GRUPO MERPES PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>269.03</t>
+  </si>
+  <si>
+    <t>PE006905001H</t>
+  </si>
+  <si>
+    <t>UEZU COMERCIAL SAC</t>
+  </si>
+  <si>
+    <t>265.52</t>
+  </si>
+  <si>
+    <t>-0.15</t>
+  </si>
+  <si>
+    <t>PE008257001H</t>
+  </si>
+  <si>
+    <t>COLDSMART PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>230.81</t>
+  </si>
+  <si>
+    <t>32.11</t>
+  </si>
+  <si>
+    <t>PE007687001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL FRIONORTE E.I.R.L.</t>
+  </si>
+  <si>
+    <t>180.01</t>
+  </si>
+  <si>
+    <t>PE008420001H</t>
+  </si>
+  <si>
+    <t>AIR COOL SYSTEM SM S.A.C.</t>
+  </si>
+  <si>
+    <t>178.30</t>
+  </si>
+  <si>
+    <t>PE004417001H</t>
+  </si>
+  <si>
+    <t>REPRESENTACIONES MONTERO S.R.L</t>
+  </si>
+  <si>
+    <t>176.13</t>
+  </si>
+  <si>
+    <t>UY000854004H</t>
+  </si>
+  <si>
+    <t>Solution Box Uruguay</t>
+  </si>
+  <si>
+    <t>172.02</t>
+  </si>
+  <si>
+    <t>PE000717001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL COUNTRY S.A.</t>
+  </si>
+  <si>
+    <t>160.39</t>
+  </si>
+  <si>
+    <t>22.51</t>
+  </si>
+  <si>
+    <t>PE008466001H</t>
+  </si>
+  <si>
+    <t>SONEPAR PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>128.69</t>
+  </si>
+  <si>
+    <t>PE008453001H</t>
+  </si>
+  <si>
+    <t>MAXIMA INTERNACIONAL S.A.</t>
+  </si>
+  <si>
+    <t>128.50</t>
+  </si>
+  <si>
+    <t>28.11</t>
+  </si>
+  <si>
+    <t>PE008292001H</t>
+  </si>
+  <si>
+    <t>One time_OBS</t>
+  </si>
+  <si>
+    <t>109.76</t>
+  </si>
+  <si>
+    <t>16.42</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>-0.69</t>
+  </si>
+  <si>
+    <t>22.87</t>
+  </si>
+  <si>
+    <t>20.35</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>PE008153001H</t>
+  </si>
+  <si>
+    <t>DACER SOCIEDAD ANONIMA CERRADA</t>
+  </si>
+  <si>
+    <t>99.95</t>
+  </si>
+  <si>
+    <t>PE001507001H</t>
+  </si>
+  <si>
+    <t>IREDI INTERNATIONAL S.R.L</t>
+  </si>
+  <si>
+    <t>99.22</t>
+  </si>
+  <si>
+    <t>PA000001010H</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS PANAMA S.A.</t>
+  </si>
+  <si>
+    <t>91.45</t>
+  </si>
+  <si>
+    <t>PE003288001H</t>
+  </si>
+  <si>
+    <t>PKC TECHNOLOGY S.R.L.</t>
+  </si>
+  <si>
+    <t>88.18</t>
+  </si>
+  <si>
+    <t>-1.16</t>
+  </si>
+  <si>
+    <t>PE008291001H</t>
+  </si>
+  <si>
+    <t>SERFAC S.A.C.</t>
+  </si>
+  <si>
+    <t>76.76</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>PE000854001H</t>
+  </si>
+  <si>
+    <t>SUCESION JUAN PINTO RUIZ</t>
+  </si>
+  <si>
+    <t>73.50</t>
+  </si>
+  <si>
+    <t>PE000853001H</t>
+  </si>
+  <si>
+    <t>JUAN PABLO MORI E.I.R.L.</t>
+  </si>
+  <si>
+    <t>68.20</t>
+  </si>
+  <si>
+    <t>PE007607001H</t>
+  </si>
+  <si>
+    <t>INGENIEROS FRIOTEMP S.A.C.</t>
+  </si>
+  <si>
+    <t>65.23</t>
+  </si>
+  <si>
+    <t>PE008441001H</t>
+  </si>
+  <si>
+    <t>RICOH DEL PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>61.28</t>
+  </si>
+  <si>
+    <t>PE007714001H</t>
+  </si>
+  <si>
+    <t>COINREFRI AIR S.A.C.</t>
+  </si>
+  <si>
+    <t>56.87</t>
+  </si>
+  <si>
+    <t>12.66</t>
+  </si>
+  <si>
+    <t>UY000858004H</t>
+  </si>
+  <si>
+    <t>JOACAMAR</t>
+  </si>
+  <si>
+    <t>50.90</t>
+  </si>
+  <si>
+    <t>PY001162002H</t>
+  </si>
+  <si>
+    <t>CENTRONIC S.A.</t>
+  </si>
+  <si>
+    <t>49.94</t>
+  </si>
+  <si>
+    <t>PE008312001H</t>
+  </si>
+  <si>
+    <t>TIENDAS CHANCAFE S.A.C.</t>
+  </si>
+  <si>
+    <t>45.25</t>
+  </si>
+  <si>
+    <t>-0.78</t>
+  </si>
+  <si>
+    <t>PE004725001H</t>
+  </si>
+  <si>
+    <t>NEXSYS DEL PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>44.94</t>
+  </si>
+  <si>
+    <t>-9.15</t>
+  </si>
+  <si>
+    <t>-7.09</t>
+  </si>
+  <si>
+    <t>PE008017001H</t>
+  </si>
+  <si>
+    <t>CHANCAFE ORIENTE S.A.C.</t>
+  </si>
+  <si>
+    <t>42.19</t>
+  </si>
+  <si>
+    <t>-0.60</t>
+  </si>
+  <si>
+    <t>PE004373001H</t>
+  </si>
+  <si>
+    <t>PROTERM PERU S..AC.</t>
+  </si>
+  <si>
+    <t>37.89</t>
+  </si>
+  <si>
+    <t>CO000002006H</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>37.09</t>
+  </si>
+  <si>
+    <t>PE008165001H</t>
+  </si>
+  <si>
+    <t>TODOCLIMA PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>32.57</t>
+  </si>
+  <si>
+    <t>PE008064001H</t>
+  </si>
+  <si>
+    <t>MEGA SHOP FRIO SOC. COM. RESPO</t>
+  </si>
+  <si>
+    <t>29.07</t>
+  </si>
+  <si>
+    <t>5.00</t>
+  </si>
+  <si>
+    <t>PE008139001H</t>
+  </si>
+  <si>
+    <t>GREENCORP PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>25.66</t>
+  </si>
+  <si>
+    <t>PE008020001H</t>
+  </si>
+  <si>
+    <t>HIPERMERCADOS TOTTUS ORIENTE S</t>
+  </si>
+  <si>
+    <t>23.78</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>PE000777001H</t>
+  </si>
+  <si>
+    <t>ELECTRONICA NORTE S.R.LTDA</t>
+  </si>
+  <si>
+    <t>8.91</t>
+  </si>
+  <si>
+    <t>PE003268001H</t>
+  </si>
+  <si>
+    <t>SERVICIOS ELECTRONICOS LA RECO</t>
+  </si>
+  <si>
+    <t>8.29</t>
   </si>
   <si>
     <t>-0.40</t>
   </si>
   <si>
-    <t>-4.48</t>
-  </si>
-  <si>
-    <t>PE002897001H</t>
-  </si>
-  <si>
-    <t>GRUPO DELTRON S.A.</t>
-  </si>
-  <si>
-    <t>1,213.91</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>68.34</t>
-  </si>
-  <si>
-    <t>-0.34</t>
-  </si>
-  <si>
-    <t>-74.40</t>
-  </si>
-  <si>
-    <t>UY000615003H</t>
-  </si>
-  <si>
-    <t>OCEANLUX, S.A.</t>
-  </si>
-  <si>
-    <t>1,179.76</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>PE008303001H</t>
-  </si>
-  <si>
-    <t>GRUPO MERPES PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>1,022.31</t>
-  </si>
-  <si>
-    <t>PE006905001H</t>
-  </si>
-  <si>
-    <t>UEZU COMERCIAL SAC</t>
-  </si>
-  <si>
-    <t>1,008.98</t>
-  </si>
-  <si>
-    <t>-0.55</t>
-  </si>
-  <si>
-    <t>PE008257001H</t>
-  </si>
-  <si>
-    <t>COLDSMART PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>877.09</t>
-  </si>
-  <si>
-    <t>122.01</t>
-  </si>
-  <si>
-    <t>PE007687001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL FRIONORTE E.I.R.L.</t>
-  </si>
-  <si>
-    <t>684.05</t>
-  </si>
-  <si>
-    <t>PE008420001H</t>
-  </si>
-  <si>
-    <t>AIR COOL SYSTEM SM S.A.C.</t>
-  </si>
-  <si>
-    <t>677.53</t>
-  </si>
-  <si>
-    <t>PE004417001H</t>
-  </si>
-  <si>
-    <t>REPRESENTACIONES MONTERO S.R.L</t>
-  </si>
-  <si>
-    <t>669.29</t>
-  </si>
-  <si>
-    <t>UY000854004H</t>
-  </si>
-  <si>
-    <t>Solution Box Uruguay</t>
-  </si>
-  <si>
-    <t>653.68</t>
-  </si>
-  <si>
-    <t>PE000717001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL COUNTRY S.A.</t>
-  </si>
-  <si>
-    <t>609.48</t>
-  </si>
-  <si>
-    <t>85.54</t>
-  </si>
-  <si>
-    <t>PE008466001H</t>
-  </si>
-  <si>
-    <t>SONEPAR PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>489.00</t>
-  </si>
-  <si>
-    <t>PE008453001H</t>
-  </si>
-  <si>
-    <t>MAXIMA INTERNACIONAL S.A.</t>
-  </si>
-  <si>
-    <t>488.30</t>
-  </si>
-  <si>
-    <t>106.81</t>
-  </si>
-  <si>
-    <t>PE008292001H</t>
-  </si>
-  <si>
-    <t>One time_OBS</t>
-  </si>
-  <si>
-    <t>417.11</t>
-  </si>
-  <si>
-    <t>62.40</t>
+    <t>PY001038002H</t>
+  </si>
+  <si>
+    <t>SERVIPHIL S.R.L</t>
+  </si>
+  <si>
+    <t>7.96</t>
+  </si>
+  <si>
+    <t>PE001020001H</t>
+  </si>
+  <si>
+    <t>TECNICAV S</t>
+  </si>
+  <si>
+    <t>7.93</t>
+  </si>
+  <si>
+    <t>PE008083001H</t>
+  </si>
+  <si>
+    <t>CLIMA TECNICA PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>7.26</t>
+  </si>
+  <si>
+    <t>PE008141001H</t>
+  </si>
+  <si>
+    <t>ANIXTER PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>6.88</t>
+  </si>
+  <si>
+    <t>UY000836002H</t>
+  </si>
+  <si>
+    <t>LAVOMAT</t>
+  </si>
+  <si>
+    <t>6.69</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>PE006831001H</t>
+  </si>
+  <si>
+    <t>FORCE SERVICE S.R.L.</t>
+  </si>
+  <si>
+    <t>6.27</t>
+  </si>
+  <si>
+    <t>PE005273001H</t>
+  </si>
+  <si>
+    <t>CESER EIRL</t>
+  </si>
+  <si>
+    <t>5.88</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>UY000853002H</t>
+  </si>
+  <si>
+    <t>Odalmar S.A.</t>
+  </si>
+  <si>
+    <t>5.44</t>
+  </si>
+  <si>
+    <t>3.41</t>
+  </si>
+  <si>
+    <t>PE006934001H</t>
+  </si>
+  <si>
+    <t>PROMOTICK S.A.C.</t>
+  </si>
+  <si>
+    <t>5.21</t>
+  </si>
+  <si>
+    <t>4.85</t>
+  </si>
+  <si>
+    <t>-0.08</t>
+  </si>
+  <si>
+    <t>-0.68</t>
+  </si>
+  <si>
+    <t>PE008455001H</t>
+  </si>
+  <si>
+    <t>REWARDS PERU S.A.C.</t>
+  </si>
+  <si>
+    <t>5.19</t>
+  </si>
+  <si>
+    <t>BO000662002H</t>
+  </si>
+  <si>
+    <t>Censel</t>
+  </si>
+  <si>
+    <t>5.06</t>
+  </si>
+  <si>
+    <t>PE008022001H</t>
+  </si>
+  <si>
+    <t>SERTEPI E.I.R.L.</t>
+  </si>
+  <si>
+    <t>4.59</t>
+  </si>
+  <si>
+    <t>PE008105001H</t>
+  </si>
+  <si>
+    <t>LATINAMENITIES S.A.C.</t>
+  </si>
+  <si>
+    <t>4.55</t>
+  </si>
+  <si>
+    <t>PE004102001H</t>
+  </si>
+  <si>
+    <t>MI NEGOCIO EMPRESA INDIVIDUAL</t>
+  </si>
+  <si>
+    <t>-1.61</t>
+  </si>
+  <si>
+    <t>-0.72</t>
+  </si>
+  <si>
+    <t>-1.55</t>
+  </si>
+  <si>
+    <t>PE007296001H</t>
+  </si>
+  <si>
+    <t>One time_Employee</t>
+  </si>
+  <si>
+    <t>4.44</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
+    <t>PE004799001H</t>
+  </si>
+  <si>
+    <t>SERVINORTE EIRL</t>
+  </si>
+  <si>
+    <t>4.26</t>
+  </si>
+  <si>
+    <t>PE004800001H</t>
+  </si>
+  <si>
+    <t>MULTIREPARACIONES DIGITALES IC</t>
+  </si>
+  <si>
+    <t>3.98</t>
+  </si>
+  <si>
+    <t>-0.07</t>
+  </si>
+  <si>
+    <t>PE001399001H</t>
+  </si>
+  <si>
+    <t>ASPERSUD</t>
+  </si>
+  <si>
+    <t>3.61</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>PE008175001H</t>
+  </si>
+  <si>
+    <t>HAROLD MULTISERVIS EIRL</t>
+  </si>
+  <si>
+    <t>3.54</t>
+  </si>
+  <si>
+    <t>PE008108001H</t>
+  </si>
+  <si>
+    <t>SERVICIOS DIGITALES E &amp; R E.I.</t>
+  </si>
+  <si>
+    <t>3.16</t>
+  </si>
+  <si>
+    <t>PE008237001H</t>
+  </si>
+  <si>
+    <t>TGESTIONA SERVICIOS GLOBALES S</t>
+  </si>
+  <si>
+    <t>2.06</t>
+  </si>
+  <si>
+    <t>PE004853001H</t>
+  </si>
+  <si>
+    <t>E LAU SI EIRL</t>
+  </si>
+  <si>
+    <t>1.89</t>
+  </si>
+  <si>
+    <t>PE008036001H</t>
+  </si>
+  <si>
+    <t>SERVICIOS ELECTRONICOS SERVINO</t>
+  </si>
+  <si>
+    <t>1.61</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>PE001016001H</t>
+  </si>
+  <si>
+    <t>SERV.TEC.</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>PE008198001H</t>
+  </si>
+  <si>
+    <t>CORPORACION EFAMEINSA E INGENI</t>
+  </si>
+  <si>
+    <t>1.42</t>
+  </si>
+  <si>
+    <t>PE008171001H</t>
+  </si>
+  <si>
+    <t>TELECOMUNICACIONES STUDIO WEB</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>PE007297001H</t>
+  </si>
+  <si>
+    <t>One time_SVC</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>-0.02</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>PY001043003H</t>
+  </si>
+  <si>
+    <t>ENVING S.A.</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>PE008439001H</t>
+  </si>
+  <si>
+    <t>SEAL TELECOM COMERCIO E SERVIC</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>UY000851005H</t>
+  </si>
+  <si>
+    <t>INGENIERO TUGENTMAN</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>PE005274001H</t>
+  </si>
+  <si>
+    <t>CORPORACION PERUANA DE SERVICI</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>PE003269001H</t>
+  </si>
+  <si>
+    <t>MELGISC ELECTRONICS EIRL</t>
+  </si>
+  <si>
+    <t>PY001035002H</t>
+  </si>
+  <si>
+    <t>MIGUEL MAKOTO NISHIOEDA TSUKUD</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>PE008030001H</t>
+  </si>
+  <si>
+    <t>T &amp; C ELECTRONIC'S E.I.R.L.</t>
+  </si>
+  <si>
+    <t>PY001168001H</t>
+  </si>
+  <si>
+    <t>RIGSTAR S.A.</t>
+  </si>
+  <si>
+    <t>95.61</t>
+  </si>
+  <si>
+    <t>PE000001006H</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS PERU S.A.</t>
+  </si>
+  <si>
+    <t>82.56</t>
+  </si>
+  <si>
+    <t>PE005206001H</t>
+  </si>
+  <si>
+    <t>COMERCIAL IMPORTADORA J. MORA</t>
+  </si>
+  <si>
+    <t>18.71</t>
+  </si>
+  <si>
+    <t>-1.24</t>
+  </si>
+  <si>
+    <t>PE008239001H</t>
+  </si>
+  <si>
+    <t>DELEXPORT E.I.R.L.</t>
+  </si>
+  <si>
+    <t>9.39</t>
+  </si>
+  <si>
+    <t>PE000759001H</t>
+  </si>
+  <si>
+    <t>DERRAMA MAGISTERIAL</t>
+  </si>
+  <si>
+    <t>9.02</t>
+  </si>
+  <si>
+    <t>7.31</t>
+  </si>
+  <si>
+    <t>PE008220001H</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES MONTERO E.I.R.L.</t>
+  </si>
+  <si>
+    <t>8.19</t>
+  </si>
+  <si>
+    <t>PE008423001H</t>
+  </si>
+  <si>
+    <t>SUMINISTROS E INVERSIONES DEL</t>
+  </si>
+  <si>
+    <t>4.41</t>
+  </si>
+  <si>
+    <t>PE000690001H</t>
+  </si>
+  <si>
+    <t>CENSEL E.I.R.L.</t>
+  </si>
+  <si>
+    <t>1.63</t>
+  </si>
+  <si>
+    <t>PE008125001H</t>
+  </si>
+  <si>
+    <t>TORALVA FLORES JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>PE008131001H</t>
+  </si>
+  <si>
+    <t>COLD MACHINES S.A.C</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>PE001009001H</t>
+  </si>
+  <si>
+    <t>ELECTRONICA A Y C EIRL</t>
+  </si>
+  <si>
+    <t>PE008217001H</t>
+  </si>
+  <si>
+    <t>OK HOUSE E.I.R.L.</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>PE007675002H</t>
+  </si>
+  <si>
+    <t>VIDAL GONZAGA CARLOS ENRIQUE</t>
+  </si>
+  <si>
+    <t>PE008468001H</t>
+  </si>
+  <si>
+    <t>SERVICIO TECNICO MARTIN VILLAR</t>
+  </si>
+  <si>
+    <t>PE008121001H</t>
+  </si>
+  <si>
+    <t>SOLUCIONES MULTITECNICAS S.A.C</t>
+  </si>
+  <si>
+    <t>PE008117001H</t>
+  </si>
+  <si>
+    <t>V &amp; S SERVICIOS ELECTRONICOS E</t>
+  </si>
+  <si>
+    <t>PE008053001H</t>
+  </si>
+  <si>
+    <t>XPERTOS SERVICIOS GENERALES S.</t>
   </si>
   <si>
     <t>0.03</t>
   </si>
   <si>
-    <t>3.40</t>
-  </si>
-  <si>
-    <t>-2.61</t>
-  </si>
-  <si>
-    <t>-1.67</t>
-  </si>
-  <si>
-    <t>86.92</t>
-  </si>
-  <si>
-    <t>77.32</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>PE008153001H</t>
-  </si>
-  <si>
-    <t>DACER SOCIEDAD ANONIMA CERRADA</t>
-  </si>
-  <si>
-    <t>379.82</t>
-  </si>
-  <si>
-    <t>PE001507001H</t>
-  </si>
-  <si>
-    <t>IREDI INTERNATIONAL S.R.L</t>
-  </si>
-  <si>
-    <t>377.04</t>
-  </si>
-  <si>
-    <t>PA000001010H</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS PANAMA S.A.</t>
-  </si>
-  <si>
-    <t>347.51</t>
-  </si>
-  <si>
-    <t>PE003288001H</t>
-  </si>
-  <si>
-    <t>PKC TECHNOLOGY S.R.L.</t>
-  </si>
-  <si>
-    <t>335.08</t>
-  </si>
-  <si>
-    <t>-4.42</t>
-  </si>
-  <si>
-    <t>PE008291001H</t>
-  </si>
-  <si>
-    <t>SERFAC S.A.C.</t>
-  </si>
-  <si>
-    <t>291.71</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>PE000854001H</t>
-  </si>
-  <si>
-    <t>SUCESION JUAN PINTO RUIZ</t>
-  </si>
-  <si>
-    <t>279.31</t>
-  </si>
-  <si>
-    <t>PE000853001H</t>
-  </si>
-  <si>
-    <t>JUAN PABLO MORI E.I.R.L.</t>
-  </si>
-  <si>
-    <t>259.18</t>
-  </si>
-  <si>
-    <t>PE007607001H</t>
-  </si>
-  <si>
-    <t>INGENIEROS FRIOTEMP S.A.C.</t>
-  </si>
-  <si>
-    <t>247.86</t>
-  </si>
-  <si>
-    <t>PE008441001H</t>
-  </si>
-  <si>
-    <t>RICOH DEL PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>232.86</t>
-  </si>
-  <si>
-    <t>PE007714001H</t>
-  </si>
-  <si>
-    <t>COINREFRI AIR S.A.C.</t>
-  </si>
-  <si>
-    <t>216.11</t>
-  </si>
-  <si>
-    <t>48.12</t>
-  </si>
-  <si>
-    <t>UY000858004H</t>
-  </si>
-  <si>
-    <t>JOACAMAR</t>
-  </si>
-  <si>
-    <t>193.42</t>
-  </si>
-  <si>
-    <t>PY001162002H</t>
-  </si>
-  <si>
-    <t>CENTRONIC S.A.</t>
-  </si>
-  <si>
-    <t>189.77</t>
-  </si>
-  <si>
-    <t>PE008312001H</t>
-  </si>
-  <si>
-    <t>TIENDAS CHANCAFE S.A.C.</t>
-  </si>
-  <si>
-    <t>171.96</t>
-  </si>
-  <si>
-    <t>-2.95</t>
-  </si>
-  <si>
-    <t>PE004725001H</t>
-  </si>
-  <si>
-    <t>NEXSYS DEL PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>170.75</t>
-  </si>
-  <si>
-    <t>-34.79</t>
-  </si>
-  <si>
-    <t>-26.95</t>
-  </si>
-  <si>
-    <t>PE008017001H</t>
-  </si>
-  <si>
-    <t>CHANCAFE ORIENTE S.A.C.</t>
-  </si>
-  <si>
-    <t>160.32</t>
-  </si>
-  <si>
-    <t>-2.27</t>
-  </si>
-  <si>
-    <t>PE004373001H</t>
-  </si>
-  <si>
-    <t>PROTERM PERU S..AC.</t>
-  </si>
-  <si>
-    <t>143.98</t>
-  </si>
-  <si>
-    <t>CO000002006H</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS COLOMBIA LTDA</t>
-  </si>
-  <si>
-    <t>140.96</t>
-  </si>
-  <si>
-    <t>PE008165001H</t>
-  </si>
-  <si>
-    <t>TODOCLIMA PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>123.77</t>
-  </si>
-  <si>
-    <t>PE008064001H</t>
-  </si>
-  <si>
-    <t>MEGA SHOP FRIO SOC. COM. RESPO</t>
-  </si>
-  <si>
-    <t>110.48</t>
-  </si>
-  <si>
-    <t>19.00</t>
-  </si>
-  <si>
-    <t>PE008139001H</t>
-  </si>
-  <si>
-    <t>GREENCORP PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>97.50</t>
-  </si>
-  <si>
-    <t>PE008020001H</t>
-  </si>
-  <si>
-    <t>HIPERMERCADOS TOTTUS ORIENTE S</t>
-  </si>
-  <si>
-    <t>90.36</t>
-  </si>
-  <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>PE000777001H</t>
-  </si>
-  <si>
-    <t>ELECTRONICA NORTE S.R.LTDA</t>
-  </si>
-  <si>
-    <t>33.87</t>
-  </si>
-  <si>
-    <t>PE003268001H</t>
-  </si>
-  <si>
-    <t>SERVICIOS ELECTRONICOS LA RECO</t>
-  </si>
-  <si>
-    <t>31.51</t>
-  </si>
-  <si>
-    <t>-1.53</t>
-  </si>
-  <si>
-    <t>PY001038002H</t>
-  </si>
-  <si>
-    <t>SERVIPHIL S.R.L</t>
-  </si>
-  <si>
-    <t>30.23</t>
-  </si>
-  <si>
-    <t>PE001020001H</t>
-  </si>
-  <si>
-    <t>TECNICAV S</t>
-  </si>
-  <si>
-    <t>30.12</t>
-  </si>
-  <si>
-    <t>PE008083001H</t>
-  </si>
-  <si>
-    <t>CLIMA TECNICA PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>27.58</t>
-  </si>
-  <si>
-    <t>PE008141001H</t>
-  </si>
-  <si>
-    <t>ANIXTER PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>26.14</t>
-  </si>
-  <si>
-    <t>UY000836002H</t>
-  </si>
-  <si>
-    <t>LAVOMAT</t>
-  </si>
-  <si>
-    <t>25.44</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>PE006831001H</t>
-  </si>
-  <si>
-    <t>FORCE SERVICE S.R.L.</t>
-  </si>
-  <si>
-    <t>23.82</t>
-  </si>
-  <si>
-    <t>PE005273001H</t>
-  </si>
-  <si>
-    <t>CESER EIRL</t>
-  </si>
-  <si>
-    <t>22.36</t>
-  </si>
-  <si>
-    <t>1.39</t>
-  </si>
-  <si>
-    <t>UY000853002H</t>
-  </si>
-  <si>
-    <t>Odalmar S.A.</t>
-  </si>
-  <si>
-    <t>20.67</t>
-  </si>
-  <si>
-    <t>12.97</t>
-  </si>
-  <si>
-    <t>PE006934001H</t>
-  </si>
-  <si>
-    <t>PROMOTICK S.A.C.</t>
-  </si>
-  <si>
-    <t>19.79</t>
-  </si>
-  <si>
-    <t>18.43</t>
-  </si>
-  <si>
-    <t>-0.30</t>
-  </si>
-  <si>
-    <t>-2.60</t>
-  </si>
-  <si>
-    <t>PE008455001H</t>
-  </si>
-  <si>
-    <t>REWARDS PERU S.A.C.</t>
-  </si>
-  <si>
-    <t>19.72</t>
-  </si>
-  <si>
-    <t>BO000662002H</t>
-  </si>
-  <si>
-    <t>Censel</t>
-  </si>
-  <si>
-    <t>19.24</t>
-  </si>
-  <si>
-    <t>PE008022001H</t>
-  </si>
-  <si>
-    <t>SERTEPI E.I.R.L.</t>
-  </si>
-  <si>
-    <t>17.46</t>
-  </si>
-  <si>
-    <t>PE008105001H</t>
-  </si>
-  <si>
-    <t>LATINAMENITIES S.A.C.</t>
-  </si>
-  <si>
-    <t>17.30</t>
-  </si>
-  <si>
-    <t>PE004102001H</t>
-  </si>
-  <si>
-    <t>MI NEGOCIO EMPRESA INDIVIDUAL</t>
-  </si>
-  <si>
-    <t>17.27</t>
-  </si>
-  <si>
-    <t>-6.10</t>
-  </si>
-  <si>
-    <t>-2.75</t>
-  </si>
-  <si>
-    <t>-5.90</t>
-  </si>
-  <si>
-    <t>PE007296001H</t>
-  </si>
-  <si>
-    <t>One time_Employee</t>
-  </si>
-  <si>
-    <t>16.85</t>
-  </si>
-  <si>
-    <t>1.04</t>
-  </si>
-  <si>
-    <t>4.95</t>
-  </si>
-  <si>
-    <t>PE004799001H</t>
-  </si>
-  <si>
-    <t>SERVINORTE EIRL</t>
-  </si>
-  <si>
-    <t>16.19</t>
-  </si>
-  <si>
-    <t>PE004800001H</t>
-  </si>
-  <si>
-    <t>MULTIREPARACIONES DIGITALES IC</t>
-  </si>
-  <si>
-    <t>15.11</t>
-  </si>
-  <si>
-    <t>-0.27</t>
-  </si>
-  <si>
-    <t>PE001399001H</t>
-  </si>
-  <si>
-    <t>ASPERSUD</t>
-  </si>
-  <si>
-    <t>13.71</t>
-  </si>
-  <si>
-    <t>8.83</t>
-  </si>
-  <si>
-    <t>PE008175001H</t>
-  </si>
-  <si>
-    <t>HAROLD MULTISERVIS EIRL</t>
-  </si>
-  <si>
-    <t>13.46</t>
-  </si>
-  <si>
-    <t>PE008108001H</t>
-  </si>
-  <si>
-    <t>SERVICIOS DIGITALES E &amp; R E.I.</t>
-  </si>
-  <si>
-    <t>11.99</t>
-  </si>
-  <si>
-    <t>PE008237001H</t>
-  </si>
-  <si>
-    <t>TGESTIONA SERVICIOS GLOBALES S</t>
-  </si>
-  <si>
-    <t>7.83</t>
-  </si>
-  <si>
-    <t>PE004853001H</t>
-  </si>
-  <si>
-    <t>E LAU SI EIRL</t>
-  </si>
-  <si>
-    <t>7.17</t>
-  </si>
-  <si>
-    <t>PE008036001H</t>
-  </si>
-  <si>
-    <t>SERVICIOS ELECTRONICOS SERVINO</t>
-  </si>
-  <si>
-    <t>6.11</t>
-  </si>
-  <si>
-    <t>1.26</t>
-  </si>
-  <si>
-    <t>PE001016001H</t>
-  </si>
-  <si>
-    <t>SERV.TEC.</t>
-  </si>
-  <si>
-    <t>5.64</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>PE008198001H</t>
-  </si>
-  <si>
-    <t>CORPORACION EFAMEINSA E INGENI</t>
-  </si>
-  <si>
-    <t>5.39</t>
-  </si>
-  <si>
-    <t>PE008171001H</t>
-  </si>
-  <si>
-    <t>TELECOMUNICACIONES STUDIO WEB</t>
-  </si>
-  <si>
-    <t>2.97</t>
-  </si>
-  <si>
-    <t>PE007297001H</t>
-  </si>
-  <si>
-    <t>One time_SVC</t>
-  </si>
-  <si>
-    <t>2.46</t>
-  </si>
-  <si>
-    <t>-0.09</t>
-  </si>
-  <si>
-    <t>0.19</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>PY001043003H</t>
-  </si>
-  <si>
-    <t>ENVING S.A.</t>
-  </si>
-  <si>
-    <t>2.36</t>
-  </si>
-  <si>
-    <t>PE008439001H</t>
-  </si>
-  <si>
-    <t>SEAL TELECOM COMERCIO E SERVIC</t>
-  </si>
-  <si>
-    <t>2.33</t>
-  </si>
-  <si>
-    <t>UY000851005H</t>
-  </si>
-  <si>
-    <t>INGENIERO TUGENTMAN</t>
-  </si>
-  <si>
-    <t>1.13</t>
-  </si>
-  <si>
-    <t>PE005274001H</t>
-  </si>
-  <si>
-    <t>CORPORACION PERUANA DE SERVICI</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>PE003269001H</t>
-  </si>
-  <si>
-    <t>MELGISC ELECTRONICS EIRL</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>PY001035002H</t>
-  </si>
-  <si>
-    <t>MIGUEL MAKOTO NISHIOEDA TSUKUD</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>PE008030001H</t>
-  </si>
-  <si>
-    <t>T &amp; C ELECTRONIC'S E.I.R.L.</t>
-  </si>
-  <si>
-    <t>PY001168001H</t>
-  </si>
-  <si>
-    <t>RIGSTAR S.A.</t>
-  </si>
-  <si>
-    <t>363.33</t>
-  </si>
-  <si>
-    <t>PE000001006H</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS PERU S.A.</t>
-  </si>
-  <si>
-    <t>313.74</t>
-  </si>
-  <si>
-    <t>PE005206001H</t>
-  </si>
-  <si>
-    <t>COMERCIAL IMPORTADORA J. MORA</t>
-  </si>
-  <si>
-    <t>71.12</t>
-  </si>
-  <si>
-    <t>-4.70</t>
-  </si>
-  <si>
-    <t>PE008239001H</t>
-  </si>
-  <si>
-    <t>DELEXPORT E.I.R.L.</t>
-  </si>
-  <si>
-    <t>35.68</t>
-  </si>
-  <si>
-    <t>PE000759001H</t>
-  </si>
-  <si>
-    <t>DERRAMA MAGISTERIAL</t>
-  </si>
-  <si>
-    <t>34.27</t>
-  </si>
-  <si>
-    <t>27.79</t>
-  </si>
-  <si>
-    <t>PE008220001H</t>
-  </si>
-  <si>
-    <t>IMPORTACIONES MONTERO E.I.R.L.</t>
-  </si>
-  <si>
-    <t>31.12</t>
-  </si>
-  <si>
-    <t>PE008423001H</t>
-  </si>
-  <si>
-    <t>SUMINISTROS E INVERSIONES DEL</t>
-  </si>
-  <si>
-    <t>16.77</t>
-  </si>
-  <si>
-    <t>PE000690001H</t>
-  </si>
-  <si>
-    <t>CENSEL E.I.R.L.</t>
-  </si>
-  <si>
-    <t>6.18</t>
-  </si>
-  <si>
-    <t>PE008125001H</t>
-  </si>
-  <si>
-    <t>TORALVA FLORES JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>2.92</t>
-  </si>
-  <si>
-    <t>PE008131001H</t>
-  </si>
-  <si>
-    <t>COLD MACHINES S.A.C</t>
-  </si>
-  <si>
-    <t>1.71</t>
-  </si>
-  <si>
-    <t>PE001009001H</t>
-  </si>
-  <si>
-    <t>ELECTRONICA A Y C EIRL</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>PE008217001H</t>
-  </si>
-  <si>
-    <t>OK HOUSE E.I.R.L.</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>PE007675002H</t>
-  </si>
-  <si>
-    <t>VIDAL GONZAGA CARLOS ENRIQUE</t>
-  </si>
-  <si>
-    <t>PE008468001H</t>
-  </si>
-  <si>
-    <t>SERVICIO TECNICO MARTIN VILLAR</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>PE008121001H</t>
-  </si>
-  <si>
-    <t>SOLUCIONES MULTITECNICAS S.A.C</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>PE008117001H</t>
-  </si>
-  <si>
-    <t>V &amp; S SERVICIOS ELECTRONICOS E</t>
-  </si>
-  <si>
-    <t>PE008053001H</t>
-  </si>
-  <si>
-    <t>XPERTOS SERVICIOS GENERALES S.</t>
-  </si>
-  <si>
-    <t>0.12</t>
-  </si>
-  <si>
     <t>PE001097001H</t>
   </si>
   <si>
@@ -1529,7 +1499,7 @@
     <t>TAI LOY S.A.</t>
   </si>
   <si>
-    <t>-3.76</t>
+    <t>-0.99</t>
   </si>
   <si>
     <t>AR000001039H</t>
@@ -1538,7 +1508,7 @@
     <t>LGEAR</t>
   </si>
   <si>
-    <t>21.39</t>
+    <t>5.63</t>
   </si>
 </sst>
 </file>
@@ -2463,46 +2433,46 @@
         <v>21</v>
       </c>
       <c r="P6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6" t="s">
         <v>73</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" t="s">
+        <v>21</v>
+      </c>
+      <c r="T6" t="s">
+        <v>21</v>
+      </c>
+      <c r="U6" t="s">
+        <v>21</v>
+      </c>
+      <c r="V6" t="s">
+        <v>21</v>
+      </c>
+      <c r="W6" t="s">
+        <v>21</v>
+      </c>
+      <c r="X6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC6" t="s">
         <v>74</v>
-      </c>
-      <c r="R6" t="s">
-        <v>21</v>
-      </c>
-      <c r="S6" t="s">
-        <v>21</v>
-      </c>
-      <c r="T6" t="s">
-        <v>21</v>
-      </c>
-      <c r="U6" t="s">
-        <v>21</v>
-      </c>
-      <c r="V6" t="s">
-        <v>21</v>
-      </c>
-      <c r="W6" t="s">
-        <v>21</v>
-      </c>
-      <c r="X6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>75</v>
       </c>
       <c r="AD6" t="s">
         <v>21</v>
@@ -2525,88 +2495,88 @@
     </row>
     <row r="7" spans="1:35">
       <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
         <v>76</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>77</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>78</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="s">
         <v>79</v>
       </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>80</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" t="s">
+        <v>21</v>
+      </c>
+      <c r="U7" t="s">
+        <v>21</v>
+      </c>
+      <c r="V7" t="s">
+        <v>21</v>
+      </c>
+      <c r="W7" t="s">
+        <v>21</v>
+      </c>
+      <c r="X7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB7" t="s">
         <v>81</v>
-      </c>
-      <c r="S7" t="s">
-        <v>21</v>
-      </c>
-      <c r="T7" t="s">
-        <v>21</v>
-      </c>
-      <c r="U7" t="s">
-        <v>21</v>
-      </c>
-      <c r="V7" t="s">
-        <v>21</v>
-      </c>
-      <c r="W7" t="s">
-        <v>21</v>
-      </c>
-      <c r="X7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>82</v>
       </c>
       <c r="AC7" t="s">
         <v>21</v>
@@ -2632,94 +2602,94 @@
     </row>
     <row r="8" spans="1:35">
       <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
         <v>83</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
         <v>84</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>85</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" t="s">
         <v>86</v>
       </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>87</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>88</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
+        <v>21</v>
+      </c>
+      <c r="T8" t="s">
         <v>89</v>
       </c>
-      <c r="S8" t="s">
-        <v>21</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
+        <v>21</v>
+      </c>
+      <c r="V8" t="s">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s">
         <v>90</v>
       </c>
-      <c r="U8" t="s">
-        <v>21</v>
-      </c>
-      <c r="V8" t="s">
-        <v>21</v>
-      </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s">
         <v>91</v>
       </c>
-      <c r="X8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>92</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>93</v>
       </c>
       <c r="AE8" t="s">
         <v>21</v>
@@ -2739,91 +2709,91 @@
     </row>
     <row r="9" spans="1:35">
       <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
         <v>94</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>95</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>96</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>97</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" t="s">
         <v>98</v>
       </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" t="s">
-        <v>21</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>99</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" t="s">
+        <v>21</v>
+      </c>
+      <c r="T9" t="s">
+        <v>21</v>
+      </c>
+      <c r="U9" t="s">
+        <v>21</v>
+      </c>
+      <c r="V9" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9" t="s">
+        <v>21</v>
+      </c>
+      <c r="X9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB9" t="s">
         <v>100</v>
       </c>
-      <c r="R9" t="s">
-        <v>21</v>
-      </c>
-      <c r="S9" t="s">
-        <v>21</v>
-      </c>
-      <c r="T9" t="s">
-        <v>21</v>
-      </c>
-      <c r="U9" t="s">
-        <v>21</v>
-      </c>
-      <c r="V9" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9" t="s">
-        <v>21</v>
-      </c>
-      <c r="X9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>101</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>102</v>
       </c>
       <c r="AD9" t="s">
         <v>21</v>
@@ -2846,19 +2816,19 @@
     </row>
     <row r="10" spans="1:35">
       <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
         <v>103</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
         <v>104</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>105</v>
-      </c>
-      <c r="E10" t="s">
-        <v>106</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -2953,19 +2923,19 @@
     </row>
     <row r="11" spans="1:35">
       <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
         <v>107</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>108</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>110</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -3060,52 +3030,52 @@
     </row>
     <row r="12" spans="1:35">
       <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
         <v>111</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
         <v>112</v>
       </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
         <v>113</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" t="s">
-        <v>17</v>
-      </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" t="s">
-        <v>114</v>
       </c>
       <c r="Q12" t="s">
         <v>21</v>
@@ -3167,16 +3137,16 @@
     </row>
     <row r="13" spans="1:35">
       <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
         <v>115</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
         <v>116</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>117</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
@@ -3274,85 +3244,85 @@
     </row>
     <row r="14" spans="1:35">
       <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
         <v>118</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
         <v>119</v>
       </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>21</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>21</v>
+      </c>
+      <c r="U14" t="s">
+        <v>21</v>
+      </c>
+      <c r="V14" t="s">
+        <v>21</v>
+      </c>
+      <c r="W14" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA14" t="s">
         <v>120</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O14" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" t="s">
-        <v>21</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>21</v>
-      </c>
-      <c r="U14" t="s">
-        <v>21</v>
-      </c>
-      <c r="V14" t="s">
-        <v>21</v>
-      </c>
-      <c r="W14" t="s">
-        <v>21</v>
-      </c>
-      <c r="X14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>121</v>
       </c>
       <c r="AB14" t="s">
         <v>21</v>
@@ -3381,19 +3351,19 @@
     </row>
     <row r="15" spans="1:35">
       <c r="A15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" t="s">
         <v>122</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
         <v>123</v>
       </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>124</v>
-      </c>
-      <c r="E15" t="s">
-        <v>125</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -3488,67 +3458,67 @@
     </row>
     <row r="16" spans="1:35">
       <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
         <v>126</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
         <v>127</v>
       </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
         <v>128</v>
       </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>17</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>129</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>130</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>131</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>132</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>133</v>
-      </c>
-      <c r="U16" t="s">
-        <v>134</v>
       </c>
       <c r="V16" t="s">
         <v>21</v>
@@ -3595,64 +3565,64 @@
     </row>
     <row r="17" spans="1:35">
       <c r="A17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" t="s">
         <v>135</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
         <v>136</v>
       </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>137</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" t="s">
+        <v>17</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
         <v>138</v>
       </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" t="s">
-        <v>17</v>
-      </c>
-      <c r="O17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>139</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>140</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>141</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>142</v>
-      </c>
-      <c r="T17" t="s">
-        <v>143</v>
       </c>
       <c r="U17" t="s">
         <v>21</v>
@@ -3702,52 +3672,52 @@
     </row>
     <row r="18" spans="1:35">
       <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" t="s">
         <v>144</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
         <v>145</v>
       </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+      <c r="O18" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" t="s">
         <v>146</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" t="s">
-        <v>17</v>
-      </c>
-      <c r="O18" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18" t="s">
-        <v>147</v>
       </c>
       <c r="Q18" t="s">
         <v>21</v>
@@ -3809,88 +3779,88 @@
     </row>
     <row r="19" spans="1:35">
       <c r="A19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" t="s">
         <v>148</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
         <v>149</v>
       </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>150</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>21</v>
+      </c>
+      <c r="U19" t="s">
+        <v>21</v>
+      </c>
+      <c r="V19" t="s">
+        <v>21</v>
+      </c>
+      <c r="W19" t="s">
+        <v>21</v>
+      </c>
+      <c r="X19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" t="s">
         <v>151</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" t="s">
-        <v>17</v>
-      </c>
-      <c r="O19" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" t="s">
-        <v>21</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>21</v>
-      </c>
-      <c r="U19" t="s">
-        <v>21</v>
-      </c>
-      <c r="V19" t="s">
-        <v>21</v>
-      </c>
-      <c r="W19" t="s">
-        <v>21</v>
-      </c>
-      <c r="X19" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>152</v>
       </c>
       <c r="AC19" t="s">
         <v>21</v>
@@ -3916,19 +3886,19 @@
     </row>
     <row r="20" spans="1:35">
       <c r="A20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" t="s">
         <v>153</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
         <v>154</v>
       </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>155</v>
-      </c>
-      <c r="E20" t="s">
-        <v>156</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -4023,61 +3993,61 @@
     </row>
     <row r="21" spans="1:35">
       <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" t="s">
         <v>157</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
         <v>158</v>
       </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>159</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
         <v>160</v>
       </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>17</v>
-      </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>161</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>162</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>163</v>
-      </c>
-      <c r="S21" t="s">
-        <v>164</v>
       </c>
       <c r="T21" t="s">
         <v>21</v>
@@ -4130,88 +4100,88 @@
     </row>
     <row r="22" spans="1:35">
       <c r="A22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" t="s">
         <v>165</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
         <v>166</v>
       </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
         <v>167</v>
       </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>168</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s">
         <v>169</v>
       </c>
-      <c r="H22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
         <v>170</v>
       </c>
-      <c r="J22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" t="s">
-        <v>17</v>
-      </c>
-      <c r="O22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s">
+        <v>21</v>
+      </c>
+      <c r="U22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V22" t="s">
+        <v>21</v>
+      </c>
+      <c r="W22" t="s">
         <v>171</v>
       </c>
-      <c r="Q22" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" t="s">
-        <v>21</v>
-      </c>
-      <c r="S22" t="s">
-        <v>21</v>
-      </c>
-      <c r="T22" t="s">
-        <v>21</v>
-      </c>
-      <c r="U22" t="s">
-        <v>21</v>
-      </c>
-      <c r="V22" t="s">
-        <v>21</v>
-      </c>
-      <c r="W22" t="s">
+      <c r="X22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s">
         <v>172</v>
-      </c>
-      <c r="X22" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>173</v>
       </c>
       <c r="AC22" t="s">
         <v>21</v>
@@ -4237,55 +4207,55 @@
     </row>
     <row r="23" spans="1:35">
       <c r="A23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" t="s">
         <v>174</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
         <v>175</v>
       </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>176</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
         <v>177</v>
       </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" t="s">
-        <v>17</v>
-      </c>
-      <c r="O23" t="s">
-        <v>21</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>178</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>179</v>
       </c>
       <c r="R23" t="s">
         <v>21</v>
@@ -4344,94 +4314,94 @@
     </row>
     <row r="24" spans="1:35">
       <c r="A24" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" t="s">
         <v>180</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
         <v>181</v>
       </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>182</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>183</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
         <v>184</v>
       </c>
-      <c r="G24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" t="s">
-        <v>17</v>
-      </c>
-      <c r="O24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
         <v>185</v>
       </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s">
         <v>186</v>
       </c>
-      <c r="S24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
+        <v>184</v>
+      </c>
+      <c r="V24" t="s">
+        <v>21</v>
+      </c>
+      <c r="W24" t="s">
+        <v>21</v>
+      </c>
+      <c r="X24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC24" t="s">
         <v>187</v>
       </c>
-      <c r="U24" t="s">
-        <v>185</v>
-      </c>
-      <c r="V24" t="s">
-        <v>21</v>
-      </c>
-      <c r="W24" t="s">
-        <v>21</v>
-      </c>
-      <c r="X24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>188</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>189</v>
       </c>
       <c r="AE24" t="s">
         <v>21</v>
@@ -4451,58 +4421,58 @@
     </row>
     <row r="25" spans="1:35">
       <c r="A25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" t="s">
         <v>190</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
         <v>191</v>
       </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
         <v>192</v>
       </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" t="s">
-        <v>17</v>
-      </c>
-      <c r="O25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>193</v>
-      </c>
-      <c r="R25" t="s">
-        <v>194</v>
       </c>
       <c r="S25" t="s">
         <v>21</v>
@@ -4558,58 +4528,58 @@
     </row>
     <row r="26" spans="1:35">
       <c r="A26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" t="s">
         <v>195</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
         <v>196</v>
       </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>197</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>198</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" t="s">
+        <v>17</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
         <v>199</v>
       </c>
-      <c r="G26" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" t="s">
-        <v>17</v>
-      </c>
-      <c r="O26" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
         <v>200</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" t="s">
-        <v>201</v>
       </c>
       <c r="S26" t="s">
         <v>21</v>
@@ -4665,17 +4635,17 @@
     </row>
     <row r="27" spans="1:35">
       <c r="A27" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" t="s">
         <v>202</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
         <v>203</v>
       </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" t="s">
-        <v>204</v>
-      </c>
       <c r="E27" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4659,7 @@
         <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="J27" t="s">
         <v>21</v>
@@ -4772,16 +4742,16 @@
     </row>
     <row r="28" spans="1:35">
       <c r="A28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
         <v>206</v>
-      </c>
-      <c r="B28" t="s">
-        <v>207</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="s">
-        <v>208</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
@@ -4879,53 +4849,53 @@
     </row>
     <row r="29" spans="1:35">
       <c r="A29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
         <v>209</v>
       </c>
-      <c r="B29" t="s">
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
         <v>210</v>
       </c>
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" t="s">
-        <v>211</v>
-      </c>
-      <c r="E29" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" t="s">
-        <v>17</v>
-      </c>
-      <c r="O29" t="s">
-        <v>21</v>
-      </c>
-      <c r="P29" t="s">
-        <v>212</v>
-      </c>
       <c r="Q29" t="s">
         <v>21</v>
       </c>
@@ -4933,7 +4903,7 @@
         <v>21</v>
       </c>
       <c r="S29" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="T29" t="s">
         <v>21</v>
@@ -4986,19 +4956,19 @@
     </row>
     <row r="30" spans="1:35">
       <c r="A30" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
         <v>213</v>
       </c>
-      <c r="B30" t="s">
+      <c r="E30" t="s">
         <v>214</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E30" t="s">
-        <v>216</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -5093,16 +5063,16 @@
     </row>
     <row r="31" spans="1:35">
       <c r="A31" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
         <v>217</v>
-      </c>
-      <c r="B31" t="s">
-        <v>218</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s">
-        <v>219</v>
       </c>
       <c r="E31" t="s">
         <v>21</v>
@@ -5200,16 +5170,16 @@
     </row>
     <row r="32" spans="1:35">
       <c r="A32" t="s">
+        <v>218</v>
+      </c>
+      <c r="B32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
         <v>220</v>
-      </c>
-      <c r="B32" t="s">
-        <v>221</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" t="s">
-        <v>222</v>
       </c>
       <c r="E32" t="s">
         <v>21</v>
@@ -5307,16 +5277,16 @@
     </row>
     <row r="33" spans="1:35">
       <c r="A33" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
         <v>223</v>
-      </c>
-      <c r="B33" t="s">
-        <v>224</v>
-      </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s">
-        <v>225</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
@@ -5414,16 +5384,16 @@
     </row>
     <row r="34" spans="1:35">
       <c r="A34" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
         <v>226</v>
-      </c>
-      <c r="B34" t="s">
-        <v>227</v>
-      </c>
-      <c r="C34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" t="s">
-        <v>228</v>
       </c>
       <c r="E34" t="s">
         <v>21</v>
@@ -5521,20 +5491,20 @@
     </row>
     <row r="35" spans="1:35">
       <c r="A35" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
         <v>229</v>
       </c>
-      <c r="B35" t="s">
+      <c r="E35" t="s">
         <v>230</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s">
-        <v>231</v>
-      </c>
-      <c r="E35" t="s">
-        <v>232</v>
-      </c>
       <c r="F35" t="s">
         <v>21</v>
       </c>
@@ -5569,7 +5539,7 @@
         <v>21</v>
       </c>
       <c r="Q35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R35" t="s">
         <v>21</v>
@@ -5628,16 +5598,16 @@
     </row>
     <row r="36" spans="1:35">
       <c r="A36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
         <v>233</v>
-      </c>
-      <c r="B36" t="s">
-        <v>234</v>
-      </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" t="s">
-        <v>235</v>
       </c>
       <c r="E36" t="s">
         <v>21</v>
@@ -5735,19 +5705,19 @@
     </row>
     <row r="37" spans="1:35">
       <c r="A37" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
         <v>236</v>
       </c>
-      <c r="B37" t="s">
+      <c r="E37" t="s">
         <v>237</v>
-      </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="s">
-        <v>238</v>
-      </c>
-      <c r="E37" t="s">
-        <v>239</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -5842,94 +5812,94 @@
     </row>
     <row r="38" spans="1:35">
       <c r="A38" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="E38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>242</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" t="s">
         <v>243</v>
       </c>
-      <c r="F38" t="s">
+      <c r="L38" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="s">
         <v>244</v>
       </c>
-      <c r="G38" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="R38" t="s">
+        <v>80</v>
+      </c>
+      <c r="S38" t="s">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s">
+        <v>21</v>
+      </c>
+      <c r="U38" t="s">
+        <v>21</v>
+      </c>
+      <c r="V38" t="s">
+        <v>21</v>
+      </c>
+      <c r="W38" t="s">
+        <v>21</v>
+      </c>
+      <c r="X38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s">
         <v>245</v>
       </c>
-      <c r="L38" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" t="s">
-        <v>17</v>
-      </c>
-      <c r="O38" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38" t="s">
+      <c r="AB38" t="s">
         <v>246</v>
       </c>
-      <c r="R38" t="s">
+      <c r="AC38" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s">
         <v>247</v>
-      </c>
-      <c r="S38" t="s">
-        <v>21</v>
-      </c>
-      <c r="T38" t="s">
-        <v>21</v>
-      </c>
-      <c r="U38" t="s">
-        <v>21</v>
-      </c>
-      <c r="V38" t="s">
-        <v>21</v>
-      </c>
-      <c r="W38" t="s">
-        <v>21</v>
-      </c>
-      <c r="X38" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>248</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>249</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>250</v>
       </c>
       <c r="AE38" t="s">
         <v>21</v>
@@ -5949,16 +5919,16 @@
     </row>
     <row r="39" spans="1:35">
       <c r="A39" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B39" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
@@ -6056,16 +6026,16 @@
     </row>
     <row r="40" spans="1:35">
       <c r="A40" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E40" t="s">
         <v>21</v>
@@ -6163,16 +6133,16 @@
     </row>
     <row r="41" spans="1:35">
       <c r="A41" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E41" t="s">
         <v>21</v>
@@ -6270,58 +6240,58 @@
     </row>
     <row r="42" spans="1:35">
       <c r="A42" t="s">
+        <v>257</v>
+      </c>
+      <c r="B42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>259</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" t="s">
+        <v>17</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" t="s">
         <v>260</v>
-      </c>
-      <c r="B42" t="s">
-        <v>261</v>
-      </c>
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" t="s">
-        <v>262</v>
-      </c>
-      <c r="E42" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" t="s">
-        <v>21</v>
-      </c>
-      <c r="H42" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" t="s">
-        <v>21</v>
-      </c>
-      <c r="J42" t="s">
-        <v>21</v>
-      </c>
-      <c r="K42" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" t="s">
-        <v>21</v>
-      </c>
-      <c r="N42" t="s">
-        <v>17</v>
-      </c>
-      <c r="O42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" t="s">
-        <v>263</v>
       </c>
       <c r="S42" t="s">
         <v>21</v>
@@ -6377,22 +6347,22 @@
     </row>
     <row r="43" spans="1:35">
       <c r="A43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B43" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
+        <v>263</v>
+      </c>
+      <c r="E43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" t="s">
         <v>264</v>
-      </c>
-      <c r="B43" t="s">
-        <v>265</v>
-      </c>
-      <c r="C43" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" t="s">
-        <v>266</v>
-      </c>
-      <c r="E43" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" t="s">
-        <v>267</v>
       </c>
       <c r="G43" t="s">
         <v>21</v>
@@ -6484,16 +6454,16 @@
     </row>
     <row r="44" spans="1:35">
       <c r="A44" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B44" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
@@ -6591,16 +6561,16 @@
     </row>
     <row r="45" spans="1:35">
       <c r="A45" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B45" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
@@ -6698,16 +6668,16 @@
     </row>
     <row r="46" spans="1:35">
       <c r="A46" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
@@ -6805,16 +6775,16 @@
     </row>
     <row r="47" spans="1:35">
       <c r="A47" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C47" t="s">
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E47" t="s">
         <v>21</v>
@@ -6912,19 +6882,19 @@
     </row>
     <row r="48" spans="1:35">
       <c r="A48" t="s">
+        <v>277</v>
+      </c>
+      <c r="B48" t="s">
+        <v>278</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" t="s">
+        <v>279</v>
+      </c>
+      <c r="E48" t="s">
         <v>280</v>
-      </c>
-      <c r="B48" t="s">
-        <v>281</v>
-      </c>
-      <c r="C48" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" t="s">
-        <v>282</v>
-      </c>
-      <c r="E48" t="s">
-        <v>283</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -7019,16 +6989,16 @@
     </row>
     <row r="49" spans="1:35">
       <c r="A49" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B49" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C49" t="s">
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E49" t="s">
         <v>21</v>
@@ -7126,16 +7096,16 @@
     </row>
     <row r="50" spans="1:35">
       <c r="A50" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B50" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E50" t="s">
         <v>21</v>
@@ -7233,58 +7203,58 @@
     </row>
     <row r="51" spans="1:35">
       <c r="A51" t="s">
+        <v>287</v>
+      </c>
+      <c r="B51" t="s">
+        <v>288</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
+        <v>289</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" t="s">
+        <v>21</v>
+      </c>
+      <c r="N51" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" t="s">
         <v>290</v>
-      </c>
-      <c r="B51" t="s">
-        <v>291</v>
-      </c>
-      <c r="C51" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" t="s">
-        <v>292</v>
-      </c>
-      <c r="E51" t="s">
-        <v>21</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" t="s">
-        <v>21</v>
-      </c>
-      <c r="H51" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s">
-        <v>21</v>
-      </c>
-      <c r="K51" t="s">
-        <v>21</v>
-      </c>
-      <c r="L51" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" t="s">
-        <v>21</v>
-      </c>
-      <c r="N51" t="s">
-        <v>17</v>
-      </c>
-      <c r="O51" t="s">
-        <v>21</v>
-      </c>
-      <c r="P51" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>21</v>
-      </c>
-      <c r="R51" t="s">
-        <v>293</v>
       </c>
       <c r="S51" t="s">
         <v>21</v>
@@ -7340,61 +7310,61 @@
     </row>
     <row r="52" spans="1:35">
       <c r="A52" t="s">
+        <v>291</v>
+      </c>
+      <c r="B52" t="s">
+        <v>292</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
+        <v>293</v>
+      </c>
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" t="s">
         <v>294</v>
       </c>
-      <c r="B52" t="s">
+      <c r="S52" t="s">
         <v>295</v>
-      </c>
-      <c r="C52" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" t="s">
-        <v>296</v>
-      </c>
-      <c r="E52" t="s">
-        <v>21</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52" t="s">
-        <v>21</v>
-      </c>
-      <c r="H52" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s">
-        <v>21</v>
-      </c>
-      <c r="K52" t="s">
-        <v>21</v>
-      </c>
-      <c r="L52" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" t="s">
-        <v>21</v>
-      </c>
-      <c r="N52" t="s">
-        <v>17</v>
-      </c>
-      <c r="O52" t="s">
-        <v>21</v>
-      </c>
-      <c r="P52" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>21</v>
-      </c>
-      <c r="R52" t="s">
-        <v>297</v>
-      </c>
-      <c r="S52" t="s">
-        <v>298</v>
       </c>
       <c r="T52" t="s">
         <v>21</v>
@@ -7447,52 +7417,52 @@
     </row>
     <row r="53" spans="1:35">
       <c r="A53" t="s">
+        <v>296</v>
+      </c>
+      <c r="B53" t="s">
+        <v>297</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>298</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" t="s">
+        <v>17</v>
+      </c>
+      <c r="O53" t="s">
+        <v>21</v>
+      </c>
+      <c r="P53" t="s">
         <v>299</v>
-      </c>
-      <c r="B53" t="s">
-        <v>300</v>
-      </c>
-      <c r="C53" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" t="s">
-        <v>301</v>
-      </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s">
-        <v>21</v>
-      </c>
-      <c r="K53" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" t="s">
-        <v>21</v>
-      </c>
-      <c r="N53" t="s">
-        <v>17</v>
-      </c>
-      <c r="O53" t="s">
-        <v>21</v>
-      </c>
-      <c r="P53" t="s">
-        <v>302</v>
       </c>
       <c r="Q53" t="s">
         <v>21</v>
@@ -7554,16 +7524,16 @@
     </row>
     <row r="54" spans="1:35">
       <c r="A54" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E54" t="s">
         <v>21</v>
@@ -7661,16 +7631,16 @@
     </row>
     <row r="55" spans="1:35">
       <c r="A55" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B55" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E55" t="s">
         <v>21</v>
@@ -7768,16 +7738,16 @@
     </row>
     <row r="56" spans="1:35">
       <c r="A56" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E56" t="s">
         <v>21</v>
@@ -7875,22 +7845,22 @@
     </row>
     <row r="57" spans="1:35">
       <c r="A57" t="s">
+        <v>309</v>
+      </c>
+      <c r="B57" t="s">
+        <v>310</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>311</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
         <v>312</v>
-      </c>
-      <c r="B57" t="s">
-        <v>313</v>
-      </c>
-      <c r="C57" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" t="s">
-        <v>314</v>
-      </c>
-      <c r="E57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F57" t="s">
-        <v>315</v>
       </c>
       <c r="G57" t="s">
         <v>21</v>
@@ -7982,16 +7952,16 @@
     </row>
     <row r="58" spans="1:35">
       <c r="A58" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B58" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E58" t="s">
         <v>21</v>
@@ -8089,91 +8059,91 @@
     </row>
     <row r="59" spans="1:35">
       <c r="A59" t="s">
+        <v>316</v>
+      </c>
+      <c r="B59" t="s">
+        <v>317</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>318</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" t="s">
+        <v>17</v>
+      </c>
+      <c r="O59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>21</v>
+      </c>
+      <c r="R59" t="s">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s">
         <v>319</v>
-      </c>
-      <c r="B59" t="s">
-        <v>320</v>
-      </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" t="s">
-        <v>321</v>
-      </c>
-      <c r="E59" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59" t="s">
-        <v>21</v>
-      </c>
-      <c r="J59" t="s">
-        <v>21</v>
-      </c>
-      <c r="K59" t="s">
-        <v>21</v>
-      </c>
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" t="s">
-        <v>17</v>
-      </c>
-      <c r="O59" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>21</v>
-      </c>
-      <c r="R59" t="s">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>322</v>
       </c>
       <c r="AD59" t="s">
         <v>21</v>
@@ -8196,16 +8166,16 @@
     </row>
     <row r="60" spans="1:35">
       <c r="A60" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B60" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E60" t="s">
         <v>21</v>
@@ -8303,64 +8273,64 @@
     </row>
     <row r="61" spans="1:35">
       <c r="A61" t="s">
+        <v>323</v>
+      </c>
+      <c r="B61" t="s">
+        <v>324</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>325</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" t="s">
+        <v>21</v>
+      </c>
+      <c r="N61" t="s">
+        <v>17</v>
+      </c>
+      <c r="O61" t="s">
+        <v>21</v>
+      </c>
+      <c r="P61" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>21</v>
+      </c>
+      <c r="R61" t="s">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s">
         <v>326</v>
-      </c>
-      <c r="B61" t="s">
-        <v>327</v>
-      </c>
-      <c r="C61" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" t="s">
-        <v>328</v>
-      </c>
-      <c r="E61" t="s">
-        <v>21</v>
-      </c>
-      <c r="F61" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s">
-        <v>21</v>
-      </c>
-      <c r="K61" t="s">
-        <v>21</v>
-      </c>
-      <c r="L61" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" t="s">
-        <v>17</v>
-      </c>
-      <c r="O61" t="s">
-        <v>21</v>
-      </c>
-      <c r="P61" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>21</v>
-      </c>
-      <c r="R61" t="s">
-        <v>21</v>
-      </c>
-      <c r="S61" t="s">
-        <v>21</v>
-      </c>
-      <c r="T61" t="s">
-        <v>329</v>
       </c>
       <c r="U61" t="s">
         <v>21</v>
@@ -8410,16 +8380,16 @@
     </row>
     <row r="62" spans="1:35">
       <c r="A62" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B62" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E62" t="s">
         <v>21</v>
@@ -8517,16 +8487,16 @@
     </row>
     <row r="63" spans="1:35">
       <c r="A63" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B63" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E63" t="s">
         <v>21</v>
@@ -8624,16 +8594,16 @@
     </row>
     <row r="64" spans="1:35">
       <c r="A64" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B64" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E64" t="s">
         <v>21</v>
@@ -8731,16 +8701,16 @@
     </row>
     <row r="65" spans="1:35">
       <c r="A65" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B65" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E65" t="s">
         <v>21</v>
@@ -8838,85 +8808,85 @@
     </row>
     <row r="66" spans="1:35">
       <c r="A66" t="s">
+        <v>339</v>
+      </c>
+      <c r="B66" t="s">
+        <v>340</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>341</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" t="s">
+        <v>17</v>
+      </c>
+      <c r="O66" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>21</v>
+      </c>
+      <c r="R66" t="s">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s">
         <v>342</v>
-      </c>
-      <c r="B66" t="s">
-        <v>343</v>
-      </c>
-      <c r="C66" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" t="s">
-        <v>344</v>
-      </c>
-      <c r="E66" t="s">
-        <v>21</v>
-      </c>
-      <c r="F66" t="s">
-        <v>21</v>
-      </c>
-      <c r="G66" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66" t="s">
-        <v>21</v>
-      </c>
-      <c r="J66" t="s">
-        <v>21</v>
-      </c>
-      <c r="K66" t="s">
-        <v>21</v>
-      </c>
-      <c r="L66" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" t="s">
-        <v>21</v>
-      </c>
-      <c r="N66" t="s">
-        <v>17</v>
-      </c>
-      <c r="O66" t="s">
-        <v>21</v>
-      </c>
-      <c r="P66" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>21</v>
-      </c>
-      <c r="R66" t="s">
-        <v>21</v>
-      </c>
-      <c r="S66" t="s">
-        <v>21</v>
-      </c>
-      <c r="T66" t="s">
-        <v>21</v>
-      </c>
-      <c r="U66" t="s">
-        <v>21</v>
-      </c>
-      <c r="V66" t="s">
-        <v>21</v>
-      </c>
-      <c r="W66" t="s">
-        <v>21</v>
-      </c>
-      <c r="X66" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>345</v>
       </c>
       <c r="AB66" t="s">
         <v>21</v>
@@ -8945,16 +8915,16 @@
     </row>
     <row r="67" spans="1:35">
       <c r="A67" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B67" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E67" t="s">
         <v>21</v>
@@ -9052,19 +9022,19 @@
     </row>
     <row r="68" spans="1:35">
       <c r="A68" t="s">
+        <v>346</v>
+      </c>
+      <c r="B68" t="s">
+        <v>347</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>348</v>
+      </c>
+      <c r="E68" t="s">
         <v>349</v>
-      </c>
-      <c r="B68" t="s">
-        <v>350</v>
-      </c>
-      <c r="C68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" t="s">
-        <v>351</v>
-      </c>
-      <c r="E68" t="s">
-        <v>352</v>
       </c>
       <c r="F68" t="s">
         <v>21</v>
@@ -9159,19 +9129,19 @@
     </row>
     <row r="69" spans="1:35">
       <c r="A69" t="s">
+        <v>350</v>
+      </c>
+      <c r="B69" t="s">
+        <v>351</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" t="s">
+        <v>352</v>
+      </c>
+      <c r="E69" t="s">
         <v>353</v>
-      </c>
-      <c r="B69" t="s">
-        <v>354</v>
-      </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" t="s">
-        <v>355</v>
-      </c>
-      <c r="E69" t="s">
-        <v>356</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -9266,67 +9236,67 @@
     </row>
     <row r="70" spans="1:35">
       <c r="A70" t="s">
+        <v>354</v>
+      </c>
+      <c r="B70" t="s">
+        <v>355</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>356</v>
+      </c>
+      <c r="E70" t="s">
         <v>357</v>
       </c>
-      <c r="B70" t="s">
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" t="s">
+        <v>17</v>
+      </c>
+      <c r="O70" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" t="s">
         <v>358</v>
       </c>
-      <c r="C70" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="Q70" t="s">
+        <v>21</v>
+      </c>
+      <c r="R70" t="s">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s">
         <v>359</v>
-      </c>
-      <c r="E70" t="s">
-        <v>360</v>
-      </c>
-      <c r="F70" t="s">
-        <v>21</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70" t="s">
-        <v>21</v>
-      </c>
-      <c r="J70" t="s">
-        <v>21</v>
-      </c>
-      <c r="K70" t="s">
-        <v>21</v>
-      </c>
-      <c r="L70" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" t="s">
-        <v>21</v>
-      </c>
-      <c r="N70" t="s">
-        <v>17</v>
-      </c>
-      <c r="O70" t="s">
-        <v>21</v>
-      </c>
-      <c r="P70" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>21</v>
-      </c>
-      <c r="R70" t="s">
-        <v>21</v>
-      </c>
-      <c r="S70" t="s">
-        <v>21</v>
-      </c>
-      <c r="T70" t="s">
-        <v>21</v>
-      </c>
-      <c r="U70" t="s">
-        <v>362</v>
       </c>
       <c r="V70" t="s">
         <v>21</v>
@@ -9373,16 +9343,16 @@
     </row>
     <row r="71" spans="1:35">
       <c r="A71" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B71" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E71" t="s">
         <v>21</v>
@@ -9480,16 +9450,16 @@
     </row>
     <row r="72" spans="1:35">
       <c r="A72" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B72" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E72" t="s">
         <v>21</v>
@@ -9587,16 +9557,16 @@
     </row>
     <row r="73" spans="1:35">
       <c r="A73" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B73" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E73" t="s">
         <v>21</v>
@@ -9694,16 +9664,16 @@
     </row>
     <row r="74" spans="1:35">
       <c r="A74" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B74" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E74" t="s">
         <v>21</v>
@@ -9801,64 +9771,64 @@
     </row>
     <row r="75" spans="1:35">
       <c r="A75" t="s">
+        <v>372</v>
+      </c>
+      <c r="B75" t="s">
+        <v>373</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>371</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" t="s">
+        <v>17</v>
+      </c>
+      <c r="O75" t="s">
+        <v>21</v>
+      </c>
+      <c r="P75" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>21</v>
+      </c>
+      <c r="R75" t="s">
+        <v>374</v>
+      </c>
+      <c r="S75" t="s">
         <v>375</v>
       </c>
-      <c r="B75" t="s">
+      <c r="T75" t="s">
         <v>376</v>
-      </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" t="s">
-        <v>377</v>
-      </c>
-      <c r="E75" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" t="s">
-        <v>21</v>
-      </c>
-      <c r="G75" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s">
-        <v>21</v>
-      </c>
-      <c r="K75" t="s">
-        <v>21</v>
-      </c>
-      <c r="L75" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" t="s">
-        <v>21</v>
-      </c>
-      <c r="N75" t="s">
-        <v>17</v>
-      </c>
-      <c r="O75" t="s">
-        <v>21</v>
-      </c>
-      <c r="P75" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>21</v>
-      </c>
-      <c r="R75" t="s">
-        <v>378</v>
-      </c>
-      <c r="S75" t="s">
-        <v>379</v>
-      </c>
-      <c r="T75" t="s">
-        <v>380</v>
       </c>
       <c r="U75" t="s">
         <v>21</v>
@@ -9908,22 +9878,22 @@
     </row>
     <row r="76" spans="1:35">
       <c r="A76" t="s">
+        <v>377</v>
+      </c>
+      <c r="B76" t="s">
+        <v>378</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>379</v>
+      </c>
+      <c r="E76" t="s">
+        <v>380</v>
+      </c>
+      <c r="F76" t="s">
         <v>381</v>
-      </c>
-      <c r="B76" t="s">
-        <v>382</v>
-      </c>
-      <c r="C76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" t="s">
-        <v>383</v>
-      </c>
-      <c r="E76" t="s">
-        <v>384</v>
-      </c>
-      <c r="F76" t="s">
-        <v>385</v>
       </c>
       <c r="G76" t="s">
         <v>21</v>
@@ -10015,16 +9985,16 @@
     </row>
     <row r="77" spans="1:35">
       <c r="A77" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B77" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E77" t="s">
         <v>21</v>
@@ -10122,16 +10092,16 @@
     </row>
     <row r="78" spans="1:35">
       <c r="A78" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B78" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E78" t="s">
         <v>21</v>
@@ -10170,7 +10140,7 @@
         <v>21</v>
       </c>
       <c r="Q78" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="R78" t="s">
         <v>21</v>
@@ -10229,19 +10199,19 @@
     </row>
     <row r="79" spans="1:35">
       <c r="A79" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B79" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E79" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F79" t="s">
         <v>21</v>
@@ -10336,16 +10306,16 @@
     </row>
     <row r="80" spans="1:35">
       <c r="A80" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B80" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C80" t="s">
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E80" t="s">
         <v>21</v>
@@ -10443,16 +10413,16 @@
     </row>
     <row r="81" spans="1:35">
       <c r="A81" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B81" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E81" t="s">
         <v>21</v>
@@ -10550,16 +10520,16 @@
     </row>
     <row r="82" spans="1:35">
       <c r="A82" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B82" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C82" t="s">
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E82" t="s">
         <v>21</v>
@@ -10657,16 +10627,16 @@
     </row>
     <row r="83" spans="1:35">
       <c r="A83" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E83" t="s">
         <v>21</v>
@@ -10764,19 +10734,19 @@
     </row>
     <row r="84" spans="1:35">
       <c r="A84" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B84" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E84" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F84" t="s">
         <v>21</v>
@@ -10871,19 +10841,19 @@
     </row>
     <row r="85" spans="1:35">
       <c r="A85" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B85" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E85" t="s">
-        <v>416</v>
+        <v>197</v>
       </c>
       <c r="F85" t="s">
         <v>21</v>
@@ -10978,16 +10948,16 @@
     </row>
     <row r="86" spans="1:35">
       <c r="A86" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B86" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E86" t="s">
         <v>21</v>
@@ -11085,16 +11055,16 @@
     </row>
     <row r="87" spans="1:35">
       <c r="A87" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B87" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E87" t="s">
         <v>21</v>
@@ -11192,16 +11162,16 @@
     </row>
     <row r="88" spans="1:35">
       <c r="A88" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B88" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E88" t="s">
         <v>21</v>
@@ -11258,7 +11228,7 @@
         <v>21</v>
       </c>
       <c r="W88" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="X88" t="s">
         <v>21</v>
@@ -11270,16 +11240,16 @@
         <v>21</v>
       </c>
       <c r="AA88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AB88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AC88" t="s">
-        <v>427</v>
+        <v>151</v>
       </c>
       <c r="AD88" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AE88" t="s">
         <v>21</v>
@@ -11299,16 +11269,16 @@
     </row>
     <row r="89" spans="1:35">
       <c r="A89" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B89" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E89" t="s">
         <v>21</v>
@@ -11406,16 +11376,16 @@
     </row>
     <row r="90" spans="1:35">
       <c r="A90" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B90" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E90" t="s">
         <v>21</v>
@@ -11513,16 +11483,16 @@
     </row>
     <row r="91" spans="1:35">
       <c r="A91" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B91" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E91" t="s">
         <v>21</v>
@@ -11620,16 +11590,16 @@
     </row>
     <row r="92" spans="1:35">
       <c r="A92" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B92" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E92" t="s">
         <v>21</v>
@@ -11727,16 +11697,16 @@
     </row>
     <row r="93" spans="1:35">
       <c r="A93" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B93" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>443</v>
+        <v>247</v>
       </c>
       <c r="E93" t="s">
         <v>21</v>
@@ -11834,16 +11804,16 @@
     </row>
     <row r="94" spans="1:35">
       <c r="A94" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B94" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="E94" t="s">
         <v>21</v>
@@ -11941,16 +11911,16 @@
     </row>
     <row r="95" spans="1:35">
       <c r="A95" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B95" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E95" t="s">
         <v>21</v>
@@ -12048,10 +12018,10 @@
     </row>
     <row r="96" spans="1:35">
       <c r="A96" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B96" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
@@ -12060,7 +12030,7 @@
         <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F96" t="s">
         <v>21</v>
@@ -12155,10 +12125,10 @@
     </row>
     <row r="97" spans="1:35">
       <c r="A97" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B97" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -12167,7 +12137,7 @@
         <v>21</v>
       </c>
       <c r="E97" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
@@ -12262,10 +12232,10 @@
     </row>
     <row r="98" spans="1:35">
       <c r="A98" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B98" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
@@ -12274,7 +12244,7 @@
         <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="F98" t="s">
         <v>21</v>
@@ -12313,7 +12283,7 @@
         <v>21</v>
       </c>
       <c r="R98" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="S98" t="s">
         <v>21</v>
@@ -12369,10 +12339,10 @@
     </row>
     <row r="99" spans="1:35">
       <c r="A99" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
@@ -12381,7 +12351,7 @@
         <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="F99" t="s">
         <v>21</v>
@@ -12476,10 +12446,10 @@
     </row>
     <row r="100" spans="1:35">
       <c r="A100" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B100" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C100" t="s">
         <v>17</v>
@@ -12488,10 +12458,10 @@
         <v>21</v>
       </c>
       <c r="E100" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F100" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="G100" t="s">
         <v>21</v>
@@ -12527,7 +12497,7 @@
         <v>21</v>
       </c>
       <c r="R100" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="S100" t="s">
         <v>21</v>
@@ -12583,10 +12553,10 @@
     </row>
     <row r="101" spans="1:35">
       <c r="A101" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B101" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
@@ -12595,7 +12565,7 @@
         <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="F101" t="s">
         <v>21</v>
@@ -12690,10 +12660,10 @@
     </row>
     <row r="102" spans="1:35">
       <c r="A102" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B102" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
@@ -12702,7 +12672,7 @@
         <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="F102" t="s">
         <v>21</v>
@@ -12797,10 +12767,10 @@
     </row>
     <row r="103" spans="1:35">
       <c r="A103" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B103" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C103" t="s">
         <v>17</v>
@@ -12809,7 +12779,7 @@
         <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F103" t="s">
         <v>21</v>
@@ -12904,10 +12874,10 @@
     </row>
     <row r="104" spans="1:35">
       <c r="A104" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B104" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C104" t="s">
         <v>17</v>
@@ -12916,7 +12886,7 @@
         <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F104" t="s">
         <v>21</v>
@@ -13011,10 +12981,10 @@
     </row>
     <row r="105" spans="1:35">
       <c r="A105" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B105" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C105" t="s">
         <v>17</v>
@@ -13023,7 +12993,7 @@
         <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F105" t="s">
         <v>21</v>
@@ -13118,10 +13088,10 @@
     </row>
     <row r="106" spans="1:35">
       <c r="A106" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B106" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C106" t="s">
         <v>17</v>
@@ -13130,7 +13100,7 @@
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>483</v>
+        <v>431</v>
       </c>
       <c r="F106" t="s">
         <v>21</v>
@@ -13225,10 +13195,10 @@
     </row>
     <row r="107" spans="1:35">
       <c r="A107" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="B107" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C107" t="s">
         <v>17</v>
@@ -13237,7 +13207,7 @@
         <v>21</v>
       </c>
       <c r="E107" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F107" t="s">
         <v>21</v>
@@ -13332,10 +13302,10 @@
     </row>
     <row r="108" spans="1:35">
       <c r="A108" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="B108" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C108" t="s">
         <v>17</v>
@@ -13344,7 +13314,7 @@
         <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F108" t="s">
         <v>21</v>
@@ -13439,10 +13409,10 @@
     </row>
     <row r="109" spans="1:35">
       <c r="A109" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="B109" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C109" t="s">
         <v>17</v>
@@ -13451,7 +13421,7 @@
         <v>21</v>
       </c>
       <c r="E109" t="s">
-        <v>491</v>
+        <v>439</v>
       </c>
       <c r="F109" t="s">
         <v>21</v>
@@ -13546,10 +13516,10 @@
     </row>
     <row r="110" spans="1:35">
       <c r="A110" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B110" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
@@ -13558,7 +13528,7 @@
         <v>21</v>
       </c>
       <c r="E110" t="s">
-        <v>494</v>
+        <v>151</v>
       </c>
       <c r="F110" t="s">
         <v>21</v>
@@ -13653,10 +13623,10 @@
     </row>
     <row r="111" spans="1:35">
       <c r="A111" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="B111" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="C111" t="s">
         <v>17</v>
@@ -13665,7 +13635,7 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>427</v>
+        <v>151</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
@@ -13760,10 +13730,10 @@
     </row>
     <row r="112" spans="1:35">
       <c r="A112" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B112" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C112" t="s">
         <v>17</v>
@@ -13772,7 +13742,7 @@
         <v>21</v>
       </c>
       <c r="E112" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -13867,10 +13837,10 @@
     </row>
     <row r="113" spans="1:35">
       <c r="A113" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B113" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C113" t="s">
         <v>17</v>
@@ -13882,7 +13852,7 @@
         <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G113" t="s">
         <v>21</v>
@@ -13974,10 +13944,10 @@
     </row>
     <row r="114" spans="1:35">
       <c r="A114" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="B114" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C114" t="s">
         <v>17</v>
@@ -14034,7 +14004,7 @@
         <v>21</v>
       </c>
       <c r="U114" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="V114" t="s">
         <v>21</v>
@@ -14081,10 +14051,10 @@
     </row>
     <row r="115" spans="1:35">
       <c r="A115" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B115" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C115" t="s">
         <v>17</v>
@@ -14111,7 +14081,7 @@
         <v>21</v>
       </c>
       <c r="K115" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="L115" t="s">
         <v>21</v>
